--- a/downloads/finance/output_automacao_financas.xlsx
+++ b/downloads/finance/output_automacao_financas.xlsx
@@ -34129,7 +34129,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F333"/>
+  <dimension ref="A1:E167"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -34147,9 +34147,6 @@
       <c r="E1" t="str">
         <v>campos</v>
       </c>
-      <c r="F1" t="str">
-        <v>tipo_campo</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -34167,1336 +34164,1135 @@
       <c r="E2" t="str">
         <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real</v>
       </c>
-      <c r="F2" t="str">
-        <v>Campo Calculado</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Resultado financeiro - Grupo econômico</v>
+        <v>CTR12 - Inflação - Global por Nota FIscal MoM</v>
       </c>
       <c r="B3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmico/2-FateGPSAP</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CTR12-Inflao-GlobalporNotaFIscalMoM/1-InflaoGlobalGeral</v>
       </c>
       <c r="C3" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
+        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; BISTGBRONZE.EXCEL_IMP_INFLACAO_PRODUTO; Filtros e Parâmetros; Init Param</v>
       </c>
       <c r="D3" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/923/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1578/lineage</v>
       </c>
       <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Botão Aplicar; Consulta do SQL personalizado (Count); Filtro Última Registro Concat; True; VISAO; Visão; VL_INFLACAO; VLM_ANTERIOR; VLM_ATUAL; CD_PRODUTO_COMPRAS; Código do Produto; Filtro MoM; Filtro Rank; Filtro Variação; FILTRO_MOM; Index; NM_FAMILIA; NM_PRODUTO_COMPRAS; NM_SUBFAMILIA; Nome da Família; Nome da Subfamília; Nome do Produto; PERC_RANK; PERC_VARIACAO; QT_TOTAL_COMPRA; Qtd Total; RANK_ACUMULADO; UN; Valor Total; VL_MEDIA_ANT_ZERO; VL_TOTAL_COMPRA; VL_VARIACAO; VM_ANTERIOR; VM_ATUAL; Cd Filial; Dt Carga; EXCEL_IMP_INFLACAO_PRODUTO (Count); FL_MES_EXPURGO; Mês; Mês expurgo; NM_FILIAL; NM_SEGMENTO; Sk Data; [fn] Data acesso; [fn] Usuario; Botão Atualizar; CD_BUSINESS_UNIT; CD_DIRETORIA; CD_FAMILIA; CD_FILIAL; CD_REGIONAL; CD_SEGMENTO; Concat Diretoria; Concat Familia; Concat Filial; Concat Filial 1; Concat Filial 10; Concat Filial 11; Concat Filial 12; Concat Filial 2; Concat Filial 3; Concat Filial 4; Concat Filial 5; Concat Filial 6; Concat Filial 7; Concat Filial 8; Concat Filial 9; Concat Filial Aux; Concat Regional; Concat Segmento; Concat Test 1; Concat Test 2; Concat Tipo Contrato; Concat Tipo Entrega; Concat Tipo Serviço; lbl DataHora; lbl Usuario; NM_BUSINESS_UNIT; NM_DIRETORIA; FILIAL_1; FILIAL_10; FILIAL_11; FILIAL_12; FILIAL_2; FILIAL_3; FILIAL_4; FILIAL_5; FILIAL_6; FILIAL_7; FILIAL_8; FILIAL_9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CTR12 - Inflação - Global por Nota FIscal MoM</v>
+        <v>Antecipado DF</v>
       </c>
       <c r="B4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CTR12-Inflao-GlobalporNotaFIscalMoM/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AntecipadoDF/Painel1</v>
       </c>
       <c r="C4" t="str">
-        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; BISTGBRONZE.EXCEL_IMP_INFLACAO_PRODUTO; Filtros e Parâmetros; Init Param</v>
+        <v>SAÍDAS POR ITENS 09.2023.csv++ (Múltiplas conexões)</v>
       </c>
       <c r="D4" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1578/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E4" t="str">
-        <v>:Measure Names; Botão Aplicar; Consulta do SQL personalizado (Count); Filtro Última Registro Concat; True; VISAO; Visão; VL_INFLACAO; VLM_ANTERIOR; VLM_ATUAL; CD_PRODUTO_COMPRAS; Código do Produto; Filtro MoM; Filtro Rank; Filtro Variação; FILTRO_MOM; Index; NM_FAMILIA; NM_PRODUTO_COMPRAS; NM_SUBFAMILIA; Nome da Família; Nome da Subfamília; Nome do Produto; PERC_RANK; PERC_VARIACAO; QT_TOTAL_COMPRA; Qtd Total; RANK_ACUMULADO; UN; Valor Total; VL_MEDIA_ANT_ZERO; VL_TOTAL_COMPRA; VL_VARIACAO; VM_ANTERIOR; VM_ATUAL; Cd Filial; Dt Carga; EXCEL_IMP_INFLACAO_PRODUTO (Count); FL_MES_EXPURGO; Mês; Mês expurgo; NM_FILIAL; NM_SEGMENTO; Sk Data; [fn] Data acesso; [fn] Usuario; Botão Atualizar; CD_BUSINESS_UNIT; CD_DIRETORIA; CD_FAMILIA; CD_FILIAL; CD_REGIONAL; CD_SEGMENTO; Concat Diretoria; Concat Familia; Concat Filial; Concat Filial 1; Concat Filial 10; Concat Filial 11; Concat Filial 12; Concat Filial 2; Concat Filial 3; Concat Filial 4; Concat Filial 5; Concat Filial 6; Concat Filial 7; Concat Filial 8; Concat Filial 9; Concat Filial Aux; Concat Regional; Concat Segmento; Concat Test 1; Concat Test 2; Concat Tipo Contrato; Concat Tipo Entrega; Concat Tipo Serviço; lbl DataHora; lbl Usuario; NM_BUSINESS_UNIT; NM_DIRETORIA; FILIAL_1; FILIAL_10; FILIAL_11; FILIAL_12; FILIAL_2; FILIAL_3; FILIAL_4; FILIAL_5; FILIAL_6; FILIAL_7; FILIAL_8; FILIAL_9</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Campo Calculado</v>
+        <v>Aliquota ICMS; Base FCP; Base ICMS; Base IPI; BC com reducao; Cálculo MVA; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CNPJ Remetente; Cst Icms; Data Lançamento; Descrição do material; Despesa; ENTRADAS POR ITENS 09_2023.csv (Count); FCP aliq; Filial; ICMS ajustado; ICMS antecipado; ICMS Com MVA e Red; ICMS interestadual; ICMS interna; index; IPI aliq; Item Texto; MVA; NCM; NCM (NCM DF ANTECIPADO.csv)1; NCM DF ANTECIPADO.csv (Count); NF; Nº do material; Nº documento; Nº item do documento; Número Pedido Item; Path; Quantidade; Reducao; Série; Tipo NF; UF</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CTR12 - Inflação - Global por Nota FIscal MoM</v>
+        <v>Menu de Dashboards - Finanças para segmento</v>
       </c>
       <c r="B5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CTR12-Inflao-GlobalporNotaFIscalMoM/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MenudeDashboards-Finanasparasegmento/Menudedashboards-Finanasparasegmento</v>
       </c>
       <c r="C5" t="str">
-        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; BISTGBRONZE.EXCEL_IMP_INFLACAO_PRODUTO; Filtros e Parâmetros; Init Param</v>
+        <v>Centro_Lucro</v>
       </c>
       <c r="D5" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1578/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage</v>
       </c>
       <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Antecipado DF</v>
+        <v>CTR11 - Inflação - Global por Nota FIscal YoY</v>
       </c>
       <c r="B6" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AntecipadoDF/Painel1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CTR11-Inflao-GlobalporNotaFIscalYoY/1-InflaoGlobalGeral</v>
       </c>
       <c r="C6" t="str">
-        <v>SAÍDAS POR ITENS 09.2023.csv++ (Múltiplas conexões)</v>
+        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; Filtros e Parâmetros; Init Param</v>
       </c>
       <c r="D6" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/640/lineage</v>
       </c>
       <c r="E6" t="str">
-        <v>Aliquota ICMS; Base FCP; Base ICMS; Base IPI; BC com reducao; Cálculo MVA; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CNPJ Remetente; Cst Icms; Data Lançamento; Descrição do material; Despesa; ENTRADAS POR ITENS 09_2023.csv (Count); FCP aliq; Filial; ICMS ajustado; ICMS antecipado; ICMS Com MVA e Red; ICMS interestadual; ICMS interna; index; IPI aliq; Item Texto; MVA; NCM; NCM (NCM DF ANTECIPADO.csv)1; NCM DF ANTECIPADO.csv (Count); NF; Nº do material; Nº documento; Nº item do documento; Número Pedido Item; Path; Quantidade; Reducao; Série; Tipo NF; UF</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Botão Aplicar; Consulta do SQL personalizado (Count); Filtro Última Registro Concat; True; VISAO; Visão; VL_INFLACAO; VLM_ANTERIOR; VLM_ATUAL; CD_PRODUTO_COMPRAS; Código do Produto; Filtro Rank; Filtro Variação; Index; NM_FAMILIA; NM_PRODUTO_COMPRAS; NM_SUBFAMILIA; Nome da Família; Nome da Subfamília; Nome do Produto; PERC_RANK; PERC_VARIACAO; QT_TOTAL_COMPRA; Qtd Total; RANK_ACUMULADO; UN; Valor Total; VL_TOTAL_COMPRA; VL_VARIACAO; VM_ANTERIOR; VM_ATUAL; [fn] Data acesso; [fn] Usuario; Botão Atualizar; CD_DIRETORIA; CD_FAMILIA; CD_FILIAL; CD_REGIONAL; CD_SEGMENTO; Concat Diretoria; Concat Familia; Concat Filial; Concat Filial 1; Concat Filial 10; Concat Filial 11; Concat Filial 12; Concat Filial 2; Concat Filial 3; Concat Filial 4; Concat Filial 5; Concat Filial 6; Concat Filial 7; Concat Filial 8; Concat Filial 9; Concat Filial Aux; Concat Regional; Concat Segmento; Concat Tipo Contrato; Concat Tipo Entrega; Concat Tipo Serviço; lbl DataHora; lbl Usuario; NM_DIRETORIA; NM_FILIAL; NM_REGIONAL; NM_SEGMENTO; NM_TIPO_CONTRATO; NM_TIPO_ENTREGA; FILIAL_1; FILIAL_10; FILIAL_11; FILIAL_12; FILIAL_2; FILIAL_3; FILIAL_4; FILIAL_5; FILIAL_6; FILIAL_7; FILIAL_8; FILIAL_9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Antecipado DF</v>
+        <v>IE01 - Performance de Atendimento</v>
       </c>
       <c r="B7" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AntecipadoDF/Painel1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento_17483757698620/PerformancedeAtendimento</v>
       </c>
       <c r="C7" t="str">
-        <v>SAÍDAS POR ITENS 09.2023.csv++ (Múltiplas conexões)</v>
+        <v>BICSCFINANCAS - Chamados; BICSCFINANCAS - Pesquisa Satisfação</v>
       </c>
       <c r="D7" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/59662/lineage; https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage</v>
       </c>
       <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Cancelados; % Cancelados + Reabertos; % Reabertos; % Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Usuario; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; Cálculo1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Mês Selecionado (copy); CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; Custom SQL Query (Count); Custom SQL Query1 (Count); Domain; DS_CANAL; DS_CATEGORIA_PRINCIPAL; DS_CATEGORIA_PRINCIPAL (Custom SQL Query1); DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); Dt Competência Anterior (short text) (copy); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; EMAIL; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Anterior 2; Filtro Mês Selecionado; Filtro Mês Selecionado 2; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Detrator Entrega Comparativo (copy); Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Promotor Entrega Comparativo (copy); Gauge Respondidos vs Concluídos Comparativo</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Menu de Dashboards - Finanças para segmento</v>
+        <v>DSO FY26</v>
       </c>
       <c r="B8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MenudeDashboards-Finanasparasegmento/Menudedashboards-Finanasparasegmento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/DSOFY26/1-DSO</v>
       </c>
       <c r="C8" t="str">
-        <v>Centro_Lucro</v>
+        <v>Centro_Lucro; Base (BASE DASH DSO - BRAZIL FY24); Planilha1 (Target Segmentos)</v>
       </c>
       <c r="D8" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2287/lineage</v>
       </c>
       <c r="E8" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; :Measure Names; Base (Count); Cálculo1; Centro de Lucro; Cliente1; Contas a receber; Contas a receber S/ overdue; Contas a receber S/ provisão; Contas a receber total; CUGR; CUGR (grupo); Datas; DD; Dias; Dias após Vencimento; Diretoria1; DSO; DSO contas a receber; DSO num+petro; DSO OVERDUE; DSO provisão; DSO S/Overdue; Empresa; Faturamento Tri; Faturamento Tri (cópia); FY1; index; Numera+petrobras; Númerário em Trânsito; Overdue_PDD; Periodo; Petrobrás; Provisão; Regional; Segmento1; Serviço; Status1; Teste; Tipo1; TOTAL DSO CÁLCULO; F1; F2; F3; Planilha1 (Count); Variação</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Menu de Dashboards - Finanças para segmento</v>
+        <v>Manifestadas</v>
       </c>
       <c r="B9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MenudeDashboards-Finanasparasegmento/Menudedashboards-Finanasparasegmento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Manifestadas/Manifestadaajustada</v>
       </c>
       <c r="C9" t="str">
-        <v>Centro_Lucro</v>
+        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
       </c>
       <c r="D9" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2463/lineage</v>
       </c>
       <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cd Business Unit; Cd Cardapio; Cd Centro Lucro; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Grupoeconomico; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Regional; Cd Segmento; Cd Site; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Abertura; Dt Carga (Vw Mdt Centro Lucro); Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Centro Custo; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; Chave NF; CL Provisão; Planilha1 (Count); Chave NFe; Chave NFe2; CL; CNPJ Fornecedor; Conta; Conta concat; Data atual; Data de reversão; Data de reversão (grupo); Data provisão; Data reversão 2; Dias vencimento; Diferença dias; Emissão NF; Fornecedor; Lançamento provisão; Nº Nf; Origem Da Identificação; Provisão; Provisão (grupo); Provisão (grupo) 1; Provisão Notas fora (Count); Reversão; Série; Status; Tipo; Tipo (grupo); Valor NF</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>CTR11 - Inflação - Global por Nota FIscal YoY</v>
+        <v>SKO01 - Performance Operacional de Atendimento</v>
       </c>
       <c r="B10" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CTR11-Inflao-GlobalporNotaFIscalYoY/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IE02-PerformanceOperacionaldeAtendimento/VE-VisoEficiencia</v>
       </c>
       <c r="C10" t="str">
-        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; Filtros e Parâmetros; Init Param</v>
+        <v>BICSCFINANCAS - CA_IVANTI - Tabela SLA Limits; BICSCFINANCAS - Capacidade de Atendimento de Chamados</v>
       </c>
       <c r="D10" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/640/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/43900/lineage; https://analyticsbi.sodexo.com.br/#/datasources/43901/lineage</v>
       </c>
       <c r="E10" t="str">
-        <v>:Measure Names; Botão Aplicar; Consulta do SQL personalizado (Count); Filtro Última Registro Concat; True; VISAO; Visão; VL_INFLACAO; VLM_ANTERIOR; VLM_ATUAL; CD_PRODUTO_COMPRAS; Código do Produto; Filtro Rank; Filtro Variação; Index; NM_FAMILIA; NM_PRODUTO_COMPRAS; NM_SUBFAMILIA; Nome da Família; Nome da Subfamília; Nome do Produto; PERC_RANK; PERC_VARIACAO; QT_TOTAL_COMPRA; Qtd Total; RANK_ACUMULADO; UN; Valor Total; VL_TOTAL_COMPRA; VL_VARIACAO; VM_ANTERIOR; VM_ATUAL; [fn] Data acesso; [fn] Usuario; Botão Atualizar; CD_DIRETORIA; CD_FAMILIA; CD_FILIAL; CD_REGIONAL; CD_SEGMENTO; Concat Diretoria; Concat Familia; Concat Filial; Concat Filial 1; Concat Filial 10; Concat Filial 11; Concat Filial 12; Concat Filial 2; Concat Filial 3; Concat Filial 4; Concat Filial 5; Concat Filial 6; Concat Filial 7; Concat Filial 8; Concat Filial 9; Concat Filial Aux; Concat Regional; Concat Segmento; Concat Tipo Contrato; Concat Tipo Entrega; Concat Tipo Serviço; lbl DataHora; lbl Usuario; NM_DIRETORIA; NM_FILIAL; NM_REGIONAL; NM_SEGMENTO; NM_TIPO_CONTRATO; NM_TIPO_ENTREGA; FILIAL_1; FILIAL_10; FILIAL_11; FILIAL_12; FILIAL_2; FILIAL_3; FILIAL_4; FILIAL_5; FILIAL_6; FILIAL_7; FILIAL_8; FILIAL_9</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Campo Calculado</v>
+        <v>blank; Custom SQL Query (Count); Desv Pad (fixed); Domain; Dsc Dia; Dsc Dia (Dia); Dsc Hierarquia; Dsc Macroprocesso; Dt Competência - dia; Dt Competência - MesAno; Filtro Mês Atual; Flg Sla Violado; New Nr Chamados Resolvidos (cor); Nm Colaborador; Nm Grupo; Nm Responsavel; Nr Chamados Aberto; Nr Chamados Resolvidos; Nr Chamados Resolvidos (Cor); Nr Chamados Resolvidos (Gauge); NR_CHAMADOS_ABERTOS; NR_CHAMADOS_RESOLVIDOS; Origem; Perc Aderencia SLA; Perc Eixo; Perc Sla Violado; Perc Sla Violado (kpi); RPA; Vl Desv Pad; Vl Desv Pad (kpi); Vl Máx Entre Resolvidos e Abertos; Vl Média Diária; Vl Média Diária (kpi); Vl Média Diária (Max); Vl Média Diária (Max) (kpi); Vl Média Diária + Desv Pad; Vl Média Diária + Desv Pad (fixed); Vl Média Diária + Desv Pad (Gauge); Vl Média Diária + Desv Pad (kpi); % Chamados; % Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Data atualização New; [fn] Usuario; Ano Fiscal; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; CC: Nr Dias Atendimento (c/ pendente)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CTR11 - Inflação - Global por Nota FIscal YoY</v>
+        <v>INV01 - P2P Invoice Processing</v>
       </c>
       <c r="B11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CTR11-Inflao-GlobalporNotaFIscalYoY/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/INV01-P2PInvoiceProcessing/Documentoslanados</v>
       </c>
       <c r="C11" t="str">
-        <v>BICompras - Compras Mensal; BICompras - Compras Mensal Detalhe; Filtros e Parâmetros; Init Param</v>
+        <v>BICSCFINANCAS - Invoice Processing; BICSCFINANCAS - Invoice Processing Menu; BICSCFINANCAS - Invoice Processing XPED</v>
       </c>
       <c r="D11" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/640/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48322/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17523/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17527/lineage</v>
       </c>
       <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>[fn] Data atualização; [fn] Usuario; Cd Business Unit; Cd Diretoria; Cd Filial; Cd Regional; Cd Segmento; CD_CONDICOES_PGTO; Dsc Categoria; Dsc Período; Dt Carga; Dt Competencia; Dt Competência (Max); Filtro Ano Anterior; Filtro Dt Competência 13 Meses; Filtro Mês Anterior; Filtro Mês Atual; Filtro Tp Nf; Gauge Mês Atual x Ano Anter; Gauge Mês Atual x Mês Anter; lbl DataHora; lbl Usuario; Nm Arquivo; Nm Business Unit; Nm Diretoria; Nm Filial; Nm Regional; Nm Segmento; Nr Ano Fiscal; Tp Extemporaneas; Tp Nf; Vl Qtd Mês Atual x Ano Anter; Vl Qtd Mês Atual x Mês Anter; Vl Quantidade; VL_MONTANTE_MOEDA_INTERNA; VW_F_CSC_INV (Count); Cd Menu; Dsc Menu; Dummy; Filtro Menu; MENU_INVOICE_PROCESSING (Count); Nm Origem; Tp Nitemped; Tp Xped; Vl Quantidade (w/o null); VW_F_CSC_XPED (Count)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IE01 - Performance de Atendimento</v>
+        <v>Reajuste</v>
       </c>
       <c r="B12" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento_17483757698620/PerformancedeAtendimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Reajuste_16860831886180/Basereajuste</v>
       </c>
       <c r="C12" t="str">
-        <v>BICSCFINANCAS - Chamados; BICSCFINANCAS - Pesquisa Satisfação</v>
+        <v>Reajuste_Contrato; Planilha2 (Reajuste_Preço - Target FY26)</v>
       </c>
       <c r="D12" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/59662/lineage; https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/489/lineage</v>
       </c>
       <c r="E12" t="str">
-        <v>% Cancelados; % Cancelados + Reabertos; % Reabertos; % Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Usuario; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; Cálculo1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Mês Selecionado (copy); CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; Custom SQL Query (Count); Custom SQL Query1 (Count); Domain; DS_CANAL; DS_CATEGORIA_PRINCIPAL; DS_CATEGORIA_PRINCIPAL (Custom SQL Query1); DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); Dt Competência Anterior (short text) (copy); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; EMAIL; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Anterior 2; Filtro Mês Selecionado; Filtro Mês Selecionado 2; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Detrator Entrega Comparativo (copy); Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Promotor Entrega Comparativo (copy); Gauge Respondidos vs Concluídos Comparativo</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; ANDAMENTO; CODUNIDADEFILIAL; Dados migrados (Count); DATAHORAFIMHIST; DATAHORAINICIOHIST; DATAMESCORRENTE; DATAMESREAJUSTERETROATIVO; DATAREAJUSTERETROATIVO; DESCINDICECOMPOSICAOREAJUSTE; DESCSITUACAOPROCESSO; DESCWORKFLOW; DIFERENCAAPLICADOCALCULADO; FATORMESACUMULADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; Cálculo1 reajuste budget; CL; Data; Planilha2 (Count); Reajuste Budget</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>IE01 - Performance de Atendimento</v>
+        <v>FISCAL09 - Painel Check de Valores (XML vs Nota)</v>
       </c>
       <c r="B13" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento_17483757698620/PerformancedeAtendimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL09-PainelCheckdeValoresXMLvsNota/CheckdeValores-XmlvsLanamento</v>
       </c>
       <c r="C13" t="str">
-        <v>BICSCFINANCAS - Chamados; BICSCFINANCAS - Pesquisa Satisfação</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
       </c>
       <c r="D13" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/59662/lineage; https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/10/lineage</v>
       </c>
       <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Dif Valor; Diferença VL XML vs NF</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>DSO FY26</v>
+        <v>P2P01 - P2P Títulos</v>
       </c>
       <c r="B14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DSOFY26/1-DSO</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/P2P01-P2PTtulos/SpendeOutrosIndicadores</v>
       </c>
       <c r="C14" t="str">
-        <v>Centro_Lucro; Base (BASE DASH DSO - BRAZIL FY24); Planilha1 (Target Segmentos)</v>
+        <v>BICSCFINANCAS - P2P Títulos</v>
       </c>
       <c r="D14" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2287/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
       </c>
       <c r="E14" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; :Measure Names; Base (Count); Cálculo1; Centro de Lucro; Cliente1; Contas a receber; Contas a receber S/ overdue; Contas a receber S/ provisão; Contas a receber total; CUGR; CUGR (grupo); Datas; DD; Dias; Dias após Vencimento; Diretoria1; DSO; DSO contas a receber; DSO num+petro; DSO OVERDUE; DSO provisão; DSO S/Overdue; Empresa; Faturamento Tri; Faturamento Tri (cópia); FY1; index; Numera+petrobras; Númerário em Trânsito; Overdue_PDD; Periodo; Petrobrás; Provisão; Regional; Segmento1; Serviço; Status1; Teste; Tipo1; TOTAL DSO CÁLCULO; F1; F2; F3; Planilha1 (Count); Variação</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Campo Calculado</v>
+        <v>% Total VL_MONTANTE; :Measure Names; BN - % Total; BN - % Total (copy); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO; CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto) (gauge); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto,); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual) (gauge); CC: VL_QUANTIDADE (Pagamento auto,); CC: VL_QUANTIDADE (Pagamento manual); CD_CONDICOES_PGTO; Custom SQL Query (Count); DSC_AGING; DSC_AGING_FINAL; DSC_AGING_VENCIDOS; DSC_CATEGORIA; DSC_CLASSIFICACAO_CONTA; DSC_POLITICA; DSC_POLITICA (cópia); DSC_PRAZO; DSC_STATUS_TITULO; DT_ANALISE; Filtro Data Competência; Filtro Data Competência (M-1); Filtro Data Competência (M-2); Filtro nulos analise de aging; FY; Hoje(); Max Dt Analise; NM_BANCO_PAGADOR; Perc valor montante vencido; PERC_VENCIDOS; Período; QT_TITULOS_PAGOS_SEM_BONIF; QT_TITULOS_PAGOS_SEM_BONIF (Evolução); QT_TITULOS_PAGOS_SEM_BONIF (Evolução) (gauge); QT_TITULOS_PAGOS_SEM_BONIF_AJUST; QT_TITULOS_PAGOS_SEM_BONIF_AJUST (Rótulo); RANK 1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DSO FY26</v>
+        <v>FISCAL08 - Painel Notas Incluídas vs Canceladas ou Operação ñ Realizada</v>
       </c>
       <c r="B15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DSOFY26/1-DSO</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL08-PainelNotasIncludasvsCanceladasouOperaoRealizada/Painel-NFsIncludasvsCanceladasouOperaoRealizada</v>
       </c>
       <c r="C15" t="str">
-        <v>Centro_Lucro; Base (BASE DASH DSO - BRAZIL FY24); Planilha1 (Target Segmentos)</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
       </c>
       <c r="D15" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2287/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/23/lineage</v>
       </c>
       <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; contagem; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Manifestadas</v>
+        <v>SLA Performance Insights</v>
       </c>
       <c r="B16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Manifestadas/Manifestadaajustada</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/SLAPerformanceInsights_17550940970210/SLAPerformanceInsights-Cancelamentos</v>
       </c>
       <c r="C16" t="str">
-        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
+        <v>BICSCFINANCAS - Pesquisa Satisfação; BIGOLD - Chamados Ivanti</v>
       </c>
       <c r="D16" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2463/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage; https://analyticsbi.sodexo.com.br/#/datasources/40609/lineage</v>
       </c>
       <c r="E16" t="str">
-        <v>Cd Business Unit; Cd Cardapio; Cd Centro Lucro; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Grupoeconomico; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Regional; Cd Segmento; Cd Site; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Abertura; Dt Carga (Vw Mdt Centro Lucro); Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Centro Custo; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; Chave NF; CL Provisão; Planilha1 (Count); Chave NFe; Chave NFe2; CL; CNPJ Fornecedor; Conta; Conta concat; Data atual; Data de reversão; Data de reversão (grupo); Data provisão; Data reversão 2; Dias vencimento; Diferença dias; Emissão NF; Fornecedor; Lançamento provisão; Nº Nf; Origem Da Identificação; Provisão; Provisão (grupo); Provisão (grupo) 1; Provisão Notas fora (Count); Reversão; Série; Status; Tipo; Tipo (grupo); Valor NF</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Custom SQL Query (Count); Custom SQL Query1 (Count); Domain; DS_CANAL; DS_CATEGORIA_PRINCIPAL; DS_CATEGORIA_PRINCIPAL (Custom SQL Query1); DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); Dt Competência Anterior (short text) (copy); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; EMAIL; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Anterior 2; Filtro Mês Selecionado; Filtro Mês Selecionado 2; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Detrator Entrega Comparativo (copy); Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Promotor Entrega Comparativo (copy); Gauge Respondidos vs Concluídos Comparativo; Cd Chamado; Cd Uf; Dh Processamento (Evt Chamado Ivanti); Ds Canal; Ds Canal (Vw Fin F Chamado Pesquisa Ivanti Ca); Ds Categoria; Ds Comentario; Ds Detalhe Resolucao; Ds Estado; Ds Hierarquia; Ds Nivel Urgencia; Ds Origem; Ds Razao Cancelamento; Ds Razao Cancelamento Cliente; Ds Resumo; Ds Tipo Solicitacao; DS_CATEGORIA_PRINCIPAL (VW_FIN_F_CHAMADO_PESQUISA_IVANTI_CA); Dsc Canal De Atendimento; Dsc Cancelado Por; Dsc Cancelamento; Dsc Categoria; Dsc Categoria (Vw Fin F Chamado Pesquisa Ivanti Ca); Dsc Comentario Resposta; Dsc Comprovante Pagamento; Dsc Domain; Dsc Domain (Vw Fin F Chamado Pesquisa Ivanti Ca); Dsc Grupo; Dsc Macroprocesso; Dsc Pesquisa Respondida; Dsc Rsp Atendimento; Dsc Rsp Entrega; Dsc Solucao; Dsc Status; Dsc Subprocesso; Dt Abertura; Dt Abertura (Vw Fin F Chamado Pesquisa Ivanti Ca); Dt Cancelado Em; Dt Carga; Dt Carga (Evt Chamado Ivanti)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Manifestadas</v>
+        <v>SKO02 - Performance Operacional de Rotina e Demandas</v>
       </c>
       <c r="B17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Manifestadas/Manifestadaajustada</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PerformanceOperacionaldeRotinaeDemandas/DashboardProcessos</v>
       </c>
       <c r="C17" t="str">
-        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
+        <v>Base Processos - smartsheet</v>
       </c>
       <c r="D17" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2463/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E17" t="str">
-        <v/>
-      </c>
-      <c r="F17" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Parâmetro; :Measure Names; 0; Ano fiscal; Base de Processos (Count); Cálculo em dias; Cálculo horas no mês; Cálculo2; Carga horária; Contagem Parâmetro; Data; Domain; Dt Competência; Dt Competência (MAX); Eixo; Esforço dedicado (Horas); Filtro 12 meses; Filtro Mês Atual; FTE; FTE Ajustado; Macroprocesso; Média FTE; Média FTE Ajustado; Parâmetro; Período; Processo; Rank; Responsável; Subprocesso; Tempo; Tempo (Horas); Tempo médio; Tipo; Volume; Volume médio; Volume mensal</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SKO01 - Performance Operacional de Atendimento</v>
+        <v>Vendas FY25</v>
       </c>
       <c r="B18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE02-PerformanceOperacionaldeAtendimento/VE-VisoEficiencia</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY25V3_17485411362870/Relatriodevendas</v>
       </c>
       <c r="C18" t="str">
-        <v>BICSCFINANCAS - CA_IVANTI - Tabela SLA Limits; BICSCFINANCAS - Capacidade de Atendimento de Chamados</v>
+        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
       </c>
       <c r="D18" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/43900/lineage; https://analyticsbi.sodexo.com.br/#/datasources/43901/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2119/lineage</v>
       </c>
       <c r="E18" t="str">
-        <v>blank; Custom SQL Query (Count); Desv Pad (fixed); Domain; Dsc Dia; Dsc Dia (Dia); Dsc Hierarquia; Dsc Macroprocesso; Dt Competência - dia; Dt Competência - MesAno; Filtro Mês Atual; Flg Sla Violado; New Nr Chamados Resolvidos (cor); Nm Colaborador; Nm Grupo; Nm Responsavel; Nr Chamados Aberto; Nr Chamados Resolvidos; Nr Chamados Resolvidos (Cor); Nr Chamados Resolvidos (Gauge); NR_CHAMADOS_ABERTOS; NR_CHAMADOS_RESOLVIDOS; Origem; Perc Aderencia SLA; Perc Eixo; Perc Sla Violado; Perc Sla Violado (kpi); RPA; Vl Desv Pad; Vl Desv Pad (kpi); Vl Máx Entre Resolvidos e Abertos; Vl Média Diária; Vl Média Diária (kpi); Vl Média Diária (Max); Vl Média Diária (Max) (kpi); Vl Média Diária + Desv Pad; Vl Média Diária + Desv Pad (fixed); Vl Média Diária + Desv Pad (Gauge); Vl Média Diária + Desv Pad (kpi); % Chamados; % Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Data atualização New; [fn] Usuario; Ano Fiscal; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; CC: Nr Dias Atendimento (c/ pendente)</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Faturamento FY24; LY (Count); Regional; :Measure Names; Concat; Fat Real; Fat vendas; Faturamento ANUALIZADO; Faturamento ANUALIZADO META; Faturamento MF YTD; FY25 Fat OR; Fy25 Gp Or; Gp Mf Ytd; GP Real; GP Vendas Anualizado; Meta de vendas (Count); Tipo1; Vendas vs MF; Anualizado YTD; Diretoria; KPI Vendas; Meta de vendas (Meta de vendas); Meta vendas; Tipo; % GM vendas FY; CC1; City; Competitor; Contract duration in months; Data; Empresa; F25; F26; F27; Filtro tipo; Full year FC; Full year Gross Profit of new units; Full year sales of new units; FY Vendas Fat; GP FY Vendas; Mês; Motivo do Sucesso; Opening date; Period1; Planilha1 (Count); Regional1; Segment; Service; Signed date; Site; Site / Contract; Site Name; Subsegment; UF; UF, City; Cross selling; Novas vendas; Segmento; Total geral; Vendas + CS; Budget MF; Conversão; Period; Planilha2 (Count); Segmento1; Target; Taxa de conversão; % Desvio; % YTD MF; Conversão desvio; Desvio %; Desvio vendas; Fat desvio; GM % Real; GM%; GP Desvio; GP%; KPI (cópia) (cópia 2); KPI (último); KPI Budget; Período; Total (Count); Venda vs MF; Fili Cidade; Fili Codigo; Fili Nmdirecao; Fili Nmempresa; Fili Nmgrupoeconomico; Fili Nmregional; Fili Nmsegmento; Fili Nmsite; Fili Nmtipocontrato; Fili Nmtiposervico; Fili Nome; Fili Nomediretoroperacional; Fili Nomegerentearea; Fili Nomegerenteregional; Fili Tipofilial; Mês, Ano de FILI DTABERTURA; Mês, Ano de FILI DTENCERRAMENTO; Sheet 1 (Count)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SKO01 - Performance Operacional de Atendimento</v>
+        <v>FISCAL05 - Painel Gestão do Desconhecimento</v>
       </c>
       <c r="B19" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE02-PerformanceOperacionaldeAtendimento/VE-VisoEficiencia</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL05-PainelGestodoDesconhecimento/1-PainelGestodoDesconhecimento</v>
       </c>
       <c r="C19" t="str">
-        <v>BICSCFINANCAS - CA_IVANTI - Tabela SLA Limits; BICSCFINANCAS - Capacidade de Atendimento de Chamados</v>
+        <v>Varredura - XML NF Header</v>
       </c>
       <c r="D19" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/43900/lineage; https://analyticsbi.sodexo.com.br/#/datasources/43901/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
       </c>
       <c r="E19" t="str">
-        <v/>
-      </c>
-      <c r="F19" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Mascara 20 NL; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd pessoal NL; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; CNPJ Fornecedor NL; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>INV01 - P2P Invoice Processing</v>
+        <v>Tableau Reembolsos - Owner</v>
       </c>
       <c r="B20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/INV01-P2PInvoiceProcessing/Documentoslanados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/TableauReembolsos-Owner/Reembolso</v>
       </c>
       <c r="C20" t="str">
-        <v>BICSCFINANCAS - Invoice Processing; BICSCFINANCAS - Invoice Processing Menu; BICSCFINANCAS - Invoice Processing XPED</v>
+        <v>Relatório WF</v>
       </c>
       <c r="D20" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48322/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17523/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17527/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2285/lineage</v>
       </c>
       <c r="E20" t="str">
-        <v>[fn] Data atualização; [fn] Usuario; Cd Business Unit; Cd Diretoria; Cd Filial; Cd Regional; Cd Segmento; CD_CONDICOES_PGTO; Dsc Categoria; Dsc Período; Dt Carga; Dt Competencia; Dt Competência (Max); Filtro Ano Anterior; Filtro Dt Competência 13 Meses; Filtro Mês Anterior; Filtro Mês Atual; Filtro Tp Nf; Gauge Mês Atual x Ano Anter; Gauge Mês Atual x Mês Anter; lbl DataHora; lbl Usuario; Nm Arquivo; Nm Business Unit; Nm Diretoria; Nm Filial; Nm Regional; Nm Segmento; Nr Ano Fiscal; Tp Extemporaneas; Tp Nf; Vl Qtd Mês Atual x Ano Anter; Vl Qtd Mês Atual x Mês Anter; Vl Quantidade; VL_MONTANTE_MOEDA_INTERNA; VW_F_CSC_INV (Count); Cd Menu; Dsc Menu; Dummy; Filtro Menu; MENU_INVOICE_PROCESSING (Count); Nm Origem; Tp Nitemped; Tp Xped; Vl Quantidade (w/o null); VW_F_CSC_XPED (Count)</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Campo Calculado</v>
+        <v>Adto; Ano Fiscal; Aprovador; Autorização; Centro de lucro; Cód. SAP; Conta Contábil; Conta do Razão; Conta do Razão (Sheet1); Data de lançamento; Descrição; Descrição Conta; Descrição da Conta; Empresa; Exceção SAP; Filtro; Filtro (grupo); Link; Mês Fiscal; Nº documento; Nome Aprovador; Nome Colaborador; Nome do usuário; Owner; Owners; Portfólio; Referência; Relatório Geral (Count); Sheet1 (Count); Teste; Texto; TicketMédio; Tipo doc; Top; Valor; Workflow</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>INV01 - P2P Invoice Processing</v>
+        <v>Extração XML para Importação Mastersaf AM v3</v>
       </c>
       <c r="B21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/INV01-P2PInvoiceProcessing/Documentoslanados</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAMv3/PainelXMLMastersafAM</v>
       </c>
       <c r="C21" t="str">
-        <v>BICSCFINANCAS - Invoice Processing; BICSCFINANCAS - Invoice Processing Menu; BICSCFINANCAS - Invoice Processing XPED</v>
+        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
       </c>
       <c r="D21" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48322/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17523/lineage; https://analyticsbi.sodexo.com.br/#/datasources/17527/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
       </c>
       <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Reajuste</v>
+        <v>ADH10 - Base PVMv2</v>
       </c>
       <c r="B22" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Reajuste_16860831886180/Basereajuste</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ADH10-BasePVMv2/ADH10-BasePVMv2</v>
       </c>
       <c r="C22" t="str">
-        <v>Reajuste_Contrato; Planilha2 (Reajuste_Preço - Target FY26)</v>
+        <v>BICOMPRAS - Compras Diaria</v>
       </c>
       <c r="D22" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/489/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
       </c>
       <c r="E22" t="str">
-        <v>:Measure Names; ANDAMENTO; CODUNIDADEFILIAL; Dados migrados (Count); DATAHORAFIMHIST; DATAHORAINICIOHIST; DATAMESCORRENTE; DATAMESREAJUSTERETROATIVO; DATAREAJUSTERETROATIVO; DESCINDICECOMPOSICAOREAJUSTE; DESCSITUACAOPROCESSO; DESCWORKFLOW; DIFERENCAAPLICADOCALCULADO; FATORMESACUMULADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; Cálculo1 reajuste budget; CL; Data; Planilha2 (Count); Reajuste Budget</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Campo Calculado</v>
+        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Reajuste</v>
+        <v>Análise Prévia Consumo Outubro 2025</v>
       </c>
       <c r="B23" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Reajuste_16860831886180/Basereajuste</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoOutubro2025/AnlisePrviadoConsumo</v>
       </c>
       <c r="C23" t="str">
-        <v>Reajuste_Contrato; Planilha2 (Reajuste_Preço - Target FY26)</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/489/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E23" t="str">
         <v/>
-      </c>
-      <c r="F23" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FISCAL09 - Painel Check de Valores (XML vs Nota)</v>
+        <v>ADH07 - CD-PAP</v>
       </c>
       <c r="B24" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL09-PainelCheckdeValoresXMLvsNota/CheckdeValores-XmlvsLanamento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ADH07-CD-PAP/ADH7-CD-PAP</v>
       </c>
       <c r="C24" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/10/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E24" t="str">
-        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Dif Valor; Diferença VL XML vs NF</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>FISCAL09 - Painel Check de Valores (XML vs Nota)</v>
+        <v>Performance_Retails consolidado</v>
       </c>
       <c r="B25" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL09-PainelCheckdeValoresXMLvsNota/CheckdeValores-XmlvsLanamento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retailsconsolidado/PerformanceRetail</v>
       </c>
       <c r="C25" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v>Centro_Lucro; Contabil</v>
       </c>
       <c r="D25" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/10/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
       </c>
       <c r="E25" t="str">
-        <v/>
-      </c>
-      <c r="F25" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>P2P01 - P2P Títulos</v>
+        <v>Painel de Monitoramento de NFs x Ordens de compra</v>
       </c>
       <c r="B26" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/P2P01-P2PTtulos/SpendeOutrosIndicadores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeMonitoramentodeNFsxOrdensdecompra_17308902149110/VisoGeralNFs</v>
       </c>
       <c r="C26" t="str">
-        <v>BICSCFINANCAS - P2P Títulos</v>
+        <v>BICOMPRAS - NL Recebimento Ordem Compras; BISILVER - Finance - Nota Fiscal Recebimento</v>
       </c>
       <c r="D26" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/26392/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage</v>
       </c>
       <c r="E26" t="str">
-        <v>% Total VL_MONTANTE; :Measure Names; BN - % Total; BN - % Total (copy); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO; CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto) (gauge); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto,); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual) (gauge); CC: VL_QUANTIDADE (Pagamento auto,); CC: VL_QUANTIDADE (Pagamento manual); CD_CONDICOES_PGTO; Custom SQL Query (Count); DSC_AGING; DSC_AGING_FINAL; DSC_AGING_VENCIDOS; DSC_CATEGORIA; DSC_CLASSIFICACAO_CONTA; DSC_POLITICA; DSC_POLITICA (cópia); DSC_PRAZO; DSC_STATUS_TITULO; DT_ANALISE; Filtro Data Competência; Filtro Data Competência (M-1); Filtro Data Competência (M-2); Filtro nulos analise de aging; FY; Hoje(); Max Dt Analise; NM_BANCO_PAGADOR; Perc valor montante vencido; PERC_VENCIDOS; Período; QT_TITULOS_PAGOS_SEM_BONIF; QT_TITULOS_PAGOS_SEM_BONIF (Evolução); QT_TITULOS_PAGOS_SEM_BONIF (Evolução) (gauge); QT_TITULOS_PAGOS_SEM_BONIF_AJUST; QT_TITULOS_PAGOS_SEM_BONIF_AJUST (Rótulo); RANK 1</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_USUARIO; Dt Abertura; Dt Carga; Dt Encerramento; filtraExtração; Fl Familia Gerenciada; Fl Familia Integrante Cesta; Fl Ficticia; Fl Homologado; Fl Item Compra; Fl Obsoleto; Multiple Values; Cd Business Unit; Cd Centro Lucro; Cd Grupoeconomico; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Site; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Carga (Vw Mdt Centro Lucro)</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>P2P01 - P2P Títulos</v>
+        <v>Notas Lançadas Operação Mandato</v>
       </c>
       <c r="B27" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/P2P01-P2PTtulos/SpendeOutrosIndicadores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/NotasLanadasOperaoMandato/NotasLanadasMandato</v>
       </c>
       <c r="C27" t="str">
-        <v>BICSCFINANCAS - P2P Títulos</v>
+        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply; Plan1 (Operações Ativas NL)</v>
       </c>
       <c r="D27" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/694/lineage</v>
       </c>
       <c r="E27" t="str">
-        <v/>
-      </c>
-      <c r="F27" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Cod Oper; Des Especie Est; Des Oper; Plan1 (Count); Tip Oper; Tipo Oper</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>FISCAL08 - Painel Notas Incluídas vs Canceladas ou Operação ñ Realizada</v>
+        <v>SKO03 - Capacidade Produtiva</v>
       </c>
       <c r="B28" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL08-PainelNotasIncludasvsCanceladasouOperaoRealizada/Painel-NFsIncludasvsCanceladasouOperaoRealizada</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/SKO03-CapacidadeProdutiva/VisoGeral</v>
       </c>
       <c r="C28" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v>BICSCFINANCAS - Capacidade Produtiva; Execução (Consolidado FTE CSC)</v>
       </c>
       <c r="D28" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/23/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/31583/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1889/lineage</v>
       </c>
       <c r="E28" t="str">
-        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; contagem; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Campo Calculado</v>
+        <v>[fn] Data atualização; [fn] Usuario; Apoio; Capacidade Produtiva (Count); COMPROVANTE_PAGAMENTO; Dsc Domain; Dsc Domain (continuo); Dsc Hierarquia; Dsc Macroprocesso; Dsc Período; Dsc RPA; Dsc Subprocesso; DSC_COMPROVANTE_PAGAMENTO; Dt Carga; Dt Competencia; Dt Competência; Dt Competência (Max); Filtro 12 Meses; Filtro 6 Meses; Filtro Mês Atual; lbl DataHora; lbl Usuario; Nm Responsavel; Nm Responsável; Nm Source; Nr Chamado; Perc Utilização; Table Sort; Target 80%; Título Período; Vl Fte; Vl Fte Ajustado; Vl Fte Ajustado (fixed); Vl Tempo Em Andamento; Cargo; Colaborador; Competência; Domain; Email; Execução (Count); FTE Oficial Hierarquia; Hierarquia; Nome para Ivanti; Qtd. FTE Oficial; Tipo de Contrato</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>FISCAL08 - Painel Notas Incluídas vs Canceladas ou Operação ñ Realizada</v>
+        <v>Monitor de Conformidade de Pedidos</v>
       </c>
       <c r="B29" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL08-PainelNotasIncludasvsCanceladasouOperaoRealizada/Painel-NFsIncludasvsCanceladasouOperaoRealizada</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MonitordeConformidadedePedidos_17401714988840/VisoGeral</v>
       </c>
       <c r="C29" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v>Consolidado_pedidos_suspeitos</v>
       </c>
       <c r="D29" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/23/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; AnoComp; CC: Análise Suspeitos; CC: É data?; CC: É Mandato?; CC: NúmeroCL; CC: Pedidos Suspeitos; CC: Qtd Notas NOT OK; CC: Taxa Conformidade (qtd); CC: Taxa Conformidade (vl); Cliente; Consolidado_FOOD_FM (Count); Data Lançamento; Diretoria; Dt Competência; Dt Competência (Max); Eixo; Filial; Filtro 13 meses; Filtro Mês Anterior; Filtro Mês Atual; Index; MêsComp; Nota Fiscal; Número do Pedido; Rank; Segmento; Tipo Atuação; Valor</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SLA Performance Insights</v>
+        <v>IDN01 - Business Outcome Indicator (BOI)</v>
       </c>
       <c r="B30" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/SLAPerformanceInsights_17550940970210/SLAPerformanceInsights-Cancelamentos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IDN01-BusinessOutcomeIndicatorBOI/PainelDPO</v>
       </c>
       <c r="C30" t="str">
-        <v>BICSCFINANCAS - Pesquisa Satisfação; BIGOLD - Chamados Ivanti</v>
+        <v>BICSCFINANCAS - BOI Métricas; BICSCFINANCAS - P2P Títulos</v>
       </c>
       <c r="D30" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage; https://analyticsbi.sodexo.com.br/#/datasources/40609/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/31544/lineage; https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
       </c>
       <c r="E30" t="str">
-        <v>:Measure Names; Custom SQL Query (Count); Custom SQL Query1 (Count); Domain; DS_CANAL; DS_CATEGORIA_PRINCIPAL; DS_CATEGORIA_PRINCIPAL (Custom SQL Query1); DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); Dt Competência Anterior (short text) (copy); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; EMAIL; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Anterior 2; Filtro Mês Selecionado; Filtro Mês Selecionado 2; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Detrator Entrega Comparativo (copy); Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Promotor Entrega Comparativo (copy); Gauge Respondidos vs Concluídos Comparativo; Cd Chamado; Cd Uf; Dh Processamento (Evt Chamado Ivanti); Ds Canal; Ds Canal (Vw Fin F Chamado Pesquisa Ivanti Ca); Ds Categoria; Ds Comentario; Ds Detalhe Resolucao; Ds Estado; Ds Hierarquia; Ds Nivel Urgencia; Ds Origem; Ds Razao Cancelamento; Ds Razao Cancelamento Cliente; Ds Resumo; Ds Tipo Solicitacao; DS_CATEGORIA_PRINCIPAL (VW_FIN_F_CHAMADO_PESQUISA_IVANTI_CA); Dsc Canal De Atendimento; Dsc Cancelado Por; Dsc Cancelamento; Dsc Categoria; Dsc Categoria (Vw Fin F Chamado Pesquisa Ivanti Ca); Dsc Comentario Resposta; Dsc Comprovante Pagamento; Dsc Domain; Dsc Domain (Vw Fin F Chamado Pesquisa Ivanti Ca); Dsc Grupo; Dsc Macroprocesso; Dsc Pesquisa Respondida; Dsc Rsp Atendimento; Dsc Rsp Entrega; Dsc Solucao; Dsc Status; Dsc Subprocesso; Dt Abertura; Dt Abertura (Vw Fin F Chamado Pesquisa Ivanti Ca); Dt Cancelado Em; Dt Carga; Dt Carga (Evt Chamado Ivanti)</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Campo Calculado</v>
+        <v>[fn] Data atualização; [fn] Usuario; Dsc Categoria; Dsc Categoria (continuo); Dsc Metrica; Dsc Periodo; Dsc Período; Dt Carga; Dt Competencia; Filtro 12 meses; Filtro mês atual; lbl DataHora; lbl Usuario; Tp Pagamento Fornecedor; Vl Metrica; VW_F_CSC_BOI (Count); % Total VL_MONTANTE; :Measure Names; BN - % Total; BN - % Total (copy); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO; CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto) (gauge); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto,); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual) (gauge); CC: VL_QUANTIDADE (Pagamento auto,); CC: VL_QUANTIDADE (Pagamento manual); CD_CONDICOES_PGTO; Custom SQL Query (Count); DSC_AGING; DSC_AGING_FINAL; DSC_AGING_VENCIDOS; DSC_CATEGORIA; DSC_CLASSIFICACAO_CONTA; DSC_POLITICA; DSC_POLITICA (cópia); DSC_PRAZO; DSC_STATUS_TITULO; DT_ANALISE; Filtro Data Competência; Filtro Data Competência (M-1); Filtro Data Competência (M-2); Filtro nulos analise de aging; FY; Hoje(); Max Dt Analise; NM_BANCO_PAGADOR; Perc valor montante vencido; PERC_VENCIDOS; Período; QT_TITULOS_PAGOS_SEM_BONIF; QT_TITULOS_PAGOS_SEM_BONIF (Evolução); QT_TITULOS_PAGOS_SEM_BONIF (Evolução) (gauge); QT_TITULOS_PAGOS_SEM_BONIF_AJUST; QT_TITULOS_PAGOS_SEM_BONIF_AJUST (Rótulo); RANK 1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SLA Performance Insights</v>
+        <v>Condição Vencimento</v>
       </c>
       <c r="B31" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/SLAPerformanceInsights_17550940970210/SLAPerformanceInsights-Cancelamentos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimento/CondiodeVencimento</v>
       </c>
       <c r="C31" t="str">
-        <v>BICSCFINANCAS - Pesquisa Satisfação; BIGOLD - Chamados Ivanti</v>
+        <v>BIFATURAMENTO - Faturamento NL NES</v>
       </c>
       <c r="D31" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/59449/lineage; https://analyticsbi.sodexo.com.br/#/datasources/40609/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
       </c>
       <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SKO02 - Performance Operacional de Rotina e Demandas</v>
+        <v>Análise Trabalhistas P01</v>
       </c>
       <c r="B32" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PerformanceOperacionaldeRotinaeDemandas/DashboardProcessos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseTrabalhistasP01/AnliseTrabalhistas</v>
       </c>
       <c r="C32" t="str">
-        <v>Base Processos - smartsheet</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Tableau (Base Tableau P4 (2))</v>
       </c>
       <c r="D32" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2260/lineage</v>
       </c>
       <c r="E32" t="str">
-        <v>% Parâmetro; :Measure Names; 0; Ano fiscal; Base de Processos (Count); Cálculo em dias; Cálculo horas no mês; Cálculo2; Carga horária; Contagem Parâmetro; Data; Domain; Dt Competência; Dt Competência (MAX); Eixo; Esforço dedicado (Horas); Filtro 12 meses; Filtro Mês Atual; FTE; FTE Ajustado; Macroprocesso; Média FTE; Média FTE Ajustado; Parâmetro; Período; Processo; Rank; Responsável; Subprocesso; Tempo; Tempo (Horas); Tempo médio; Tipo; Volume; Volume médio; Volume mensal</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; Cenário; Centro De Custo - Br; Fase; Mudança de Fase; Obs do Fechamento; Período; Planilha1 (Count); Processo; Segmento; Semana; Valor Ajuste De Provisão (Impacto)</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SKO02 - Performance Operacional de Rotina e Demandas</v>
+        <v>Campanha de incentivo GU Q1 FY26v2</v>
       </c>
       <c r="B33" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PerformanceOperacionaldeRotinaeDemandas/DashboardProcessos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1FY26v2/CampanhadeincentivoGU</v>
       </c>
       <c r="C33" t="str">
-        <v>Base Processos - smartsheet</v>
+        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
       </c>
       <c r="D33" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2440/lineage</v>
       </c>
       <c r="E33" t="str">
-        <v/>
-      </c>
-      <c r="F33" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Vendas FY25</v>
+        <v>Rateio Custo CD Mensal Data Corte FY26</v>
       </c>
       <c r="B34" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY25V3_17485411362870/Relatriodevendas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDMensalDataCorteFY26/RateioCustoCDDiario</v>
       </c>
       <c r="C34" t="str">
-        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
+        <v>BICOMPRAS - Compras Diaria</v>
       </c>
       <c r="D34" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2119/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
       </c>
       <c r="E34" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Faturamento FY24; LY (Count); Regional; :Measure Names; Concat; Fat Real; Fat vendas; Faturamento ANUALIZADO; Faturamento ANUALIZADO META; Faturamento MF YTD; FY25 Fat OR; Fy25 Gp Or; Gp Mf Ytd; GP Real; GP Vendas Anualizado; Meta de vendas (Count); Tipo1; Vendas vs MF; Anualizado YTD; Diretoria; KPI Vendas; Meta de vendas (Meta de vendas); Meta vendas; Tipo; % GM vendas FY; CC1; City; Competitor; Contract duration in months; Data; Empresa; F25; F26; F27; Filtro tipo; Full year FC; Full year Gross Profit of new units; Full year sales of new units; FY Vendas Fat; GP FY Vendas; Mês; Motivo do Sucesso; Opening date; Period1; Planilha1 (Count); Regional1; Segment; Service; Signed date; Site; Site / Contract; Site Name; Subsegment; UF; UF, City; Cross selling; Novas vendas; Segmento; Total geral; Vendas + CS; Budget MF; Conversão; Period; Planilha2 (Count); Segmento1; Target; Taxa de conversão; % Desvio; % YTD MF; Conversão desvio; Desvio %; Desvio vendas; Fat desvio; GM % Real; GM%; GP Desvio; GP%; KPI (cópia) (cópia 2); KPI (último); KPI Budget; Período; Total (Count); Venda vs MF; Fili Cidade; Fili Codigo; Fili Nmdirecao; Fili Nmempresa; Fili Nmgrupoeconomico; Fili Nmregional; Fili Nmsegmento; Fili Nmsite; Fili Nmtipocontrato; Fili Nmtiposervico; Fili Nome; Fili Nomediretoroperacional; Fili Nomegerentearea; Fili Nomegerenteregional; Fili Tipofilial; Mês, Ano de FILI DTABERTURA; Mês, Ano de FILI DTENCERRAMENTO; Sheet 1 (Count)</v>
-      </c>
-      <c r="F34" t="str">
-        <v>Campo Calculado</v>
+        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Vendas FY25</v>
+        <v>Cálculo savings - Met 1</v>
       </c>
       <c r="B35" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY25V3_17485411362870/Relatriodevendas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Clculosavings-Met1/ADH15-Clculosavings-Met_1</v>
       </c>
       <c r="C35" t="str">
-        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
+        <v>BICompras - Compras Mensal</v>
       </c>
       <c r="D35" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2119/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
       </c>
       <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>FISCAL05 - Painel Gestão do Desconhecimento</v>
+        <v>Vendas FY26</v>
       </c>
       <c r="B36" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL05-PainelGestodoDesconhecimento/1-PainelGestodoDesconhecimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY26/RealizadoClientes</v>
       </c>
       <c r="C36" t="str">
-        <v>Varredura - XML NF Header</v>
+        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
       </c>
       <c r="D36" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2348/lineage</v>
       </c>
       <c r="E36" t="str">
-        <v>Status XML; :Measure Names; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Mascara 20 NL; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd pessoal NL; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; CNPJ Fornecedor NL; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Faturamento FY24; LY (Count); Regional; :Measure Names; Concat; Fat Real; Fat vendas; Faturamento ANUALIZADO; Faturamento ANUALIZADO META; Faturamento MF YTD; FY25 Fat OR; Fy25 Gp Or; Gp Mf Ytd; GP Real; GP Vendas Anualizado; Meta de vendas (Count); Tipo1; Vendas vs MF; Anualizado YTD; Diretoria; KPI Vendas; Meta de vendas (Meta de vendas); Meta vendas; Tipo; % GM vendas FY; CC1; City; Competitor; Contract duration in months; Data; Empresa; Filtro tipo; Full year FC; Full year Gross Profit of new units; Full year sales of new units; FY Vendas Fat; GP FY Vendas; Mês; Motivo do Sucesso; Opening date; Period1; Planilha1 (Count); Regional1; Segment; Service; Signed date; Site; Site / Contract; Site Name; Subsegment; UF; UF, City; Cross selling; Novas vendas; Segmento; Total geral; Vendas + CS; Budget MF; Conversão; Period; Planilha2 (Count); Segmento1; Target; Taxa de conversão; % Desvio; % YTD MF; Conversão desvio; Desvio %; Desvio vendas; Fat desvio; GM % Real; GM%; GP Desvio; GP%; KPI (cópia) (cópia 2); KPI (último); KPI Budget; Período; Total (Count); Venda vs MF; Fili Cidade; Fili Codigo; Fili Nmdirecao; Fili Nmempresa; Fili Nmgrupoeconomico; Fili Nmregional; Fili Nmsegmento; Fili Nmsite; Fili Nmtipocontrato; Fili Nmtiposervico; Fili Nome; Fili Nomediretoroperacional; Fili Nomegerentearea; Fili Nomegerenteregional; Fili Tipofilial; Mês, Ano de FILI DTABERTURA; Mês, Ano de FILI DTENCERRAMENTO; Sheet 1 (Count)</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FISCAL05 - Painel Gestão do Desconhecimento</v>
+        <v>Análise Prévia Consumo Média PAP - Novembro 25</v>
       </c>
       <c r="B37" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL05-PainelGestodoDesconhecimento/1-PainelGestodoDesconhecimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Novembro25/Anliseprviaconsumo</v>
       </c>
       <c r="C37" t="str">
-        <v>Varredura - XML NF Header</v>
+        <v/>
       </c>
       <c r="D37" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E37" t="str">
         <v/>
-      </c>
-      <c r="F37" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tableau Reembolsos - Owner</v>
+        <v>Labor Efficiency Junho 19</v>
       </c>
       <c r="B38" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TableauReembolsos-Owner/Reembolso</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiencyJunho19/LaborEfficiency</v>
       </c>
       <c r="C38" t="str">
-        <v>Relatório WF</v>
+        <v/>
       </c>
       <c r="D38" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2285/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E38" t="str">
-        <v>Adto; Ano Fiscal; Aprovador; Autorização; Centro de lucro; Cód. SAP; Conta Contábil; Conta do Razão; Conta do Razão (Sheet1); Data de lançamento; Descrição; Descrição Conta; Descrição da Conta; Empresa; Exceção SAP; Filtro; Filtro (grupo); Link; Mês Fiscal; Nº documento; Nome Aprovador; Nome Colaborador; Nome do usuário; Owner; Owners; Portfólio; Referência; Relatório Geral (Count); Sheet1 (Count); Teste; Texto; TicketMédio; Tipo doc; Top; Valor; Workflow</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tableau Reembolsos - Owner</v>
+        <v>Análise NR Evento</v>
       </c>
       <c r="B39" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TableauReembolsos-Owner/Reembolso</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseNREvento/AnliseNREvento</v>
       </c>
       <c r="C39" t="str">
-        <v>Relatório WF</v>
+        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
       </c>
       <c r="D39" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2285/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
       </c>
       <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Extração XML para Importação Mastersaf AM v3</v>
+        <v>Condição Vencimento por UF</v>
       </c>
       <c r="B40" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAMv3/PainelXMLMastersafAM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimentoporUF/CondiodeVencimento</v>
       </c>
       <c r="C40" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>BIFATURAMENTO - Faturamento NL NES</v>
       </c>
       <c r="D40" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
       </c>
       <c r="E40" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Extração XML para Importação Mastersaf AM v3</v>
+        <v>Quality Assurance - DANFe</v>
       </c>
       <c r="B41" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAMv3/PainelXMLMastersafAM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/QualityAssurance-DANFe_17544023211490/QualityAssurance-DANFEAnaltico</v>
       </c>
       <c r="C41" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>Notas Fora vs. BISILVER | Projeto : INV estratégicos</v>
       </c>
       <c r="D41" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/58204/lineage</v>
       </c>
       <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>CNPJ Fornecedor; Dados Adicionais NF; Data da Carga; Diferença dias; Dt Emissao; Dt Fechamento; Dt Recebimento; É linha duplicada?; Emissão NF; File Paths; Fornecedor; GO; Justificativa; Log; NF Chave NFE (BISILVER); NF Chave NFE (NotaFora); Nº NF; Nome Diretor; Nome Diretoria; ORIGEM DA IDENTIFICAÇÃO; Portfólio; Previsão de Encerramento; Retorno; Segmento; Série; Table Names; UF; UF do CL; Unidade; Valor NF</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ADH10 - Base PVMv2</v>
+        <v>Evolução dos processos de reajuste FY25</v>
       </c>
       <c r="B42" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH10-BasePVMv2/ADH10-BasePVMv2</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Evoluodoprocessodereajuste/Reajuste-Evoluoprocessos</v>
       </c>
       <c r="C42" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v>Sheet 1 (REAJUSTE 2)</v>
       </c>
       <c r="D42" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1974/lineage</v>
       </c>
       <c r="E42" t="str">
-        <v/>
-      </c>
-      <c r="F42" t="str">
-        <v>Campo Calculado</v>
+        <v>% Calculado; % Concedido; :Measure Names; Centro de lucro; Cliente; Direção1; Fat. média 3 meses da data fim; Fator; Mês, Ano de Data Base1; Mês, Ano de Data fim processo; Mês, Ano de Data inicio do processo; Mês, Dia, Ano de Data reajuste retroativo mes; Nome; Período1; Processo; Reajuste calculado mês; Reajuste calculado YTD; Reajuste concedido mês; Reajuste concedido YTD; Regional; Segmento1; Serviço; Sheet 1 (Count); Situação do processo1; Tipo reajuste1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ADH10 - Base PVMv2</v>
+        <v>Organic Growth - FY26</v>
       </c>
       <c r="B43" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH10-BasePVMv2/ADH10-BasePVMv2</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY26/OGDiretoria</v>
       </c>
       <c r="C43" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa; Clipboard_20251219T110253</v>
       </c>
       <c r="D43" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2430/lineage</v>
       </c>
       <c r="E43" t="str">
-        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
-      </c>
-      <c r="F43" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; Clipboard_20251219T110253 (Count); Fili Nmgrupoeconomico; FILI NMSEGMENTO (grupo); Nomes de medida; OG Real; Valores de medida</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Análise Prévia Consumo Outubro 2025</v>
+        <v>FISCAL06 - Painel Check CNPJ</v>
       </c>
       <c r="B44" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoOutubro2025/AnlisePrviadoConsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL06-PainelCheckCNPJ/CheckCNPJ-XmlvsNL</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
       </c>
       <c r="D44" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/11/lineage</v>
       </c>
       <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; Xml UF Fornecedor; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; CNPJ Xml vs Nota; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Análise Prévia Consumo Outubro 2025</v>
+        <v>FISCAL11 - Status Serviço por CNPJ</v>
       </c>
       <c r="B45" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoOutubro2025/AnlisePrviadoConsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL11-StatusServioporCNPJ/PainelStatusServioporCNPJ</v>
       </c>
       <c r="C45" t="str">
-        <v/>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); VW_D_FILIAL_NL (BIVARREDURA)</v>
       </c>
       <c r="D45" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/9/lineage</v>
       </c>
       <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Empresa; Cd Filial; CD Ind Inativo; CNPJ RAIZ; Cnpj Unidade Nl; Cód Pessoa Nl; Cód Unidade Nl; Empresa; IE; Ind Senha Unidade; Qtd Cnpj; Sk Filial; Status CNPJ; Status Servico CNPJ; Status Unidade Nl; UF; Unidade Nl</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ADH07 - CD-PAP</v>
+        <v>Painel Inadimplência e PDD</v>
       </c>
       <c r="B46" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH07-CD-PAP/ADH7-CD-PAP</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelInadimplnciaePDD/RelatrioInadimplnciaePDDs-VisoSegmento</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>Base de Títulos</v>
       </c>
       <c r="D46" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v>Campo Calculado</v>
+        <v>% PDD sobre Carteira; Atraso após vencimento líquido; Atribuição; Base de Títulos (Count); BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento 1; Business Unit; Central de Compras; Centro de lucro; Centro de lucro (Sheet1); Chave referência 3; Cidade (End.Entrega); CNPJ Centralizador; Cód.Razão Especial; Condições pagamento; Conta; Data abertura revisada; Data Corte Inadimplência; Data de compensação; Data do documento; Diretoria; Dt Competência; Dt Competência (Max); Dt Vencimento; Empresa; Empresa (Sheet1); Estado (End.Entrega); Filial Teknisa; Filtro 13 meses; Filtro 18 meses; Filtro 3 meses; Filtro 6 meses; Filtro de Vencimento Válido; Filtro Gráfico</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ADH07 - CD-PAP</v>
+        <v>CR07 - Análise de Venda à Vista</v>
       </c>
       <c r="B47" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH07-CD-PAP/ADH7-CD-PAP</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CR07-AnlisedeVendaVista/AnlisedeVendaVista</v>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>Análise Venda à Vista</v>
       </c>
       <c r="D47" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/520/lineage</v>
       </c>
       <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Crescimento Mês; % Crescimento Mês (cópia); % do Total; :Measure Names; Ano Fiscal; Campo Base; CD_BUSINESS_UNIT; CD_CARDAPIO; CD_CENTRO_CUSTO; CD_CLIENTE_NL; CD_DIRETORIA; CD_EMPRESA_SODEXO; CD_FILIAL_FICTICIA; CD_FILIAL_NL; CD_GRUPOECONOMICO; CD_MATRICULA_DIRETOR_OPERAC; CD_MATRICULA_GERENTE_AREA; CD_MATRICULA_GERENTE_REGIONAL; CD_MATRIZ; CD_ORIGEM; CD_REGIONAL; CD_SEGMENTO; CD_TIPO_ATUACAO; CD_TIPO_CONTRATO; CD_TIPO_SERVICO; CD_UF; Cliente; Cliente CNPJ CPF; Cód Filial; Consulta do SQL personalizado (Count); Conta; Data Faturamento; Data Referência; Diretoria; DSC_ORIGEM; DT_ABERTURA; DT_ARQUIVO; DT_CARGA; DT_ENCERRAMENTO; Filial</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Performance_Retails consolidado</v>
+        <v>Análise Prévia Consumo Novembro 2025</v>
       </c>
       <c r="B48" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retailsconsolidado/PerformanceRetail</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoNovembro2025/AnlisePrviadoConsumo</v>
       </c>
       <c r="C48" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v/>
       </c>
       <c r="D48" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E48" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Performance_Retails consolidado</v>
+        <v>FI01 - Mapa Fiscal - Extração - V12</v>
       </c>
       <c r="B49" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retailsconsolidado/PerformanceRetail</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V11/Painel-MapaFiscalporUF</v>
       </c>
       <c r="C49" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
       </c>
       <c r="D49" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2059/lineage</v>
       </c>
       <c r="E49" t="str">
-        <v/>
-      </c>
-      <c r="F49" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Aliquotadifal; Aliquotadiferenca; Aliquotainterna; Aliquotaorigem; Basedecalculo; Cd Filial; Cnpjremetente; Dados migrados (Count); Dtcompetencia; Dtlancamento; Ieremetente; Impostocreditado; Isentas; Nronf; Number of Records; Outras; Percaliqinterestadual; Percaliqinterna; Percdiferencialaliquota; Serie; Sk Aliquotauf Od; Sk Aliquotauf Od (D Aliquotauf Od); Sk Filial; Uf Destino; Uf Origem; Uf Origemdestino; Uffilial; Ufremetente; Valorcontabil; Valordiferencialaliquota; VL Difal; Vlraliqinterest; Vlraliqinterna; Cargauf; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial (Vw D Filial); Cd Filial Ficticia; Cd Lancamento; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Uf (Vw D Filial); Cfop; Cnpjdestinatario; Conta Contabil; Creditoentradas; Dt Abertura; Dt Ano Mes; Dt Carga; Dt Carga (Vw D Tempo); Dt Encerramento; Dtcompetencia filtra ate jan21; Filial; FILIAL UF; Centrodelucro; Competencia; SK_FILIAL; VALOR_CALCULO; VL Outros Créditos; VL OutrosCreditos Calculo; Cd Contacontabil; Chavelancamento; Conta Contabil (grupo); Contacontabil; Dt Carga (Vw D Filial); Estornocom; Fl Ficticia; Hierarquia; Inscricaoestadual; Locnegocios; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Contacontabil; Nm Diretor Operacional; Nm Diretoria</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Painel de Monitoramento de NFs x Ordens de compra</v>
+        <v>DE01 - Demográfico</v>
       </c>
       <c r="B50" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeMonitoramentodeNFsxOrdensdecompra_17308902149110/VisoGeralNFs</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/DE01-Demogrfico/Demogrfico</v>
       </c>
       <c r="C50" t="str">
-        <v>BICOMPRAS - NL Recebimento Ordem Compras; BISILVER - Finance - Nota Fiscal Recebimento</v>
+        <v>BICSCFINANCAS - Quantitativo Colaboradores</v>
       </c>
       <c r="D50" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/26392/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/31663/lineage</v>
       </c>
       <c r="E50" t="str">
-        <v>Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_USUARIO; Dt Abertura; Dt Carga; Dt Encerramento; filtraExtração; Fl Familia Gerenciada; Fl Familia Integrante Cesta; Fl Ficticia; Fl Homologado; Fl Item Compra; Fl Obsoleto; Multiple Values; Cd Business Unit; Cd Centro Lucro; Cd Grupoeconomico; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Site; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Carga (Vw Mdt Centro Lucro)</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Campo Calculado</v>
+        <v>*%HE; *Aculmulado Admissão+Desligamento / 2; *CC Colaboradores Admissão; *CC Colaboradores Desligamento; *CC Perc Turn Over; *Dif Horas Meses e Extras; *Periodo Ajustado; *Periodo Ajustado (texto); :Measure Names; [fn] Data atualização; [fn] Usuario; { FIXED [Ano Competencia]:sum(IIF([Fleg Rescisao]='S',[Qtd Co...; 1; 1 (1); Ano Mes Competencia; Cálculo1; Cálculo2; CC Colaboradores ativos; CC Filtro Ano; CC Filtro Mes; CC FTE budget; CC Perc Attr; CC Qt Attrition; CC Qt Recisao; Cd Filial; Domain; DSC_ATTRITION_RATE; Dt Competencia; Dt Competência (Max); F_SSC_QUANTITATIVO_COLABORADOR (Count); Faixa Idade; Filtro 12 Meses; Filtro 3 Meses; Filtro Ano Atual; Filtro Mês Abaixo; Filtro Mês Atual; Fleg Ativo; Fleg Gestor; Fleg Rescisao; FLEG_ADMISSAO</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Painel de Monitoramento de NFs x Ordens de compra</v>
+        <v>Painel Controller RYDOO</v>
       </c>
       <c r="B51" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeMonitoramentodeNFsxOrdensdecompra_17308902149110/VisoGeralNFs</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelControllerRYDOO/PainelController</v>
       </c>
       <c r="C51" t="str">
-        <v>BICOMPRAS - NL Recebimento Ordem Compras; BISILVER - Finance - Nota Fiscal Recebimento</v>
+        <v>Base (Controller Táxi Rydoo - FY26)</v>
       </c>
       <c r="D51" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/26392/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2432/lineage</v>
       </c>
       <c r="E51" t="str">
-        <v/>
-      </c>
-      <c r="F51" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Aprovada por; Base (Count); Cadastrado; Cálculo1; Categorizado Rejeição; Controller; Data de aprovação; Email; Mês Controle; Reemboolsado; Top; Usuário; Valor; Xpd Reference</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Notas Lançadas Operação Mandato</v>
+        <v>Análise de resultado - Mapa</v>
       </c>
       <c r="B52" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasLanadasOperaoMandato/NotasLanadasMandato</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapa/Anlisedefaturamento-mapa</v>
       </c>
       <c r="C52" t="str">
-        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply; Plan1 (Operações Ativas NL)</v>
+        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
       </c>
       <c r="D52" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/694/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E52" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Cod Oper; Des Especie Est; Des Oper; Plan1 (Count); Tip Oper; Tipo Oper</v>
-      </c>
-      <c r="F52" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Notas Lançadas Operação Mandato</v>
+        <v>Resultado financeiro - Fat e GP Ano Fiscal</v>
       </c>
       <c r="B53" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasLanadasOperaoMandato/NotasLanadasMandato</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscal/FateGPSAP-Anofiscal</v>
       </c>
       <c r="C53" t="str">
-        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply; Plan1 (Operações Ativas NL)</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D53" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/694/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2050/lineage</v>
       </c>
       <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SKO03 - Capacidade Produtiva</v>
+        <v>Base ordem de compras completa</v>
       </c>
       <c r="B54" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/SKO03-CapacidadeProdutiva/VisoGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecomprascompleta/Baseordemdecompras</v>
       </c>
       <c r="C54" t="str">
-        <v>BICSCFINANCAS - Capacidade Produtiva; Execução (Consolidado FTE CSC)</v>
+        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
       </c>
       <c r="D54" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31583/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1889/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
       </c>
       <c r="E54" t="str">
-        <v>[fn] Data atualização; [fn] Usuario; Apoio; Capacidade Produtiva (Count); COMPROVANTE_PAGAMENTO; Dsc Domain; Dsc Domain (continuo); Dsc Hierarquia; Dsc Macroprocesso; Dsc Período; Dsc RPA; Dsc Subprocesso; DSC_COMPROVANTE_PAGAMENTO; Dt Carga; Dt Competencia; Dt Competência; Dt Competência (Max); Filtro 12 Meses; Filtro 6 Meses; Filtro Mês Atual; lbl DataHora; lbl Usuario; Nm Responsavel; Nm Responsável; Nm Source; Nr Chamado; Perc Utilização; Table Sort; Target 80%; Título Período; Vl Fte; Vl Fte Ajustado; Vl Fte Ajustado (fixed); Vl Tempo Em Andamento; Cargo; Colaborador; Competência; Domain; Email; Execução (Count); FTE Oficial Hierarquia; Hierarquia; Nome para Ivanti; Qtd. FTE Oficial; Tipo de Contrato</v>
-      </c>
-      <c r="F54" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SKO03 - Capacidade Produtiva</v>
+        <v>Análise PROVISÃO NF2</v>
       </c>
       <c r="B55" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/SKO03-CapacidadeProdutiva/VisoGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF2/Planilha24</v>
       </c>
       <c r="C55" t="str">
-        <v>BICSCFINANCAS - Capacidade Produtiva; Execução (Consolidado FTE CSC)</v>
+        <v/>
       </c>
       <c r="D55" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31583/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1889/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E55" t="str">
         <v/>
-      </c>
-      <c r="F55" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Monitor de Conformidade de Pedidos</v>
+        <v>Análise de resultado - Mapa Cidade</v>
       </c>
       <c r="B56" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MonitordeConformidadedePedidos_17401714988840/VisoGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaCidade/Anlisedefaturamento-mapa</v>
       </c>
       <c r="C56" t="str">
-        <v>Consolidado_pedidos_suspeitos</v>
+        <v/>
       </c>
       <c r="D56" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E56" t="str">
-        <v>:Measure Names; AnoComp; CC: Análise Suspeitos; CC: É data?; CC: É Mandato?; CC: NúmeroCL; CC: Pedidos Suspeitos; CC: Qtd Notas NOT OK; CC: Taxa Conformidade (qtd); CC: Taxa Conformidade (vl); Cliente; Consolidado_FOOD_FM (Count); Data Lançamento; Diretoria; Dt Competência; Dt Competência (Max); Eixo; Filial; Filtro 13 meses; Filtro Mês Anterior; Filtro Mês Atual; Index; MêsComp; Nota Fiscal; Número do Pedido; Rank; Segmento; Tipo Atuação; Valor</v>
-      </c>
-      <c r="F56" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Monitor de Conformidade de Pedidos</v>
+        <v>PIS/COFINS sobre NF</v>
       </c>
       <c r="B57" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MonitordeConformidadedePedidos_17401714988840/VisoGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PISCOFINSsobreNF/PISCOFINSsobreNF</v>
       </c>
       <c r="C57" t="str">
-        <v>Consolidado_pedidos_suspeitos</v>
+        <v>Centro_Lucro; União de linhas (Razão consumo)</v>
       </c>
       <c r="D57" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2171/lineage</v>
       </c>
       <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; % COFINS S/NF; % Gasto com CD; % ICMS S/NF; % Logistica; % PIS S/NF; % PIS/COFINS CD; % Total PIS/COFINS; :Measure Names; Cálculo1; Cálculo2; Cen.lucro; COFINS SOBRE NF; Conta; Conta (cópia); D; DATA; Data doc/; Data lçto/; Denominação; Doc.compra; em MdICenL; Empr; Fornec.; Fornec. (grupo); Fornec. (grupo) 1; Fornecedor 2; Gastos com CD; ICMS SOBRE NF; Logistica Alimentar; NF; Nº conta; Nº doc.; Nºdoc.ref.; Others; Outros; Período; PIS SOBRE NF; PIS/COFINS CD; Sheet; Table Name</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>IDN01 - Business Outcome Indicator (BOI)</v>
+        <v>Resultado financeiro - Desvio consumo</v>
       </c>
       <c r="B58" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IDN01-BusinessOutcomeIndicatorBOI/PainelDPO</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Desvioconsumo/Desvioconsumo</v>
       </c>
       <c r="C58" t="str">
-        <v>BICSCFINANCAS - BOI Métricas; BICSCFINANCAS - P2P Títulos</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D58" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31544/lineage; https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2055/lineage</v>
       </c>
       <c r="E58" t="str">
-        <v>[fn] Data atualização; [fn] Usuario; Dsc Categoria; Dsc Categoria (continuo); Dsc Metrica; Dsc Periodo; Dsc Período; Dt Carga; Dt Competencia; Filtro 12 meses; Filtro mês atual; lbl DataHora; lbl Usuario; Tp Pagamento Fornecedor; Vl Metrica; VW_F_CSC_BOI (Count); % Total VL_MONTANTE; :Measure Names; BN - % Total; BN - % Total (copy); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO; CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto) (gauge); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento auto,); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual); CC: VL_MONTANTE_MOEDA_INTERNA_AJUSTADO (Pagamento manual) (gauge); CC: VL_QUANTIDADE (Pagamento auto,); CC: VL_QUANTIDADE (Pagamento manual); CD_CONDICOES_PGTO; Custom SQL Query (Count); DSC_AGING; DSC_AGING_FINAL; DSC_AGING_VENCIDOS; DSC_CATEGORIA; DSC_CLASSIFICACAO_CONTA; DSC_POLITICA; DSC_POLITICA (cópia); DSC_PRAZO; DSC_STATUS_TITULO; DT_ANALISE; Filtro Data Competência; Filtro Data Competência (M-1); Filtro Data Competência (M-2); Filtro nulos analise de aging; FY; Hoje(); Max Dt Analise; NM_BANCO_PAGADOR; Perc valor montante vencido; PERC_VENCIDOS; Período; QT_TITULOS_PAGOS_SEM_BONIF; QT_TITULOS_PAGOS_SEM_BONIF (Evolução); QT_TITULOS_PAGOS_SEM_BONIF (Evolução) (gauge); QT_TITULOS_PAGOS_SEM_BONIF_AJUST; QT_TITULOS_PAGOS_SEM_BONIF_AJUST (Rótulo); RANK 1</v>
-      </c>
-      <c r="F58" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>IDN01 - Business Outcome Indicator (BOI)</v>
+        <v>Indicadores Fiscais</v>
       </c>
       <c r="B59" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IDN01-BusinessOutcomeIndicatorBOI/PainelDPO</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadorescontasdeimpostos/5-BaseporCL</v>
       </c>
       <c r="C59" t="str">
-        <v>BICSCFINANCAS - BOI Métricas; BICSCFINANCAS - P2P Títulos</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; 07.05 BASE ABRIL (07.05 BASE ABRIL.xls)</v>
       </c>
       <c r="D59" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31544/lineage; https://analyticsbi.sodexo.com.br/#/datasources/31690/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1871/lineage</v>
       </c>
       <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Crédito PIS Cofins; 07.05 BASE ABRIL (Count); Cen.lucro; Cliente; D; Data doc.; Data lçto.; Denominação; Doc.compra; Doc.venda; em MdICenL; Empr; Fornec.; Nº conta; Nº doc.; Nºdoc.ref.; Período; Texto; Tip Ft; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Condição Vencimento</v>
+        <v>Rateio Custo CD Consolidador Data Corte FY26</v>
       </c>
       <c r="B60" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimento/CondiodeVencimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDConsolidadorDataCorteFY26/RateioCustoCDConsolidadorDiario</v>
       </c>
       <c r="C60" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES</v>
+        <v>BICOMPRAS - Compras Diaria</v>
       </c>
       <c r="D60" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
       </c>
       <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v>Campo Calculado</v>
+        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Condição Vencimento</v>
+        <v>Performance_Retails</v>
       </c>
       <c r="B61" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimento/CondiodeVencimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retails/PerformanceRetail_1</v>
       </c>
       <c r="C61" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES</v>
+        <v>Centro_Lucro; Contabil</v>
       </c>
       <c r="D61" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
       </c>
       <c r="E61" t="str">
-        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato</v>
-      </c>
-      <c r="F61" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Análise Trabalhistas P01</v>
+        <v>Projeção de Inflação - Global por Nota Fiscal MoM</v>
       </c>
       <c r="B62" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseTrabalhistasP01/AnliseTrabalhistas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ProjeodeInflao-GlobalporNotaFiscalMoM/1-InflaoGlobalGeral</v>
       </c>
       <c r="C62" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Tableau (Base Tableau P4 (2))</v>
+        <v>Projeção</v>
       </c>
       <c r="D62" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2260/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/587/lineage</v>
       </c>
       <c r="E62" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; Cenário; Centro De Custo - Br; Fase; Mudança de Fase; Obs do Fechamento; Período; Planilha1 (Count); Processo; Segmento; Semana; Valor Ajuste De Provisão (Impacto)</v>
-      </c>
-      <c r="F62" t="str">
-        <v>Campo Calculado</v>
+        <v>% a ser considerado na var; % a ser considerado na var (PAP); % a ser considerado na var (TRA); % Considerado no calculo; % Estq 3 meses (TRA); % Inflação (Proj. M2); % Inflação (Proj. M2) (PAP); % Inflação (Proj. M2) (Segmento); % Inflação (Proj. M2) (Segmento) (PAP); % Inflação (Proj. M2) (Segmento) (TRA); % Inflação (Proj. M2) (TRA); % Inflação (Proj. M3); % Inflação (Proj. M3) (PAP); % Inflação (Proj. M3) (Segmento); % Inflação (Proj. M3) (Segmento) (PAP); % Inflação (Proj. M3) (Segmento) (TRA); % Inflação (Proj. M3) (TRA); % Inflação (Proj. M4) (PAP); % Inflação (Proj. M4) (Segmento); % Inflação (Proj. M4) (Segmento) (PAP); % Inflação (Proj. M4) (Segmento) (TRA); % Inflação (Proj. M4) (TRA); % Inflação (Proj.); % Inflação (Proj.) (Media consumo 3 meses)); % Inflação (Proj.) (PAP); % Inflação (Proj.) (Regra Estoque); % Inflação (Proj.) (Segmento); % Inflação (Proj.) (Segmento) (PAP); % Inflação (Proj.) (Segmento) (TRA); % Inflação (Proj.) (TRA); % Rank; % Repres. Bonif. Pedidos em aberto CD; % Repres. Bonificação Base Line; % Repres. Qtd Necessid. Consum. (TRA); % Variação de mercado M1 (TRA); % Variação de mercado M2; % Variação de mercado M2 (PAP); % Variação de mercado M2 (TRA); % Variação de mercado M3; % Variação de mercado M3 (PAP)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Análise Trabalhistas P01</v>
+        <v>Painel de Exclusão do ICMS de PIS_COFINS nas Entradas</v>
       </c>
       <c r="B63" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseTrabalhistasP01/AnliseTrabalhistas</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeExclusodoICMSdePIS_COFINSnasEntradas/PainelPISCOFINS</v>
       </c>
       <c r="C63" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Tableau (Base Tableau P4 (2))</v>
+        <v>BIVarredura - XML NF Item; Entradas SAP 05_2023 Sodexo</v>
       </c>
       <c r="D63" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2260/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1061/lineage</v>
       </c>
       <c r="E63" t="str">
-        <v/>
-      </c>
-      <c r="F63" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Base Cálc SEM ICMS; Base Cálculo PIS; Central de Compras; Centro de lucro1; Cidade (Todos excetuado Branch); Cnpj / Cpf; Data Lançamento; Débito de COFINS; Débito PIS; Descrição; Doc.Contáb; Empresa; Entradas SAP.csv (Count); Filial; Filial Teknisa; ID Tipo contrato; index; Modelo; Nome diretoria; Nome do Diretor; Nome do Gerente Area; Nome do Gerente Regional; Nome do Grupo Economico; Nome do Site; Nome Filial; Nota Fiscal; Nota+CNPJ; Número Documento; Opening date; Path; PIS&amp;COFINS; Razão Social; Região (Todos excetuado Branch); Regime Apuração; Regional; Segmento1; Série; Subsegment; Subserviço descrição</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Campanha de incentivo GU Q1 FY26v2</v>
+        <v>Cálculo ICMS ST a Recolher MG</v>
       </c>
       <c r="B64" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1FY26v2/CampanhadeincentivoGU</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ClculoICMSSTaRecolherMG/ICMSST</v>
       </c>
       <c r="C64" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
+        <v>BIVarredura - XML NF Item; Tabela NCM ST</v>
       </c>
       <c r="D64" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2440/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/406/lineage</v>
       </c>
       <c r="E64" t="str">
-        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
-      </c>
-      <c r="F64" t="str">
-        <v>Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Descrição; MVA; MVA Ajust; MVA Ajustado; MVA Calculo; NCM; NCM ST; Ncm Tabela; Tabela NCM ST.csv (Count)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Campanha de incentivo GU Q1 FY26v2</v>
+        <v>Custo Target</v>
       </c>
       <c r="B65" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1FY26v2/CampanhadeincentivoGU</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Target_17115510333040/Custotarget</v>
       </c>
       <c r="C65" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
+        <v>BICOMPRAS - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO - Faturamento NL NES Item (cópia); Contabil_Conta (cópia); Sheet 1 (Concatenar)</v>
       </c>
       <c r="D65" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2440/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/36425/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1277/lineage</v>
       </c>
       <c r="E65" t="str">
-        <v/>
-      </c>
-      <c r="F65" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Compliance; % Lançamento Mês; Agrupamento; Cd Cliente NL; Cd Cliente Sap; Cd Filial; Cd Filial Nl; Cd Item Cardapio; Cd Item Venda; Cd Matriz; Cd Seq Periodo; Cd Status Contrato; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Nes; CD_LISTA_PRECO_VENDA; CD_TIP_PERIODO; Cnpj Cliente; Cód Agrupamento; Cód CPR; Código Item Cardápio; Código Item Venda; Cpf Cliente; CPR; CTL_DT_ENCERRAMENTO_TERMO; Dados migrados (Count); Des Status Contrato; Des Tipo Cliente; Dia Fat; Dia Fim Fat; Dia Inicio Fat; DIA_LIMITE_FAT; DIA_VCTO10; DIA_VCTO3; DIA_VCTO4; DIA_VCTO5; DIA_VCTO6; DIA_VCTO7; DIA_VCTO8; DIA_VCTO9; :Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Sistema Origem; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_MASCARA_NL_175; CD_SITE; Cód Completo NL 175; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; Cardapio; Classificação Cardápio; Concatenar; Custo Planejado; Filial1; Item Venda; Sheet 1 (Count)</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Rateio Custo CD Mensal Data Corte FY26</v>
+        <v>Análise Prévia Consumo Média PAP - Outubro 25</v>
       </c>
       <c r="B66" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDMensalDataCorteFY26/RateioCustoCDDiario</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Outubro25/Anliseprviaconsumo</v>
       </c>
       <c r="C66" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v/>
       </c>
       <c r="D66" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E66" t="str">
         <v/>
-      </c>
-      <c r="F66" t="str">
-        <v>Campo Calculado</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Rateio Custo CD Mensal Data Corte FY26</v>
+        <v>VD51</v>
       </c>
       <c r="B67" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDMensalDataCorteFY26/RateioCustoCDDiario</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/VD51/VD51</v>
       </c>
       <c r="C67" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v>BIFATURAMENTO - Cadastro Contrato NL; Saidas por Itens; Sheet1 (CEST)</v>
       </c>
       <c r="D67" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/workbooks/509/lineage</v>
       </c>
       <c r="E67" t="str">
-        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
-      </c>
-      <c r="F67" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento; Aliquota ICMS; Base FCP; Base ICMS; Base IPI; CD FILIAL SAP; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CNPJ; CNPJ Destinatário; Cst Icms; Data Lançamento1; Descrição do material1; Despesa; Estrutura SAIDAS POR ITENS.csv (Count); F20; FCP aliq; Filial; Filtra CFOP; Index; IPI aliq; Item Texto; NCM1; NF1; Nº do material1; Nº documento; Nº item do documento; Número Pedido Item; Path; Quantidade; Série1; Tipo NF; UF Destinatário; UF1; Valor Diferencial Aliquota; Valor do Item; Valor do Item 1; Valor FCP; Valor ICMS; CEST; Código de controle; Data início; Material; Sheet1 (Count)</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Cálculo savings - Met 1</v>
+        <v>Catálogo de Painéis e Indicadores</v>
       </c>
       <c r="B68" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Clculosavings-Met1/ADH15-Clculosavings-Met_1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CatlogodePainiseIndicadores/CatlogodePainis-GestoePerformance</v>
       </c>
       <c r="C68" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v/>
       </c>
       <c r="D68" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
       </c>
       <c r="E68" t="str">
         <v/>
-      </c>
-      <c r="F68" t="str">
-        <v>Campo Calculado</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Cálculo savings - Met 1</v>
+        <v>ADH18 - Item receita</v>
       </c>
       <c r="B69" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Clculosavings-Met1/ADH15-Clculosavings-Met_1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ADH18-Itemreceita/ITEMRECEITA</v>
       </c>
       <c r="C69" t="str">
         <v>BICompras - Compras Mensal</v>
@@ -35507,5293 +35303,1676 @@
       <c r="E69" t="str">
         <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
-      <c r="F69" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Vendas FY26</v>
+        <v>Faturamento com PO</v>
       </c>
       <c r="B70" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY26/RealizadoClientes</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FaturamentocomPO/FaturamentoFood</v>
       </c>
       <c r="C70" t="str">
-        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
+        <v>BIFATURAMENTO - Faturamento NL NES; BIFATURAMENTO - Faturamento NL NES Item; Sheet1 (FM); Sheet1 (SAP Pedido)</v>
       </c>
       <c r="D70" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2348/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/701/lineage</v>
       </c>
       <c r="E70" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Faturamento FY24; LY (Count); Regional; :Measure Names; Concat; Fat Real; Fat vendas; Faturamento ANUALIZADO; Faturamento ANUALIZADO META; Faturamento MF YTD; FY25 Fat OR; Fy25 Gp Or; Gp Mf Ytd; GP Real; GP Vendas Anualizado; Meta de vendas (Count); Tipo1; Vendas vs MF; Anualizado YTD; Diretoria; KPI Vendas; Meta de vendas (Meta de vendas); Meta vendas; Tipo; % GM vendas FY; CC1; City; Competitor; Contract duration in months; Data; Empresa; Filtro tipo; Full year FC; Full year Gross Profit of new units; Full year sales of new units; FY Vendas Fat; GP FY Vendas; Mês; Motivo do Sucesso; Opening date; Period1; Planilha1 (Count); Regional1; Segment; Service; Signed date; Site; Site / Contract; Site Name; Subsegment; UF; UF, City; Cross selling; Novas vendas; Segmento; Total geral; Vendas + CS; Budget MF; Conversão; Period; Planilha2 (Count); Segmento1; Target; Taxa de conversão; % Desvio; % YTD MF; Conversão desvio; Desvio %; Desvio vendas; Fat desvio; GM % Real; GM%; GP Desvio; GP%; KPI (cópia) (cópia 2); KPI (último); KPI Budget; Período; Total (Count); Venda vs MF; Fili Cidade; Fili Codigo; Fili Nmdirecao; Fili Nmempresa; Fili Nmgrupoeconomico; Fili Nmregional; Fili Nmsegmento; Fili Nmsite; Fili Nmtipocontrato; Fili Nmtiposervico; Fili Nome; Fili Nomediretoroperacional; Fili Nomegerentearea; Fili Nomegerenteregional; Fili Tipofilial; Mês, Ano de FILI DTABERTURA; Mês, Ano de FILI DTENCERRAMENTO; Sheet 1 (Count)</v>
-      </c>
-      <c r="F70" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato; :Measure Names; Cd Business Unit; Cd Familia Venda; Cd Produto Venda; Cd Seq Periodo; Cd Sistema Origem; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Unidade Medida; CD_MASCARA_NL_175; Cód Completo NL 175; 0; Aliq COFINS; Aliq INSS; Aliq INSS (Sheet1); Aliq IRF; Aliq IRF (Sheet1); Aliq ISS; Aliq ISS (Sheet1); Aliq PIS; Aliq PIS (Sheet1); AlIq. CSLL; AlIq. CSLL (Sheet1); AliqCOFINS (Sheet1); Centro de Custo; Centro de Custo (Sheet1); Cliente Sap; CNPJ Cli; CNPJ Cli (Sheet1); CNPJ Emit.; CNPJ Emit. (Sheet1); Cnpj Fil.; CNPJ FIL. (Sheet1); Cod. Cliente (Sheet1); Código Material; Código Material (Sheet1); COFINS Ret; COFINS Ret (Sheet1); CSLL Ret; CSLL Ret (Sheet1); Data Comp; Data Comp (Sheet1); Data Lançamento; Data Lançamento (Sheet1); Descrição Material; Descrição Material (Sheet1); Descrição NCM; Descrição NCM (Sheet1); Doc Contábil; Doc Contábil (Sheet1); Doc.Comp.; 13695.2; 39197; 456.505,74; Aliquota ICMS; Base de Cálculo; Base FCP; Base ICMS; Base IPI; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CL1; CNPJ Destinatário; Cst Icms; Descrição do material; Despesa; FCP aliq; Filial; Filial Destinatário; IE Destinatário; Imposto Debitado; IPI aliq; Isentas; Item Texto; NCM; NF; Nº do material; Nº documento; Nº item do documento; Nome Destinatário; Número do Pedido; Outras; Path; Quantidade; Right; Série; Sheet</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Vendas FY26</v>
+        <v>Resultado financeiro</v>
       </c>
       <c r="B71" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VendasFY26/RealizadoClientes</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro/10-UOPMetaFixa</v>
       </c>
       <c r="C71" t="str">
-        <v>Centro_Lucro; Contabil; LY (Budget anualizado vendas); Meta de vendas (Budget anualizado vendas); Meta de vendas (Novas vendas Tableau); Planilha1 (Novas vendas Tableau); Planilha1 (Tableau meta segmento); Planilha2 (Meta mensal); Planilha6 (Budget anualizado vendas); Sheet 1 (Cadastro FY25)</v>
+        <v>Centro_Lucro; Contabil; Contabil_MetaFixa (2)</v>
       </c>
       <c r="D71" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2348/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2397/lineage</v>
       </c>
       <c r="E71" t="str">
-        <v/>
-      </c>
-      <c r="F71" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Análise Prévia Consumo Média PAP - Novembro 25</v>
+        <v>Análise de resultado por Estado</v>
       </c>
       <c r="B72" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Novembro25/Anliseprviaconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisederesultadoRS/AnlisedeResultadoporEstado</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>Centro_Lucro; Contabil</v>
       </c>
       <c r="D72" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
       </c>
       <c r="E72" t="str">
-        <v/>
-      </c>
-      <c r="F72" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Análise Prévia Consumo Média PAP - Novembro 25</v>
+        <v>Análise de resultado - Mapa gestor</v>
       </c>
       <c r="B73" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Novembro25/Anliseprviaconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapagestor/Anlisedefaturamento-mapa</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
       </c>
       <c r="D73" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E73" t="str">
-        <v/>
-      </c>
-      <c r="F73" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Labor Efficiency Junho 19</v>
+        <v>Relatorio de Quantidade</v>
       </c>
       <c r="B74" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiencyJunho19/LaborEfficiency</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade/AnliseQuantidade</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
       </c>
       <c r="D74" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
       </c>
       <c r="E74" t="str">
-        <v/>
-      </c>
-      <c r="F74" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Labor Efficiency Junho 19</v>
+        <v>Retenção FY26</v>
       </c>
       <c r="B75" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiencyJunho19/LaborEfficiency</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY26/KPIRetenoClientes</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
       </c>
       <c r="D75" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2349/lineage</v>
       </c>
       <c r="E75" t="str">
-        <v/>
-      </c>
-      <c r="F75" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Diretoria; F6; FAT Dir LY; FY24 (Count); GP Dir LY; Regional; Segmento; % Retenção FY24; % total target; Data; Desvio; MF; Planilha3 (Count); Portfólio; Real; Tipo; % GM OR; % GM Site perdidos; % GM vendas; Cálculo1; FAT OR FY25; Fat perda anual; FAT YTD FY25; Faturamento; GP; GP OR FY25; GP perda anual; GP YTD FY25; Período; Planilha1 (Count); Retenção Faturamento; Retenção Faturamento (cópia); Retenção GP; Taxa de conversão; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP Anualizado; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Perda anualizada; Period; Reason for losing1; Regional1; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; Tipo1; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target; Target %; Target valor</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Análise NR Evento</v>
+        <v>ADH14 - CD PAP PFP</v>
       </c>
       <c r="B76" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseNREvento/AnliseNREvento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ADH14-CDPAPPFP/ADH14-CDPAPPFP</v>
       </c>
       <c r="C76" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
+        <v>BICompras - Compras Mensal</v>
       </c>
       <c r="D76" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
       </c>
       <c r="E76" t="str">
-        <v/>
-      </c>
-      <c r="F76" t="str">
-        <v>Campo Calculado</v>
+        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Análise NR Evento</v>
+        <v>FISCAL04 - Painel Gestão do Manifesto</v>
       </c>
       <c r="B77" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnliseNREvento/AnliseNREvento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto/Painel-GestodoManifesto</v>
       </c>
       <c r="C77" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
       </c>
       <c r="D77" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/162/lineage</v>
       </c>
       <c r="E77" t="str">
-        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
-      </c>
-      <c r="F77" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CFOP_VENDA; Chave NFe; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE; Dt Abertura; Dt Ano Mes; Dt Carga; XMLI_COD_CFOP; XMLI_DES_CHAVE_NFE</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Condição Vencimento por UF</v>
+        <v>Extração XML para Importação Mastersaf AM_DF</v>
       </c>
       <c r="B78" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimentoporUF/CondiodeVencimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAM_DF/PainelXMLMastersafAM</v>
       </c>
       <c r="C78" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES</v>
+        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
       </c>
       <c r="D78" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
       </c>
       <c r="E78" t="str">
-        <v/>
-      </c>
-      <c r="F78" t="str">
-        <v>Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Condição Vencimento por UF</v>
+        <v>Extração XML para Importação Mastersaf UF MG</v>
       </c>
       <c r="B79" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CondioVencimentoporUF/CondiodeVencimento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafUFMG/PainelXMLMastersafMG</v>
       </c>
       <c r="C79" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES</v>
+        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
       </c>
       <c r="D79" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
       </c>
       <c r="E79" t="str">
-        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato</v>
-      </c>
-      <c r="F79" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Quality Assurance - DANFe</v>
+        <v>O2C01 - Faturamento e Provisão</v>
       </c>
       <c r="B80" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/QualityAssurance-DANFe_17544023211490/QualityAssurance-DANFEAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/O2C01-FaturamentoeProviso/O2CEstratgico</v>
       </c>
       <c r="C80" t="str">
-        <v>Notas Fora vs. BISILVER | Projeto : INV estratégicos</v>
+        <v>BICSCFINANCAS - DSO; BICSCFINANCAS - Faturamento e Provisão</v>
       </c>
       <c r="D80" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/58204/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/52506/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48321/lineage</v>
       </c>
       <c r="E80" t="str">
-        <v/>
-      </c>
-      <c r="F80" t="str">
-        <v>Campo Calculado</v>
+        <v>% DSO Atual vs DSO Ant; Ano Fiscal Competência; Ano Fiscal Parâmetro; CC: Filtro Ano Fiscal; Consulta do SQL personalizado (Count); Cor Ano Fiscal; Dt Competência (texto); DT_COMPETENCIA; Filtro Últimos 12 meses; Gauge DSO Atual vs DSO Ant; Texto DSO Atual vs DSO Ant; Vl DSO; Vl DSO (eixo); Vl DSO Ant; Vl DSO Atual; VL_DSO; VL_META; % Fat------------------; % Fat Atual vs Fat Ant; % Faturamento; % Inad Atual vs Inad Ant; % Ind; % Ind (cópia); % Prov---------------; % Prov Atual DD vs Prov Ant DD; % Prov Atual vs Prov Ant; % Provisão; % Valor a vista-------------------; % VV Atual vs VV Ant; *% Grafico 4; *Campo Negativo; *Campo Negativo %; *Campo Negativo Seta; *Campo Negativo Seta (cópia); *Campo Positivo; *Campo Positivo %; *Campo Positivo Seta; *Campo Positivo Seta (cópia); *Cor VV Atual x Ant; *Data_Atualizada; *Data_Atualizada (copy); *Data_Atualizada Para o paramentro filtro mes ano; *Data_Hora; *Dif %; *Dif % Inadiplentes; *Login; *Texto VV Atual x Ant; *Usuário; :Measure Names; 1; Ano fiscal; Cálculo1; Cálculo3; CD_BUSINESS_UNIT; CD_DIRETORIA</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Quality Assurance - DANFe</v>
+        <v>R2R01 - Indicadores Estratégicos</v>
       </c>
       <c r="B81" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/QualityAssurance-DANFe_17544023211490/QualityAssurance-DANFEAnaltico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/R2R01-IndicadoresEstratgicos_16958287260440/R2REstratgico</v>
       </c>
       <c r="C81" t="str">
-        <v>Notas Fora vs. BISILVER | Projeto : INV estratégicos</v>
+        <v>BICSCFINANCAS - Base R2R</v>
       </c>
       <c r="D81" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/58204/lineage</v>
+        <v>Planilha ou fonte sem Custom SQL Query identificavel</v>
       </c>
       <c r="E81" t="str">
-        <v>CNPJ Fornecedor; Dados Adicionais NF; Data da Carga; Diferença dias; Dt Emissao; Dt Fechamento; Dt Recebimento; É linha duplicada?; Emissão NF; File Paths; Fornecedor; GO; Justificativa; Log; NF Chave NFE (BISILVER); NF Chave NFE (NotaFora); Nº NF; Nome Diretor; Nome Diretoria; ORIGEM DA IDENTIFICAÇÃO; Portfólio; Previsão de Encerramento; Retorno; Segmento; Série; Table Names; UF; UF do CL; Unidade; Valor NF</v>
-      </c>
-      <c r="F81" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>*Ano; *Campo Positivo; *Campo Positivo Imagem ETR; *Campo Positivo Imagem ROA; *CampoNegativo; *CampoNegativo Imagems ETR; *CampoNegativo Imagems ROA; *Cor; *Cor ETR; *Cor méd 1,0; *Data Atualização; *Data_Hora; *Dif%; *Dif% (cópia); *Login_Usuario; *Usuario; Base R2R (Count); Cálculo; Cálculo1; Descrição; Empresa; Mês/Ano; Mês/Ano (MAX); MIN(0); MIN(0) (1); MIN(0) (cópia 2); MIN(0) (cópia); Path; Periodicidade; Período; Periodo 12 meses; Periodo 3 meses; Sheet; ToolTip; Unidade; Valor; Valor (eixo negativo); Valor (eixo positivo); Valor ETR; Valores</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Evolução dos processos de reajuste FY25</v>
+        <v>MDM01 - MDM Estratégicos</v>
       </c>
       <c r="B82" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Evoluodoprocessodereajuste/Reajuste-Evoluoprocessos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MDM01-MDMEstratgicos/MateriaiseFornecedores</v>
       </c>
       <c r="C82" t="str">
-        <v>Sheet 1 (REAJUSTE 2)</v>
+        <v>BICSCFINANCAS - Base MDM</v>
       </c>
       <c r="D82" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1974/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/43041/lineage</v>
       </c>
       <c r="E82" t="str">
-        <v/>
-      </c>
-      <c r="F82" t="str">
-        <v>Campo Calculado</v>
+        <v>Custom SQL Query (Count); DSC_SEGMENTO_TIPO; DSC_TIPO; DT_COMPETENCIA; Dt_competencia (Max); DT_COMPETENCIA 1; Filtro 12 meses; Filtro máx mês; FY; Período; Período FY; QTD; Qtd abrev.; Qtd Mês Atual; Qtd Total (Fixed); TP_METRICA</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Evolução dos processos de reajuste FY25</v>
+        <v>Bonificação Coca</v>
       </c>
       <c r="B83" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Evoluodoprocessodereajuste/Reajuste-Evoluoprocessos</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BonificaoCoca/ReteioCoca</v>
       </c>
       <c r="C83" t="str">
-        <v>Sheet 1 (REAJUSTE 2)</v>
+        <v>BICompras - Compras Mensal</v>
       </c>
       <c r="D83" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1974/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
       </c>
       <c r="E83" t="str">
-        <v>% Calculado; % Concedido; :Measure Names; Centro de lucro; Cliente; Direção1; Fat. média 3 meses da data fim; Fator; Mês, Ano de Data Base1; Mês, Ano de Data fim processo; Mês, Ano de Data inicio do processo; Mês, Dia, Ano de Data reajuste retroativo mes; Nome; Período1; Processo; Reajuste calculado mês; Reajuste calculado YTD; Reajuste concedido mês; Reajuste concedido YTD; Regional; Segmento1; Serviço; Sheet 1 (Count); Situação do processo1; Tipo reajuste1</v>
-      </c>
-      <c r="F83" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Organic Growth - FY26</v>
+        <v>Grafico Familias</v>
       </c>
       <c r="B84" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY26/OGDiretoria</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/TabGraficoFamilias/InflaoRTM</v>
       </c>
       <c r="C84" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa; Clipboard_20251219T110253</v>
+        <v>Planilha1 (TesteTableau)</v>
       </c>
       <c r="D84" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2430/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2232/lineage</v>
       </c>
       <c r="E84" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; Clipboard_20251219T110253 (Count); Fili Nmgrupoeconomico; FILI NMSEGMENTO (grupo); Nomes de medida; OG Real; Valores de medida</v>
-      </c>
-      <c r="F84" t="str">
-        <v>Campo Calculado</v>
+        <v>Família; Inflação MoM; Inflação RTM; Inflação YoY; Inflação YTD; Mês; Planilha1 (Count); Segmento; Visão</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Organic Growth - FY26</v>
+        <v>Base ordem de compras</v>
       </c>
       <c r="B85" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY26/OGDiretoria</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831929220/Baseordemdecompras</v>
       </c>
       <c r="C85" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa; Clipboard_20251219T110253</v>
+        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
       </c>
       <c r="D85" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2430/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
       </c>
       <c r="E85" t="str">
-        <v/>
-      </c>
-      <c r="F85" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>FISCAL06 - Painel Check CNPJ</v>
+        <v>Retenção FY25</v>
       </c>
       <c r="B86" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL06-PainelCheckCNPJ/CheckCNPJ-XmlvsNL</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY25/KPIReteno</v>
       </c>
       <c r="C86" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
       </c>
       <c r="D86" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/11/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1790/lineage</v>
       </c>
       <c r="E86" t="str">
-        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; Xml UF Fornecedor; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; CNPJ Xml vs Nota; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação</v>
-      </c>
-      <c r="F86" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Diretoria; F6; FAT Dir LY; FY24 (Count); GP Dir LY; Regional; Segmento; % Retenção FY24; % total target; Data; Desvio; MF; Planilha3 (Count); Portfólio; Real; Tipo; % GM OR; % GM Site perdidos; % GM vendas; Cálculo1; FAT OR FY25; Fat perda anual; FAT YTD FY25; Faturamento; GP; GP OR FY25; GP perda anual; GP YTD FY25; Período; Planilha1 (Count); Retenção Faturamento; Retenção Faturamento (cópia); Retenção GP; Taxa de conversão; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Period1; Reason for losing1; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target; Target %; Target valor</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>FISCAL06 - Painel Check CNPJ</v>
+        <v>P2P02 - P2P T&amp;E Despesas</v>
       </c>
       <c r="B87" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL06-PainelCheckCNPJ/CheckCNPJ-XmlvsNL</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/P2P02-P2PTEDespesas_17574268903820/VisoGeral</v>
       </c>
       <c r="C87" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
+        <v>BICSCFINANCAS - P2P TAE DESPESAS; BICSCFINANCAS - P2P TAE DESPESAS (local copy)</v>
       </c>
       <c r="D87" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/11/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/4948/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2241/lineage</v>
       </c>
       <c r="E87" t="str">
-        <v/>
-      </c>
-      <c r="F87" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Dsc Conta; Dsc Conta (copy); Dsc Politica; Dsc Politica (cor 2); Dsc Politica (cor 3); Dsc Servico; Dt Competencia; Dt Competencia (máx); Filtro Data Competência; FY; Gauge tabela; Hoje(); Max. Dt Competência; Nm Segmento; NR_DIARIAS; Per N Viagens; Per Viagens; Período; Ticket médio; Ticket médio (hosp.); Ticket médio Ajustado; Ticket médio Ajustado (hosp.); Ticket Médio Ajustado (rótulo) (cópia); Últimos 12 meses; Últimos 3 meses; Vl Quantidade; Vl Quantidade Ajustado; Vl Quantidade Ajustado (rótulo); Vl Target Dif; Vl Tarifa; Vl Total; Vl Total Ajustado; Vl Total Ajustado (rótulo); VL_N_VIAGEM; Vl_quantidade_relacionados_a_viagens; Vl_total_contas_relacionados_a_viagens; VL_VIAGEM; VW_F_P2P_TAE_INDICADORES_ESTRA (Count)</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>FISCAL11 - Status Serviço por CNPJ</v>
+        <v>Análise PROVISÃO NF</v>
       </c>
       <c r="B88" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL11-StatusServioporCNPJ/PainelStatusServioporCNPJ</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF_17661662030420/Provisodenotasfora</v>
       </c>
       <c r="C88" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); VW_D_FILIAL_NL (BIVARREDURA)</v>
+        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
       </c>
       <c r="D88" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/9/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2431/lineage</v>
       </c>
       <c r="E88" t="str">
-        <v>Dados migrados (Count); Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Empresa; Cd Filial; CD Ind Inativo; CNPJ RAIZ; Cnpj Unidade Nl; Cód Pessoa Nl; Cód Unidade Nl; Empresa; IE; Ind Senha Unidade; Qtd Cnpj; Sk Filial; Status CNPJ; Status Servico CNPJ; Status Unidade Nl; UF; Unidade Nl</v>
-      </c>
-      <c r="F88" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Business Unit; Cd Cardapio; Cd Centro Lucro; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Grupoeconomico; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Regional; Cd Segmento; Cd Site; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Abertura; Dt Carga (Vw Mdt Centro Lucro); Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Centro Custo; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; Chave NF; CL Provisão; Planilha1 (Count); Chave NFe; Chave NFe2; CL; CNPJ Fornecedor; Conta; Conta concat; Data atual; Data de reversão; Data de reversão (grupo); Data provisão; Data reversão 2; Dias vencimento; Diferença dias; Emissão NF; Fornecedor; Lançamento provisão; Nº Nf; Origem Da Identificação; Provisão; Provisão (grupo); Provisão (grupo) 1; Provisão Notas fora (Count); Reversão; Série; Status; Tipo; Tipo (grupo); Valor NF</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>FISCAL11 - Status Serviço por CNPJ</v>
+        <v>Calculo ICMS Antecipado Arroz MG V2</v>
       </c>
       <c r="B89" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL11-StatusServioporCNPJ/PainelStatusServioporCNPJ</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CalculoICMSAntecipadoArrozMGV2/AntecipadoArroz</v>
       </c>
       <c r="C89" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); VW_D_FILIAL_NL (BIVARREDURA)</v>
+        <v>BIVarredura - XML NF Item</v>
       </c>
       <c r="D89" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/9/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
       </c>
       <c r="E89" t="str">
-        <v/>
-      </c>
-      <c r="F89" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Painel Inadimplência e PDD</v>
+        <v>Dashboard Aéreo</v>
       </c>
       <c r="B90" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelInadimplnciaePDD/RelatrioInadimplnciaePDDs-VisoSegmento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/DashboardAreo/PainelPrincipal</v>
       </c>
       <c r="C90" t="str">
-        <v>Base de Títulos</v>
+        <v>Painel Aéreo</v>
       </c>
       <c r="D90" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2519/lineage</v>
       </c>
       <c r="E90" t="str">
-        <v>% PDD sobre Carteira; Atraso após vencimento líquido; Atribuição; Base de Títulos (Count); BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento 1; Business Unit; Central de Compras; Centro de lucro; Centro de lucro (Sheet1); Chave referência 3; Cidade (End.Entrega); CNPJ Centralizador; Cód.Razão Especial; Condições pagamento; Conta; Data abertura revisada; Data Corte Inadimplência; Data de compensação; Data do documento; Diretoria; Dt Competência; Dt Competência (Max); Dt Vencimento; Empresa; Empresa (Sheet1); Estado (End.Entrega); Filial Teknisa; Filtro 13 meses; Filtro 18 meses; Filtro 3 meses; Filtro 6 meses; Filtro de Vencimento Válido; Filtro Gráfico</v>
-      </c>
-      <c r="F90" t="str">
-        <v>Campo Calculado</v>
+        <v>Adesão; Ano Fiscal; Ano Fiscal Faturamento; Antecedencia; Antecedencia (compartimento); Antecedência Ajustada; Antecedência R; Aprovador1; Atributo; Autorização; Bases (Count); Bilhete; Business Unit; Business Unit (Tabela1); Cálculo1; Cambio; Central de Compras; Central de Compras (Tabela1); Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); Chave de lançamento; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); Cidade Destino; Cidade Origem; Cidade Origem x Cidade Destino; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Cod Classe; Código Centro de Custo; Código de Autorização; Código Reason Code; Conjunto Responsável; Conta do Razão; D/C; Data abertura revisada; Data abertura revisada (Tabela1); Data de lançamento; Data do documento</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Painel Inadimplência e PDD</v>
+        <v>Organic Growth YTD</v>
       </c>
       <c r="B91" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelInadimplnciaePDD/RelatrioInadimplnciaePDDs-VisoSegmento</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowthYTD/OGYTDJunho21</v>
       </c>
       <c r="C91" t="str">
-        <v>Base de Títulos</v>
+        <v>Contabil_FY20 OG; Contabil_MetaFixa OG FY21</v>
       </c>
       <c r="D91" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
       </c>
       <c r="E91" t="str">
-        <v/>
-      </c>
-      <c r="F91" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>CR07 - Análise de Venda à Vista</v>
+        <v>Labor Efficiency</v>
       </c>
       <c r="B92" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR07-AnlisedeVendaVista/AnlisedeVendaVista</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiency_17678934428780/ReduesLabor</v>
       </c>
       <c r="C92" t="str">
-        <v>Análise Venda à Vista</v>
+        <v>Centro_Lucro; Contabil; RH - Colaborador Folha; Planilha1 (HC Budget); Sheet 1 (Labor dezembro)</v>
       </c>
       <c r="D92" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/520/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2453/lineage</v>
       </c>
       <c r="E92" t="str">
-        <v>% Crescimento Mês; % Crescimento Mês (cópia); % do Total; :Measure Names; Ano Fiscal; Campo Base; CD_BUSINESS_UNIT; CD_CARDAPIO; CD_CENTRO_CUSTO; CD_CLIENTE_NL; CD_DIRETORIA; CD_EMPRESA_SODEXO; CD_FILIAL_FICTICIA; CD_FILIAL_NL; CD_GRUPOECONOMICO; CD_MATRICULA_DIRETOR_OPERAC; CD_MATRICULA_GERENTE_AREA; CD_MATRICULA_GERENTE_REGIONAL; CD_MATRIZ; CD_ORIGEM; CD_REGIONAL; CD_SEGMENTO; CD_TIPO_ATUACAO; CD_TIPO_CONTRATO; CD_TIPO_SERVICO; CD_UF; Cliente; Cliente CNPJ CPF; Cód Filial; Consulta do SQL personalizado (Count); Conta; Data Faturamento; Data Referência; Diretoria; DSC_ORIGEM; DT_ABERTURA; DT_ARQUIVO; DT_CARGA; DT_ENCERRAMENTO; Filial</v>
-      </c>
-      <c r="F92" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; HC b; Planilha1 (Count); Desvio Fat/HC; Desvio Pess/HC; Fat OR; Fat RL; Fat/HC; Fat/HC OR; Hc Or; Pess/HC; Pess/HC OR; Pessoal OR; Pessoal RL; Real HC; Reduções; Sheet 1 (Count)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>CR07 - Análise de Venda à Vista</v>
+        <v>Campanha de incentivo GU Q1</v>
       </c>
       <c r="B93" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR07-AnlisedeVendaVista/AnlisedeVendaVista</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
       </c>
       <c r="C93" t="str">
-        <v>Análise Venda à Vista</v>
+        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
       </c>
       <c r="D93" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/520/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
       </c>
       <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Análise Prévia Consumo Novembro 2025</v>
+        <v>NES Oficial vs NES prevista EDU</v>
       </c>
       <c r="B94" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoNovembro2025/AnlisePrviadoConsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/NESOficialvsNESprevistaEDU/NESOficial</v>
       </c>
       <c r="C94" t="str">
-        <v/>
+        <v>BICOMPRAS Corporate - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO Corporate - Faturamento NL NES Item</v>
       </c>
       <c r="D94" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/2461/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3022/lineage</v>
       </c>
       <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Agrupamento Nl; Cd Cliente NL; Cd Cliente Sap; Cd Diretoria; Cd Filial; Cd Filial Nl; Cd Item Cardapio; Cd Item Venda; Cd Matriz; Cd Padrao Cardapio; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Status Contrato; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Nes; CD_LISTA_PRECO_VENDA; CD_TIP_PERIODO; Cnpj Cliente; Cód CPR; Código Item Cardápio; Código Item Venda; Cpf Cliente; CPR; Des Status Contrato; Des Tipo Cliente; Dia Fat; Dia Fim Fat; Dia Inicio Fat; DIA_LIMITE_FAT; DIA_VCTO10; DIA_VCTO3; DIA_VCTO4; DIA_VCTO5; DIA_VCTO6; DIA_VCTO7; DIA_VCTO8; DIA_VCTO9; Dsc Agrupamento Nl; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Config Contrato; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Produto Venda; Cd Sistema Origem; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_MASCARA_NL_175; CD_SITE; Cód Completo NL 175</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Análise Prévia Consumo Novembro 2025</v>
+        <v>Hospedagem</v>
       </c>
       <c r="B95" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoNovembro2025/AnlisePrviadoConsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Hospedagem/PainelPrincipal</v>
       </c>
       <c r="C95" t="str">
-        <v/>
+        <v>Bases+ (Múltiplas conexões)</v>
       </c>
       <c r="D95" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2518/lineage</v>
       </c>
       <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>[Diárias por OS (uma vez) por mês]; Adesão; Agencia; Ano Fiscal; Ano Fiscal Faturamento; Antecedencia; Aprovador; Atributo; Autorização; Bases (Count); Bilhete; Business Unit; Business Unit (Tabela1); C/D; Calculo 1; Cálculo1; Cálculo2; Cálculo2 (cópia); Cambio; Cancelada Por; Cancelados; Cargo; Categoria PVM; Central de Compras; Central de Compras (Tabela1); Centro de Custo; Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); CEP; Chave de lançamento; Cidade; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); Cidade Destino; Cidade Origem; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Cod Classe; Codigo C Custo Cliente</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>FI01 - Mapa Fiscal - Extração - V12</v>
+        <v>Conferência_Food</v>
       </c>
       <c r="B96" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V11/Painel-MapaFiscalporUF</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_Food/FechamentoFood-Integracao</v>
       </c>
       <c r="C96" t="str">
-        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
+        <v>NL.TXT+ (Múltiplas conexões)</v>
       </c>
       <c r="D96" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2059/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E96" t="str">
-        <v>Aliquotadifal; Aliquotadiferenca; Aliquotainterna; Aliquotaorigem; Basedecalculo; Cd Filial; Cnpjremetente; Dados migrados (Count); Dtcompetencia; Dtlancamento; Ieremetente; Impostocreditado; Isentas; Nronf; Number of Records; Outras; Percaliqinterestadual; Percaliqinterna; Percdiferencialaliquota; Serie; Sk Aliquotauf Od; Sk Aliquotauf Od (D Aliquotauf Od); Sk Filial; Uf Destino; Uf Origem; Uf Origemdestino; Uffilial; Ufremetente; Valorcontabil; Valordiferencialaliquota; VL Difal; Vlraliqinterest; Vlraliqinterna; Cargauf; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial (Vw D Filial); Cd Filial Ficticia; Cd Lancamento; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Uf (Vw D Filial); Cfop; Cnpjdestinatario; Conta Contabil; Creditoentradas; Dt Abertura; Dt Ano Mes; Dt Carga; Dt Carga (Vw D Tempo); Dt Encerramento; Dtcompetencia filtra ate jan21; Filial; FILIAL UF; Centrodelucro; Competencia; SK_FILIAL; VALOR_CALCULO; VL Outros Créditos; VL OutrosCreditos Calculo; Cd Contacontabil; Chavelancamento; Conta Contabil (grupo); Contacontabil; Dt Carga (Vw D Filial); Estornocom; Fl Ficticia; Hierarquia; Inscricaoestadual; Locnegocios; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Contacontabil; Nm Diretor Operacional; Nm Diretoria</v>
-      </c>
-      <c r="F96" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; 0; Acréscimos; AE; Aliq. COFINS; Aliq. ICMS; Aliq. IPI; Aliq. PIS; Ativo Soma; Ativos; Cálculo1; cc; CC NL; CC SAP; CD; Cd filial NL; Cd filial SAP; Centro de Lucro; Cfop; CFOP (Sheet1); CL; CL RNF2; Clie/Fornec; Cliente; CNPJ Dest; Cofins; Ctg. NF; Data da RNF; Data Emissão; Data Lanc; Desc. Clie/Fornec; Descrição Material; DIF TEKNISA; Doc; Doc Fisc Relac; Doc. Contábil; Doc. Fiscal; Empresa; Excluído; Exercício</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>FI01 - Mapa Fiscal - Extração - V12</v>
+        <v>Painel para Lançamento de NFe</v>
       </c>
       <c r="B97" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V11/Painel-MapaFiscalporUF</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe/PainelLanamentodeNFe</v>
       </c>
       <c r="C97" t="str">
-        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
+        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
       </c>
       <c r="D97" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2059/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
       </c>
       <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>DE01 - Demográfico</v>
+        <v>Análise de resultado - Mapa Portfólio</v>
       </c>
       <c r="B98" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DE01-Demogrfico/Demogrfico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaPortflio/Anlisedefaturamento-mapa</v>
       </c>
       <c r="C98" t="str">
-        <v>BICSCFINANCAS - Quantitativo Colaboradores</v>
+        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
       </c>
       <c r="D98" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31663/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
       </c>
       <c r="E98" t="str">
-        <v>*%HE; *Aculmulado Admissão+Desligamento / 2; *CC Colaboradores Admissão; *CC Colaboradores Desligamento; *CC Perc Turn Over; *Dif Horas Meses e Extras; *Periodo Ajustado; *Periodo Ajustado (texto); :Measure Names; [fn] Data atualização; [fn] Usuario; { FIXED [Ano Competencia]:sum(IIF([Fleg Rescisao]='S',[Qtd Co...; 1; 1 (1); Ano Mes Competencia; Cálculo1; Cálculo2; CC Colaboradores ativos; CC Filtro Ano; CC Filtro Mes; CC FTE budget; CC Perc Attr; CC Qt Attrition; CC Qt Recisao; Cd Filial; Domain; DSC_ATTRITION_RATE; Dt Competencia; Dt Competência (Max); F_SSC_QUANTITATIVO_COLABORADOR (Count); Faixa Idade; Filtro 12 Meses; Filtro 3 Meses; Filtro Ano Atual; Filtro Mês Abaixo; Filtro Mês Atual; Fleg Ativo; Fleg Gestor; Fleg Rescisao; FLEG_ADMISSAO</v>
-      </c>
-      <c r="F98" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>DE01 - Demográfico</v>
+        <v>TRE01 - TRE Visão Financeira</v>
       </c>
       <c r="B99" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DE01-Demogrfico/Demogrfico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/TRE01-TREVisoFinanceira/VisoGeral</v>
       </c>
       <c r="C99" t="str">
-        <v>BICSCFINANCAS - Quantitativo Colaboradores</v>
+        <v>BICSCFINANCAS - TRE Estratégicos</v>
       </c>
       <c r="D99" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/31663/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/57473/lineage</v>
       </c>
       <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>[fn] Data atualização; [fn] Usuario; Check TRE; Dsc Indicador; Dsc Periodo; Dsc Source; Dt Ano Fiscal; Dt Carga; Dt Competencia; Dt Competência; Dt Competência (Max); F_CSC_TRE (Count); Filtro Ano Fiscal; Filtro Dt Competência 12 Meses; Filtro Dt Competência 6 Meses; Filtro Dt Competência 6 Meses (Ger. de Caixa); Filtro Dt Competência Mês Anterior; Filtro Dt Competência Mês Atual; Filtro FYTD; lbl DataHora; lbl Usuario; Nm Banco; Vl Met Blc 1 Forecast; Vl Met Blc 1 Receita; Vl Met Blc 1 Receita (tooltip); Vl Met Blc 2 Rendimento CDI; Vl Met Blc 2 Rendimento CDI (tooltip); Vl Met Blc 3 Saldo por Banco; Vl Met Blc 4 Fluxo Operacional; Vl Met Blc 4 Fluxo Operacional (tooltip); Vl Met Blc 4 Saldo de Tesouraria; Vl Met Blc 5 Despesas; Vl Met Blc 5 Despesas (tooltip); Vl Met Blc 6 Fiança e Garantias; Vl Met Blc 6 Fiança e Garantias (tooltip); Vl Metrica; Vl Métrica Mês Anterior; Vl Métrica Mês Atual; Vl Perc Blc 1; Vl Perc Blc 1 Cor</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Painel Controller RYDOO</v>
+        <v>PFD100 - VARIAÇÃO DE NES E LANÇAMENTOS (Ajustes Rótulos)</v>
       </c>
       <c r="B100" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelControllerRYDOO/PainelController</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PFD100-VARIAODENESELANAMENTOSAjustesRtulos_17519186689340/TABELA</v>
       </c>
       <c r="C100" t="str">
-        <v>Base (Controller Táxi Rydoo - FY26)</v>
+        <v/>
       </c>
       <c r="D100" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2432/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E100" t="str">
-        <v>Aprovada por; Base (Count); Cadastrado; Cálculo1; Categorizado Rejeição; Controller; Data de aprovação; Email; Mês Controle; Reemboolsado; Top; Usuário; Valor; Xpd Reference</v>
-      </c>
-      <c r="F100" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Painel Controller RYDOO</v>
+        <v>Price List FY24_v2</v>
       </c>
       <c r="B101" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelControllerRYDOO/PainelController</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PriceListFY24_v2/PriceListFY24</v>
       </c>
       <c r="C101" t="str">
-        <v>Base (Controller Táxi Rydoo - FY26)</v>
+        <v/>
       </c>
       <c r="D101" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2432/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E101" t="str">
         <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Análise de resultado - Mapa</v>
+        <v>Resultado financeiro - SG&amp;A Teste budget</v>
       </c>
       <c r="B102" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapa/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-SGATestebudget/ResultadoSGA</v>
       </c>
       <c r="C102" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
+        <v>Centro_Lucro; Contabil (cópia); Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; March_Fcst_v9 (Compactada_FPA_March_Fcst_2025-03-11-v9)</v>
       </c>
       <c r="D102" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2359/lineage</v>
       </c>
       <c r="E102" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO</v>
-      </c>
-      <c r="F102" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Budget (Count); Data; Desvio; March Forecast; Nº conta; Numero do CL; Tagetik; Valor; Versão; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Análise de resultado - Mapa</v>
+        <v>Base ordem de compras consumo</v>
       </c>
       <c r="B103" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapa/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831706610/Baseordemdecompras</v>
       </c>
       <c r="C103" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
+        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
       </c>
       <c r="D103" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
       </c>
       <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Resultado financeiro - Fat e GP Ano Fiscal</v>
+        <v>Análise Prévia Consumo Janeiro 2026</v>
       </c>
       <c r="B104" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscal/FateGPSAP-Anofiscal</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
       </c>
       <c r="C104" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
+        <v/>
       </c>
       <c r="D104" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2050/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E104" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F104" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Resultado financeiro - Fat e GP Ano Fiscal</v>
+        <v>Price List_FY24</v>
       </c>
       <c r="B105" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscal/FateGPSAP-Anofiscal</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PriceList_FY24/PriceListFY24</v>
       </c>
       <c r="C105" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
+        <v/>
       </c>
       <c r="D105" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2050/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E105" t="str">
         <v/>
-      </c>
-      <c r="F105" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Base ordem de compras completa</v>
+        <v>Análise Prévia Consumo Média PAP - Janeiro 26</v>
       </c>
       <c r="B106" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecomprascompleta/Baseordemdecompras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Janeiro26/Anliseprviaconsumo</v>
       </c>
       <c r="C106" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
+        <v/>
       </c>
       <c r="D106" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E106" t="str">
-        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
-      </c>
-      <c r="F106" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Base ordem de compras completa</v>
+        <v>Mobilidade</v>
       </c>
       <c r="B107" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecomprascompleta/Baseordemdecompras</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Mobilidade/PainelPrincipal</v>
       </c>
       <c r="C107" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
+        <v>Bases (Mobilidade)</v>
       </c>
       <c r="D107" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2517/lineage</v>
       </c>
       <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Ano; Ano Fiscal; Ano Fiscal Faturamento; Atributo; Autorização; Bases (Count); BU; Business Unit; Business Unit (Tabela1); Cargo; Cargo Superior; CCusto Superior; Central de Compras; Central de Compras (Tabela1); Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); Centro de Lucro F; Chave de lançamento; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); CL; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Colaborador; Conta do Razão; Data abertura revisada; Data abertura revisada (Tabela1); Data de lançamento; Data do documento; Destino; Diretoria; Diretoria (Tabela1); E-mail; E-mail (Bases); E-mail RYDOO; Email Superior; Empresa; Empresa (Sheet1); Empresa (Tabela1)</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Análise PROVISÃO NF2</v>
+        <v>Contratos Data Limite Faturamento - Serviço</v>
       </c>
       <c r="B108" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF2/Planilha24</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosDataLimiteFaturamento-Servio/ContratosDataLimite</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
       </c>
       <c r="D108" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
       </c>
       <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v>Campo Calculado</v>
+        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Análise PROVISÃO NF2</v>
+        <v>Extração de XML por UF com Impostos</v>
       </c>
       <c r="B109" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF2/Planilha24</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraodeXMLporUFcomImpostos/ExtraodeXMLporUFcomImpostos</v>
       </c>
       <c r="C109" t="str">
-        <v/>
+        <v>BIVarredura - XML NF Item</v>
       </c>
       <c r="D109" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
       </c>
       <c r="E109" t="str">
-        <v/>
-      </c>
-      <c r="F109" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Análise de resultado - Mapa Cidade</v>
+        <v>Risco Sacado</v>
       </c>
       <c r="B110" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaCidade/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RiscoSacado/RiscoSacado</v>
       </c>
       <c r="C110" t="str">
-        <v/>
+        <v>BASE (Consolidado Risco Sacado)</v>
       </c>
       <c r="D110" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E110" t="str">
-        <v/>
-      </c>
-      <c r="F110" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; BASE (Count); Cnpj; Cnpj (Fornecedores); Cond. Pgto (FORNECEDORES1); Consolidado ZA e ZF (Count); Data de compensação (Consolidado ZA e ZF); Data De Lanç; Data de lançamento; Data De Venc; Data Inclusão; Data Inclusão (FORNECEDORES1); Dias; Dt Competência; Dt Competência (Compensadas); Dt Competência (Faturas); Dt Competência (Fornecedores); Dt Competência (Max); Empresa; Faturas enviadas (KM) (Count); Filtro 12 meses; Filtro 12 meses (Compensadas); Filtro 12 meses (Faturas); Filtro Dt Competência; Filtro gráfico; Filtro Mês Anterior; Filtro Mês Atual; Filtro Mês Atual (Compensadas); Filtro Mês Atual (Faturas); Fornecedor; Fornecedor (FORNECEDORES1); FORNECEDORES (Count); FORNECEDORES1 (Count); Montante em moeda interna; Montante em moeda interna (ajustado); Montante em moeda interna (Consolidado ZA e ZF); N° Doc; Período; Período (Faturas); Prazo médio da fatura</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Análise de resultado - Mapa Cidade</v>
+        <v>Estorno</v>
       </c>
       <c r="B111" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaCidade/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Estorno/Estorno</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E111" t="str">
         <v/>
-      </c>
-      <c r="F111" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PIS/COFINS sobre NF</v>
+        <v>Conferência Food</v>
       </c>
       <c r="B112" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PISCOFINSsobreNF/PISCOFINSsobreNF</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ConfernciaFood/FechamentoFood-Integracao</v>
       </c>
       <c r="C112" t="str">
-        <v>Centro_Lucro; União de linhas (Razão consumo)</v>
+        <v/>
       </c>
       <c r="D112" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2171/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E112" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; % COFINS S/NF; % Gasto com CD; % ICMS S/NF; % Logistica; % PIS S/NF; % PIS/COFINS CD; % Total PIS/COFINS; :Measure Names; Cálculo1; Cálculo2; Cen.lucro; COFINS SOBRE NF; Conta; Conta (cópia); D; DATA; Data doc/; Data lçto/; Denominação; Doc.compra; em MdICenL; Empr; Fornec.; Fornec. (grupo); Fornec. (grupo) 1; Fornecedor 2; Gastos com CD; ICMS SOBRE NF; Logistica Alimentar; NF; Nº conta; Nº doc.; Nºdoc.ref.; Others; Outros; Período; PIS SOBRE NF; PIS/COFINS CD; Sheet; Table Name</v>
-      </c>
-      <c r="F112" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>PIS/COFINS sobre NF</v>
+        <v>Contratos Pedido</v>
       </c>
       <c r="B113" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PISCOFINSsobreNF/PISCOFINSsobreNF</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosPedido/ContratosPedido</v>
       </c>
       <c r="C113" t="str">
-        <v>Centro_Lucro; União de linhas (Razão consumo)</v>
+        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
       </c>
       <c r="D113" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2171/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
       </c>
       <c r="E113" t="str">
-        <v/>
-      </c>
-      <c r="F113" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Resultado financeiro - Desvio consumo</v>
+        <v>Análise de Estorno</v>
       </c>
       <c r="B114" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Desvioconsumo/Desvioconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisedeEstorno/Estorno</v>
       </c>
       <c r="C114" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
+        <v/>
       </c>
       <c r="D114" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2055/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E114" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F114" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Resultado financeiro - Desvio consumo</v>
+        <v>Comparativo Food</v>
       </c>
       <c r="B115" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Desvioconsumo/Desvioconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ComparativoFood/ComparativoFood</v>
       </c>
       <c r="C115" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
+        <v/>
       </c>
       <c r="D115" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2055/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E115" t="str">
         <v/>
-      </c>
-      <c r="F115" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Indicadores Fiscais</v>
+        <v>Insights de Cancelamento de Notas Fiscais - Fatores e Impactos</v>
       </c>
       <c r="B116" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadorescontasdeimpostos/5-BaseporCL</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/InsightsdeCancelamentodeNotasFiscais-FatoreseImpactos_17313493325020/VisoGeral</v>
       </c>
       <c r="C116" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; 07.05 BASE ABRIL (07.05 BASE ABRIL.xls)</v>
+        <v>BIFATURAMENTO - Faturamento NL NES Item; Compilado (Estorno Compilado)</v>
       </c>
       <c r="D116" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1871/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1792/lineage</v>
       </c>
       <c r="E116" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Crédito PIS Cofins; 07.05 BASE ABRIL (Count); Cen.lucro; Cliente; D; Data doc.; Data lçto.; Denominação; Doc.compra; Doc.venda; em MdICenL; Empr; Fornec.; Nº conta; Nº doc.; Nºdoc.ref.; Período; Texto; Tip Ft; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real</v>
-      </c>
-      <c r="F116" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175; Business Unit; Cancelados Mês Anterior; Cancelados Mês Atual; CC; Cfop; Cliente; CNPJ Remetente; Coluna1; Competência; Competência (Max); Compilado (Count); Data Lanc; Destacar Picos; Diretoria; Display; Dt Competência; Eixo; Fator Gerador; Filial; Filial2; Filtra Mês Atual; Filtro 13 meses; Filtro Mês Anterior; Filtro Mês Atual; Ícone; IE Remetente; Imp Credit; Isentas; Motivo; NF; NF origem; Nm Filial; Nº da NF; Origem do Estorno; Outras; Qt Cancelamentos; Qt Clientes; Rank Centro de Lucro; Rank Clientes</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Indicadores Fiscais</v>
+        <v>Resultado financeiro - SG&amp;A</v>
       </c>
       <c r="B117" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadorescontasdeimpostos/5-BaseporCL</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmico_17320354393150/Colaboradoresativoseafastados</v>
       </c>
       <c r="C117" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; 07.05 BASE ABRIL (07.05 BASE ABRIL.xls)</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D117" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1871/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1802/lineage</v>
       </c>
       <c r="E117" t="str">
-        <v/>
-      </c>
-      <c r="F117" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rateio Custo CD Consolidador Data Corte FY26</v>
+        <v>Resultado financeiro - Grupo conta</v>
       </c>
       <c r="B118" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDConsolidadorDataCorteFY26/RateioCustoCDConsolidadorDiario</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoconta/Resultadogrupoconta</v>
       </c>
       <c r="C118" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha</v>
       </c>
       <c r="D118" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1503/lineage</v>
       </c>
       <c r="E118" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rateio Custo CD Consolidador Data Corte FY26</v>
+        <v>CR04 - Títulos Vencidos</v>
       </c>
       <c r="B119" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioCustoCDConsolidadorDataCorteFY26/RateioCustoCDConsolidadorDiario</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CR04-TtulosVencidos/TtulosVencidos</v>
       </c>
       <c r="C119" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
+        <v>Análise de Títulos Vencidos</v>
       </c>
       <c r="D119" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/577/lineage</v>
       </c>
       <c r="E119" t="str">
-        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
-      </c>
-      <c r="F119" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% do Total; :Measure Names; Ano Arquivo; Ano Fiscal; Ano Fiscal Data Referência; Atraso; Atribuição; Base; CD_ATR; CD_BUSINESS_UNIT; CD_CARDAPIO; CD_CENTRO_CUSTO; CD_CLIENTE_NL; CD_DIRETORIA; CD_EMPRESA_SODEXO; CD_FILIAL_FICTICIA; CD_FILIAL_NL; CD_GRUPOECONOMICO; CD_MATRICULA_DIRETOR_OPERAC; CD_MATRICULA_GERENTE_AREA; CD_MATRICULA_GERENTE_REGIONAL; CD_MATRIZ; CD_ORIGEM; CD_REGIONAL; CD_SEGMENTO; CD_TIPO_ATUACAO; CD_TIPO_CONTRATO; CD_TIPO_SERVICO; CD_UF; Cliente; Cliente CNPJ CPF; Clúster Títulos Vencidos; Cód Filial; Consulta do SQL personalizado (Count); Conta; Data; Data Vencimento; Diretoria; DSC_ORIGEM; DSC_TEXTO_CABECALHO_DOCUMENTO</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Performance_Retails</v>
+        <v>Resultado financeiro - Fat e GP Ano Fiscal mês a mês</v>
       </c>
       <c r="B120" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retails/PerformanceRetail_1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscalmsams/FateGPSAP-Anofiscal</v>
       </c>
       <c r="C120" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D120" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2051/lineage</v>
       </c>
       <c r="E120" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
-      </c>
-      <c r="F120" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Performance_Retails</v>
+        <v>Organic Growth - FY24</v>
       </c>
       <c r="B121" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Performance_Retails/PerformanceRetail_1</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY24/OrganicGrowth</v>
       </c>
       <c r="C121" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
       </c>
       <c r="D121" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
       </c>
       <c r="E121" t="str">
-        <v/>
-      </c>
-      <c r="F121" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Projeção de Inflação - Global por Nota Fiscal MoM</v>
+        <v>F03 - Extração de Itens XML por UF com Imposto</v>
       </c>
       <c r="B122" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjeodeInflao-GlobalporNotaFiscalMoM/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/F03-ExtraodeItensXMLporUFcomImposto/ExtraodeItensXMLporUFcomImposto</v>
       </c>
       <c r="C122" t="str">
-        <v>Projeção</v>
+        <v>BIVarredura - XML NF Item</v>
       </c>
       <c r="D122" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/587/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
       </c>
       <c r="E122" t="str">
-        <v>% a ser considerado na var; % a ser considerado na var (PAP); % a ser considerado na var (TRA); % Considerado no calculo; % Estq 3 meses (TRA); % Inflação (Proj. M2); % Inflação (Proj. M2) (PAP); % Inflação (Proj. M2) (Segmento); % Inflação (Proj. M2) (Segmento) (PAP); % Inflação (Proj. M2) (Segmento) (TRA); % Inflação (Proj. M2) (TRA); % Inflação (Proj. M3); % Inflação (Proj. M3) (PAP); % Inflação (Proj. M3) (Segmento); % Inflação (Proj. M3) (Segmento) (PAP); % Inflação (Proj. M3) (Segmento) (TRA); % Inflação (Proj. M3) (TRA); % Inflação (Proj. M4) (PAP); % Inflação (Proj. M4) (Segmento); % Inflação (Proj. M4) (Segmento) (PAP); % Inflação (Proj. M4) (Segmento) (TRA); % Inflação (Proj. M4) (TRA); % Inflação (Proj.); % Inflação (Proj.) (Media consumo 3 meses)); % Inflação (Proj.) (PAP); % Inflação (Proj.) (Regra Estoque); % Inflação (Proj.) (Segmento); % Inflação (Proj.) (Segmento) (PAP); % Inflação (Proj.) (Segmento) (TRA); % Inflação (Proj.) (TRA); % Rank; % Repres. Bonif. Pedidos em aberto CD; % Repres. Bonificação Base Line; % Repres. Qtd Necessid. Consum. (TRA); % Variação de mercado M1 (TRA); % Variação de mercado M2; % Variação de mercado M2 (PAP); % Variação de mercado M2 (TRA); % Variação de mercado M3; % Variação de mercado M3 (PAP)</v>
-      </c>
-      <c r="F122" t="str">
-        <v>Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Projeção de Inflação - Global por Nota Fiscal MoM</v>
+        <v>IE01 - Performance de Atendimento - V2.1</v>
       </c>
       <c r="B123" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ProjeodeInflao-GlobalporNotaFiscalMoM/1-InflaoGlobalGeral</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento-V2_1/SatisfaodoClientenoAtendimento</v>
       </c>
       <c r="C123" t="str">
-        <v>Projeção</v>
+        <v>BICSCFINANCAS - Chamados CA (NEW); BICSCFINANCAS - Satisfação</v>
       </c>
       <c r="D123" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/587/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2102/lineage</v>
       </c>
       <c r="E123" t="str">
-        <v/>
-      </c>
-      <c r="F123" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Usuario; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; CC: Nr Dias Atendimento (c/ pendente); CC: Nr Dias Atendimento (s/ pendente); CC: Tempo de Resolucao; Cd Canal; Cd Uf; Custom SQL Query (Count); Domain; DS_CANAL; DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Selecionado; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Respondidos vs Concluídos Comparativo; Gauge Total Atendimento Comparativo; Gauge Total Entrega Comparativo; Insatisfeito; Insatisfeito Entrega; NM_ANALISTA; NM_GRUPO; NM_SRC; NM_USR_AFETADO; NR_CHAMADO</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Painel de Exclusão do ICMS de PIS_COFINS nas Entradas</v>
+        <v>Resultado financeiro - Grupo econômico análise pessoal %</v>
       </c>
       <c r="B124" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeExclusodoICMSdePIS_COFINSnasEntradas/PainelPISCOFINS</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmicoanlisepessoal_17392198009060/Anlisepessoalporservio</v>
       </c>
       <c r="C124" t="str">
-        <v>BIVarredura - XML NF Item; Entradas SAP 05_2023 Sodexo</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; Clipboard_20250210T152659; Clipboard_20250210T152751; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D124" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1061/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1937/lineage</v>
       </c>
       <c r="E124" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Base Cálc SEM ICMS; Base Cálculo PIS; Central de Compras; Centro de lucro1; Cidade (Todos excetuado Branch); Cnpj / Cpf; Data Lançamento; Débito de COFINS; Débito PIS; Descrição; Doc.Contáb; Empresa; Entradas SAP.csv (Count); Filial; Filial Teknisa; ID Tipo contrato; index; Modelo; Nome diretoria; Nome do Diretor; Nome do Gerente Area; Nome do Gerente Regional; Nome do Grupo Economico; Nome do Site; Nome Filial; Nota Fiscal; Nota+CNPJ; Número Documento; Opening date; Path; PIS&amp;COFINS; Razão Social; Região (Todos excetuado Branch); Regime Apuração; Regional; Segmento1; Série; Subsegment; Subserviço descrição</v>
-      </c>
-      <c r="F124" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Pessoal; % Pessoal OR; Clipboard_20250210T152659 (Count); Mês de CONT DTFECHAMENTO; Nomes de medida; Clipboard_20250210T152751 (Count); ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Painel de Exclusão do ICMS de PIS_COFINS nas Entradas</v>
+        <v>Resultado financeiro - Trimestre</v>
       </c>
       <c r="B125" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeExclusodoICMSdePIS_COFINSnasEntradas/PainelPISCOFINS</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Trimestre/ResultadoSAPFateGP</v>
       </c>
       <c r="C125" t="str">
-        <v>BIVarredura - XML NF Item; Entradas SAP 05_2023 Sodexo</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D125" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1061/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1746/lineage</v>
       </c>
       <c r="E125" t="str">
-        <v/>
-      </c>
-      <c r="F125" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Cálculo ICMS ST a Recolher MG</v>
+        <v>Painel</v>
       </c>
       <c r="B126" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ClculoICMSSTaRecolherMG/ICMSST</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Painel/Equinor_</v>
       </c>
       <c r="C126" t="str">
-        <v>BIVarredura - XML NF Item; Tabela NCM ST</v>
+        <v/>
       </c>
       <c r="D126" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/406/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E126" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Descrição; MVA; MVA Ajust; MVA Ajustado; MVA Calculo; NCM; NCM ST; Ncm Tabela; Tabela NCM ST.csv (Count)</v>
-      </c>
-      <c r="F126" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Cálculo ICMS ST a Recolher MG</v>
+        <v>Relatorio de Materiais de Venda - MDM</v>
       </c>
       <c r="B127" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ClculoICMSSTaRecolherMG/ICMSST</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeMateriaisdeVenda-MDM/RelatriodeMateriaisdeVenda</v>
       </c>
       <c r="C127" t="str">
-        <v>BIVarredura - XML NF Item; Tabela NCM ST</v>
+        <v/>
       </c>
       <c r="D127" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/406/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E127" t="str">
         <v/>
-      </c>
-      <c r="F127" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Custo Target</v>
+        <v>Medição x Vencimento</v>
       </c>
       <c r="B128" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Target_17115510333040/Custotarget</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/MedioxVencimento/MedioxVencimento</v>
       </c>
       <c r="C128" t="str">
-        <v>BICOMPRAS - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO - Faturamento NL NES Item (cópia); Contabil_Conta (cópia); Sheet 1 (Concatenar)</v>
+        <v/>
       </c>
       <c r="D128" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/36425/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1277/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E128" t="str">
-        <v>% Compliance; % Lançamento Mês; Agrupamento; Cd Cliente NL; Cd Cliente Sap; Cd Filial; Cd Filial Nl; Cd Item Cardapio; Cd Item Venda; Cd Matriz; Cd Seq Periodo; Cd Status Contrato; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Nes; CD_LISTA_PRECO_VENDA; CD_TIP_PERIODO; Cnpj Cliente; Cód Agrupamento; Cód CPR; Código Item Cardápio; Código Item Venda; Cpf Cliente; CPR; CTL_DT_ENCERRAMENTO_TERMO; Dados migrados (Count); Des Status Contrato; Des Tipo Cliente; Dia Fat; Dia Fim Fat; Dia Inicio Fat; DIA_LIMITE_FAT; DIA_VCTO10; DIA_VCTO3; DIA_VCTO4; DIA_VCTO5; DIA_VCTO6; DIA_VCTO7; DIA_VCTO8; DIA_VCTO9; :Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Sistema Origem; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_MASCARA_NL_175; CD_SITE; Cód Completo NL 175; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; Cardapio; Classificação Cardápio; Concatenar; Custo Planejado; Filial1; Item Venda; Sheet 1 (Count)</v>
-      </c>
-      <c r="F128" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Custo Target</v>
+        <v>Relatorio de Quantidade UF</v>
       </c>
       <c r="B129" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Target_17115510333040/Custotarget</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidadeUF/Quantidade</v>
       </c>
       <c r="C129" t="str">
-        <v>BICOMPRAS - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO - Faturamento NL NES Item (cópia); Contabil_Conta (cópia); Sheet 1 (Concatenar)</v>
+        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
       </c>
       <c r="D129" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/36425/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1277/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
       </c>
       <c r="E129" t="str">
-        <v/>
-      </c>
-      <c r="F129" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Análise Prévia Consumo Média PAP - Outubro 25</v>
+        <v>Relatorio de Quantidade_Cliente</v>
       </c>
       <c r="B130" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Outubro25/Anliseprviaconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade_Cliente/Quantidade</v>
       </c>
       <c r="C130" t="str">
-        <v/>
+        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
       </c>
       <c r="D130" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
       </c>
       <c r="E130" t="str">
-        <v/>
-      </c>
-      <c r="F130" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Análise Prévia Consumo Média PAP - Outubro 25</v>
+        <v>Banco de Dados Processos CSC Finanças (ITIs)</v>
       </c>
       <c r="B131" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Outubro25/Anliseprviaconsumo</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BancodeDadosProcessosCSCFinanasITIs/BancodeDadosProcessosCSCFinanasITIs</v>
       </c>
       <c r="C131" t="str">
-        <v/>
+        <v>Banco de Dados Processos CSC FY26__6829137108881284s_(ITI_s) (Smartsheet: juliana.pantoja@sodexo.com)</v>
       </c>
       <c r="D131" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2282/lineage</v>
       </c>
       <c r="E131" t="str">
-        <v/>
-      </c>
-      <c r="F131" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>_Attachcount; _Childids; _Discusscount; _Discusstext; _Outlinelevel; _Parentid; _Rowid; _Rownum; _Workspaceid; _Workspacename; Antecessores; Aprovador; Atividades Filho; Atrasadas; Banco de Dados Processos CSC FY26__6829137108881284s_(ITI_s) (Count); Código da ITI; Controle Relacionado; Data da revisão; Data limite para revisão; Data Planejado Assessment Controle; Data Próximo Revisão de ITI por CI; Duração; Eixo; Fase Assessment; Hierarquia; N° Atrasadas; Nome da ITI; Prazos; Processo; Quant. por domain; Quant. Status; Responsável pela Revisão; Status; Status CI; Status padronizado; Subprocesso; Tipo de automação</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>VD51</v>
+        <v>Rateio Bonificação CD_FY26</v>
       </c>
       <c r="B132" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VD51/VD51</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/RateioBonificaoCD_FY26_17611615626620/RateioBonificaoCDs-Dirio</v>
       </c>
       <c r="C132" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL; Saidas por Itens; Sheet1 (CEST)</v>
+        <v>BICOMPRAS - Compras Diaria</v>
       </c>
       <c r="D132" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/workbooks/509/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
       </c>
       <c r="E132" t="str">
-        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento; Aliquota ICMS; Base FCP; Base ICMS; Base IPI; CD FILIAL SAP; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CNPJ; CNPJ Destinatário; Cst Icms; Data Lançamento1; Descrição do material1; Despesa; Estrutura SAIDAS POR ITENS.csv (Count); F20; FCP aliq; Filial; Filtra CFOP; Index; IPI aliq; Item Texto; NCM1; NF1; Nº do material1; Nº documento; Nº item do documento; Número Pedido Item; Path; Quantidade; Série1; Tipo NF; UF Destinatário; UF1; Valor Diferencial Aliquota; Valor do Item; Valor do Item 1; Valor FCP; Valor ICMS; CEST; Código de controle; Data início; Material; Sheet1 (Count)</v>
-      </c>
-      <c r="F132" t="str">
-        <v>Campo Calculado</v>
+        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>VD51</v>
+        <v>Análise Prévia Consumo Dezembro 2025</v>
       </c>
       <c r="B133" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/VD51/VD51</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoDezembro2025/AnlisePrviadoConsumo</v>
       </c>
       <c r="C133" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL; Saidas por Itens; Sheet1 (CEST)</v>
+        <v/>
       </c>
       <c r="D133" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/workbooks/509/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E133" t="str">
         <v/>
-      </c>
-      <c r="F133" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Catálogo de Painéis e Indicadores</v>
+        <v>CR08 - Provisão e Faturamento</v>
       </c>
       <c r="B134" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CatlogodePainiseIndicadores/CatlogodePainis-GestoePerformance</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CR08-ProvisoeFaturamento/EvoluodoFaturamento</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E134" t="str">
         <v/>
-      </c>
-      <c r="F134" t="str">
-        <v>Campo Calculado</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Catálogo de Painéis e Indicadores</v>
+        <v>Análise Prévia Consumo Média PAP - Dezembro 25</v>
       </c>
       <c r="B135" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CatlogodePainiseIndicadores/CatlogodePainis-GestoePerformance</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Dezembro25/Anliseprviaconsumo</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E135" t="str">
         <v/>
-      </c>
-      <c r="F135" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>ADH18 - Item receita</v>
+        <v>Base Reajuste completa</v>
       </c>
       <c r="B136" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH18-Itemreceita/ITEMRECEITA</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/BaseReajustecompleta/Basereajuste</v>
       </c>
       <c r="C136" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v>Reajuste_Contrato</v>
       </c>
       <c r="D136" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage</v>
       </c>
       <c r="E136" t="str">
-        <v/>
-      </c>
-      <c r="F136" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; ANDAMENTO; CODUNIDADEFILIAL; Dados migrados (Count); DATAHORAFIMHIST; DATAHORAINICIOHIST; DATAMESCORRENTE; DATAMESREAJUSTERETROATIVO; DATAREAJUSTERETROATIVO; DESCINDICECOMPOSICAOREAJUSTE; DESCSITUACAOPROCESSO; DESCWORKFLOW; DIFERENCAAPLICADOCALCULADO; FATORMESACUMULADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>ADH18 - Item receita</v>
+        <v>Saving</v>
       </c>
       <c r="B137" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH18-Itemreceita/ITEMRECEITA</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Saving/Anlise</v>
       </c>
       <c r="C137" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v/>
       </c>
       <c r="D137" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E137" t="str">
-        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
-      </c>
-      <c r="F137" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Faturamento com PO</v>
+        <v>FISCAL10 - Painel Manifestação Manual</v>
       </c>
       <c r="B138" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FaturamentocomPO/FaturamentoFood</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL10-PainelManifestaoManual/ManifestaoManual</v>
       </c>
       <c r="C138" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES; BIFATURAMENTO - Faturamento NL NES Item; Sheet1 (FM); Sheet1 (SAP Pedido)</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
       </c>
       <c r="D138" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/701/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/21/lineage</v>
       </c>
       <c r="E138" t="str">
-        <v>Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Sequencia Periodo; Cd Status Contrato; Cd Status Dtfat; Cd Status Nes; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Dia Vencimento; Cd Tipo Servico; Cd Tp Nes; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_SITE; Cnpj Cliente; Cpf Cliente; Dados migrados (Count); DataHora Atualização; Descrição Configuração Contrato; :Measure Names; Cd Business Unit; Cd Familia Venda; Cd Produto Venda; Cd Seq Periodo; Cd Sistema Origem; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Unidade Medida; CD_MASCARA_NL_175; Cód Completo NL 175; 0; Aliq COFINS; Aliq INSS; Aliq INSS (Sheet1); Aliq IRF; Aliq IRF (Sheet1); Aliq ISS; Aliq ISS (Sheet1); Aliq PIS; Aliq PIS (Sheet1); AlIq. CSLL; AlIq. CSLL (Sheet1); AliqCOFINS (Sheet1); Centro de Custo; Centro de Custo (Sheet1); Cliente Sap; CNPJ Cli; CNPJ Cli (Sheet1); CNPJ Emit.; CNPJ Emit. (Sheet1); Cnpj Fil.; CNPJ FIL. (Sheet1); Cod. Cliente (Sheet1); Código Material; Código Material (Sheet1); COFINS Ret; COFINS Ret (Sheet1); CSLL Ret; CSLL Ret (Sheet1); Data Comp; Data Comp (Sheet1); Data Lançamento; Data Lançamento (Sheet1); Descrição Material; Descrição Material (Sheet1); Descrição NCM; Descrição NCM (Sheet1); Doc Contábil; Doc Contábil (Sheet1); Doc.Comp.; 13695.2; 39197; 456.505,74; Aliquota ICMS; Base de Cálculo; Base FCP; Base ICMS; Base IPI; Centro de Lucro; Cfop; Chave da Nota Fiscal Eletrônica; CL1; CNPJ Destinatário; Cst Icms; Descrição do material; Despesa; FCP aliq; Filial; Filial Destinatário; IE Destinatário; Imposto Debitado; IPI aliq; Isentas; Item Texto; NCM; NF; Nº do material; Nº documento; Nº item do documento; Nome Destinatário; Número do Pedido; Outras; Path; Quantidade; Right; Série; Sheet</v>
-      </c>
-      <c r="F138" t="str">
-        <v>Campo Calculado</v>
+        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Migrated Data (Count); Number of Records; Status XML; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Faturamento com PO</v>
+        <v>Organic Growth - FY25</v>
       </c>
       <c r="B139" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FaturamentocomPO/FaturamentoFood</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY25/OGClientes</v>
       </c>
       <c r="C139" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES; BIFATURAMENTO - Faturamento NL NES Item; Sheet1 (FM); Sheet1 (SAP Pedido)</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
       </c>
       <c r="D139" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2987/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/701/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
       </c>
       <c r="E139" t="str">
-        <v/>
-      </c>
-      <c r="F139" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Resultado financeiro</v>
+        <v>Evolução dos processos de reajuste FY26</v>
       </c>
       <c r="B140" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro/10-UOPMetaFixa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/EvoluodosprocessosdereajusteFY26/Reajuste-Evoluoprocessos</v>
       </c>
       <c r="C140" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_MetaFixa (2)</v>
+        <v>Sheet 1 (REAJUSTE 2)</v>
       </c>
       <c r="D140" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2397/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2242/lineage</v>
       </c>
       <c r="E140" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F140" t="str">
-        <v>Campo Calculado</v>
+        <v>% Calculado; % Concedido; :Measure Names; Centro de lucro; Cliente; Direção1; Fat. média 3 meses da data fim; Fator; Mês, Ano de Data Base1; Mês, Ano de Data fim processo; Mês, Ano de Data inicio do processo; Mês, Dia, Ano de Data reajuste retroativo mes; Nome; Período1; Processo; Reajuste calculado mês; Reajuste calculado YTD; Reajuste concedido mês; Reajuste concedido YTD; Regional; Segmento1; Serviço; Sheet 1 (Count); Situação do processo1; Tipo reajuste1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Resultado financeiro</v>
+        <v>Livro1</v>
       </c>
       <c r="B141" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro/10-UOPMetaFixa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Livro1_17625386860670/Painel1</v>
       </c>
       <c r="C141" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_MetaFixa (2)</v>
+        <v>BICompras - Compras Mensal</v>
       </c>
       <c r="D141" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2397/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
       </c>
       <c r="E141" t="str">
-        <v/>
-      </c>
-      <c r="F141" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Análise de resultado por Estado</v>
+        <v>Painel de ICMS - RS</v>
       </c>
       <c r="B142" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisederesultadoRS/AnlisedeResultadoporEstado</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeICMS-RS/ICMS-RS</v>
       </c>
       <c r="C142" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v>BIVarredura - XML NF Item</v>
       </c>
       <c r="D142" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
       </c>
       <c r="E142" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO</v>
-      </c>
-      <c r="F142" t="str">
-        <v>Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Análise de resultado por Estado</v>
+        <v>XMLs Emitidos mês</v>
       </c>
       <c r="B143" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisederesultadoRS/AnlisedeResultadoporEstado</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosms/Painel1</v>
       </c>
       <c r="C143" t="str">
-        <v>Centro_Lucro; Contabil</v>
+        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
       </c>
       <c r="D143" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
       </c>
       <c r="E143" t="str">
-        <v/>
-      </c>
-      <c r="F143" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Análise de resultado - Mapa gestor</v>
+        <v>Análise Prévia Consumo Janeiro 2025</v>
       </c>
       <c r="B144" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapagestor/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
       </c>
       <c r="C144" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
+        <v/>
       </c>
       <c r="D144" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
       </c>
       <c r="E144" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F144" t="str">
-        <v>Campo Calculado</v>
+        <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Análise de resultado - Mapa gestor</v>
+        <v>Notas Oper Não Realizada e Manif Manual</v>
       </c>
       <c r="B145" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-Mapagestor/Anlisedefaturamento-mapa</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/NotasOperNoRealizadaeManifManual/OutrasManifestaes</v>
       </c>
       <c r="C145" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
+        <v/>
       </c>
       <c r="D145" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
+        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
       </c>
       <c r="E145" t="str">
         <v/>
-      </c>
-      <c r="F145" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Relatorio de Quantidade</v>
+        <v>ADH04 - Rateio Custos Ecolab Duque</v>
       </c>
       <c r="B146" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade/AnliseQuantidade</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ADH04-RateioCustosEcolabDuque/ADH4-RateioCustosEcolabMaca</v>
       </c>
       <c r="C146" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
+        <v>BICompras - Compras Mensal</v>
       </c>
       <c r="D146" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
       </c>
       <c r="E146" t="str">
-        <v/>
-      </c>
-      <c r="F146" t="str">
-        <v>Campo Calculado</v>
+        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Relatorio de Quantidade</v>
+        <v>Painel XML informação XPED</v>
       </c>
       <c r="B147" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade/AnliseQuantidade</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED/1-PainelNFSXPED</v>
       </c>
       <c r="C147" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
+        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
       </c>
       <c r="D147" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
       </c>
       <c r="E147" t="str">
-        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
-      </c>
-      <c r="F147" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Mascara 20 NL; Cd pessoal NL; CNPJ Fornecedor NL; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Retenção FY26</v>
+        <v>Resultado financeiro - conta a conta por cl</v>
       </c>
       <c r="B148" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY26/KPIRetenoClientes</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-contaacontaporcl/9-ContaacontaSAP</v>
       </c>
       <c r="C148" t="str">
-        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
+        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
       </c>
       <c r="D148" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2349/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2452/lineage</v>
       </c>
       <c r="E148" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Diretoria; F6; FAT Dir LY; FY24 (Count); GP Dir LY; Regional; Segmento; % Retenção FY24; % total target; Data; Desvio; MF; Planilha3 (Count); Portfólio; Real; Tipo; % GM OR; % GM Site perdidos; % GM vendas; Cálculo1; FAT OR FY25; Fat perda anual; FAT YTD FY25; Faturamento; GP; GP OR FY25; GP perda anual; GP YTD FY25; Período; Planilha1 (Count); Retenção Faturamento; Retenção Faturamento (cópia); Retenção GP; Taxa de conversão; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP Anualizado; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Perda anualizada; Period; Reason for losing1; Regional1; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; Tipo1; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target; Target %; Target valor</v>
-      </c>
-      <c r="F148" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Retenção FY26</v>
+        <v>XMLs Emitidos mês Ju</v>
       </c>
       <c r="B149" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY26/KPIRetenoClientes</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosmsJu/Painel1</v>
       </c>
       <c r="C149" t="str">
-        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
+        <v/>
       </c>
       <c r="D149" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2349/lineage</v>
+        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
       </c>
       <c r="E149" t="str">
         <v/>
-      </c>
-      <c r="F149" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ADH14 - CD PAP PFP</v>
+        <v>Painel para Lançamento de NFe - Ativo com NitemPed</v>
       </c>
       <c r="B150" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH14-CDPAPPFP/ADH14-CDPAPPFP</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe-AtivocomNitemPed/PainelLanamentodeNFe-Ativo</v>
       </c>
       <c r="C150" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
       </c>
       <c r="D150" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
       </c>
       <c r="E150" t="str">
-        <v/>
-      </c>
-      <c r="F150" t="str">
-        <v>Campo Calculado</v>
+        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ADH14 - CD PAP PFP</v>
+        <v>Extração XML Outras Operações</v>
       </c>
       <c r="B151" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH14-CDPAPPFP/ADH14-CDPAPPFP</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLOutrasOperaes/Painel1</v>
       </c>
       <c r="C151" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v>BIVarredura - Docs Simples Remessa</v>
       </c>
       <c r="D151" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/11972/lineage</v>
       </c>
       <c r="E151" t="str">
-        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
-      </c>
-      <c r="F151" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Cd Chave Nfe; Cd Flagnfe; Cd Serie; Cd Status Manifestacao; Cfop; Chaves Referenciada; Cnpj Unidade; Dados migrados (Count); Dsc Empresa Unidade; Dsc Flagnfe; Dsc Status Manifestacao; Dt Emissao; Dth Inclusao; FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento; Ind Proc Devolução; Nro Modelo; Nro Notafiscal; Number of Records</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FISCAL04 - Painel Gestão do Manifesto</v>
+        <v>Integração RNF</v>
       </c>
       <c r="B152" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto/Painel-GestodoManifesto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/IntegraoRNF/Painel1</v>
       </c>
       <c r="C152" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
+        <v>BIVARREDURA - Notas Fora</v>
       </c>
       <c r="D152" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/162/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
       </c>
       <c r="E152" t="str">
-        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CFOP_VENDA; Chave NFe; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE; Dt Abertura; Dt Ano Mes; Dt Carga; XMLI_COD_CFOP; XMLI_DES_CHAVE_NFE</v>
-      </c>
-      <c r="F152" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Serie Nota Fiscal; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Nl; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cnpj Fornecedor Nl; Cod Empresa; DES_CHAVE_NFE; Dias Excedentes; Diretoria; Dsc Flagnfe; Dt Abertura; Dt Carga; Dt Competencia; Dt Emissao Nota Fiscal; Dt Encerramento; Dt Importacao Rnf; Dt Lancamento Nota Fiscal; Dt Processamento Rnf; Dt Rnf; F_NOTAS_FORA (Count); Fili Email; Filial</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>FISCAL04 - Painel Gestão do Manifesto</v>
+        <v>Painel XML informação XPED-Indicadores</v>
       </c>
       <c r="B153" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto/Painel-GestodoManifesto</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED-Indicadores/BaseIndicadoresXped_Nitem</v>
       </c>
       <c r="C153" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
+        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
       </c>
       <c r="D153" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/162/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
       </c>
       <c r="E153" t="str">
-        <v/>
-      </c>
-      <c r="F153" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Mascara 20 NL; Cd pessoal NL; CNPJ Fornecedor NL; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Extração XML para Importação Mastersaf AM_DF</v>
+        <v>Painel Conciliação RNF NL vs SAP</v>
       </c>
       <c r="B154" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAM_DF/PainelXMLMastersafAM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelConciliaoRNFNLvsSAP/ConciliaoRNFNLvsSAP</v>
       </c>
       <c r="C154" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>BIVARREDURA - Notas Fora</v>
       </c>
       <c r="D154" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
       </c>
       <c r="E154" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
-      </c>
-      <c r="F154" t="str">
-        <v>Campo Calculado</v>
+        <v>:Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Serie Nota Fiscal; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Nl; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cnpj Fornecedor Nl; Cod Empresa; DES_CHAVE_NFE; Dias Excedentes; Diretoria; Dsc Flagnfe; Dt Abertura; Dt Carga; Dt Competencia; Dt Emissao Nota Fiscal; Dt Encerramento; Dt Importacao Rnf; Dt Lancamento Nota Fiscal; Dt Processamento Rnf; Dt Rnf; F_NOTAS_FORA (Count); Fili Email; Filial</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Extração XML para Importação Mastersaf AM_DF</v>
+        <v>Campanha de incentivo GU Q1 FY26</v>
       </c>
       <c r="B155" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafAM_DF/PainelXMLMastersafAM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
       </c>
       <c r="C155" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
       </c>
       <c r="D155" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
       </c>
       <c r="E155" t="str">
-        <v/>
-      </c>
-      <c r="F155" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Extração XML para Importação Mastersaf UF MG</v>
+        <v>Conferência_FM</v>
       </c>
       <c r="B156" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafUFMG/PainelXMLMastersafMG</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_FM/ConfernciaFM</v>
       </c>
       <c r="C156" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>NL.TXT+ (Múltiplas conexões)</v>
       </c>
       <c r="D156" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1765/lineage</v>
       </c>
       <c r="E156" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Flagnfe; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
-      </c>
-      <c r="F156" t="str">
-        <v>Campo Calculado</v>
+        <v>0; Ação (CC,Mun. Emitente); Aliq INSS; Aliq IRF; Aliq ISS; Aliq PIS; AlIq. CSLL; AliqCOFINS; Área De Hierarquia; Cálculo1; CC; Centro; Centro de Lucro; CL; CL de Mandato.; CL Mandato; CL NL; CL NL TESTE; Cliente; CNPJ Cli; CNPJ Emit.; CNPJ FIL.; Cod. Cliente; Código Material; Cofins; COFINS Ret; CSLL Ret; Data Comp; Data de lançamento; Data do faturamento; Descrição; Descrição Material; Descrição NCM; Descripção do area de hierarquia standar; DIF 0; Diferença; Doc Contábil; Doc.Comp.; DocFat.; Documento de vendas</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Extração XML para Importação Mastersaf UF MG</v>
+        <v>Painel de ST - MG</v>
       </c>
       <c r="B157" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLparaImportaoMastersafUFMG/PainelXMLMastersafMG</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeST-MG/ST-MG</v>
       </c>
       <c r="C157" t="str">
-        <v>BIVarredura - XML NF Item; BIVARREDURA - XML SEFAZ</v>
+        <v>BIVarredura - XML NF Item</v>
       </c>
       <c r="D157" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
       </c>
       <c r="E157" t="str">
-        <v/>
-      </c>
-      <c r="F157" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>O2C01 - Faturamento e Provisão</v>
+        <v>FI01 - Mapa Fiscal - Extração - V4</v>
       </c>
       <c r="B158" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/O2C01-FaturamentoeProviso/O2CEstratgico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V4/Painel-MapaFiscalporUF</v>
       </c>
       <c r="C158" t="str">
-        <v>BICSCFINANCAS - DSO; BICSCFINANCAS - Faturamento e Provisão</v>
+        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
       </c>
       <c r="D158" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52506/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48321/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/424/lineage</v>
       </c>
       <c r="E158" t="str">
-        <v>% DSO Atual vs DSO Ant; Ano Fiscal Competência; Ano Fiscal Parâmetro; CC: Filtro Ano Fiscal; Consulta do SQL personalizado (Count); Cor Ano Fiscal; Dt Competência (texto); DT_COMPETENCIA; Filtro Últimos 12 meses; Gauge DSO Atual vs DSO Ant; Texto DSO Atual vs DSO Ant; Vl DSO; Vl DSO (eixo); Vl DSO Ant; Vl DSO Atual; VL_DSO; VL_META; % Fat------------------; % Fat Atual vs Fat Ant; % Faturamento; % Inad Atual vs Inad Ant; % Ind; % Ind (cópia); % Prov---------------; % Prov Atual DD vs Prov Ant DD; % Prov Atual vs Prov Ant; % Provisão; % Valor a vista-------------------; % VV Atual vs VV Ant; *% Grafico 4; *Campo Negativo; *Campo Negativo %; *Campo Negativo Seta; *Campo Negativo Seta (cópia); *Campo Positivo; *Campo Positivo %; *Campo Positivo Seta; *Campo Positivo Seta (cópia); *Cor VV Atual x Ant; *Data_Atualizada; *Data_Atualizada (copy); *Data_Atualizada Para o paramentro filtro mes ano; *Data_Hora; *Dif %; *Dif % Inadiplentes; *Login; *Texto VV Atual x Ant; *Usuário; :Measure Names; 1; Ano fiscal; Cálculo1; Cálculo3; CD_BUSINESS_UNIT; CD_DIRETORIA</v>
-      </c>
-      <c r="F158" t="str">
-        <v>Campo Calculado</v>
+        <v>Aliquotadifal; Aliquotadiferenca; Aliquotainterna; Aliquotaorigem; Basedecalculo; Cd Filial; Cnpjremetente; Dados migrados (Count); Dtcompetencia; Dtlancamento; Ieremetente; Impostocreditado; Isentas; Nronf; Number of Records; Outras; Percaliqinterestadual; Percaliqinterna; Percdiferencialaliquota; Serie; Sk Aliquotauf Od; Sk Aliquotauf Od (D Aliquotauf Od); Sk Filial; Uf Destino; Uf Origem; Uf Origemdestino; Uffilial; Ufremetente; Valorcontabil; Valordiferencialaliquota; VL Difal; Vlraliqinterest; Vlraliqinterna; Cargauf; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial (Vw D Filial); Cd Filial Ficticia; Cd Lancamento; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Uf (Vw D Filial); Cfop; Cnpjdestinatario; Conta Contabil; Creditoentradas; Dt Abertura; Dt Ano Mes; Dt Carga; Dt Carga (Vw D Tempo); Dt Encerramento; Dtcompetencia filtra ate jan21; Filial; FILIAL UF; Centrodelucro; Competencia; SK_FILIAL; VALOR_CALCULO; VL Outros Créditos; VL OutrosCreditos Calculo; Cd Contacontabil; Chavelancamento; Conta Contabil (grupo); Contacontabil; Dt Carga (Vw D Filial); Estornocom; Fl Ficticia; Hierarquia; Inscricaoestadual; Locnegocios; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Contacontabil; Nm Diretor Operacional; Nm Diretoria</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>O2C01 - Faturamento e Provisão</v>
+        <v>Painel ICMS ST SP V3</v>
       </c>
       <c r="B159" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/O2C01-FaturamentoeProviso/O2CEstratgico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/PainelICMSSTSPV3/PainelICMSSTSP</v>
       </c>
       <c r="C159" t="str">
-        <v>BICSCFINANCAS - DSO; BICSCFINANCAS - Faturamento e Provisão</v>
+        <v>BIVarredura - XML NF Item; Tabela NCM credito ST SP</v>
       </c>
       <c r="D159" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/52506/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48321/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1666/lineage</v>
       </c>
       <c r="E159" t="str">
-        <v/>
-      </c>
-      <c r="F159" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Descrição; NCM; NCM editado; Relacionamento NCM; Tabela NCM credito ST SP.csv (Count)</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>R2R01 - Indicadores Estratégicos</v>
+        <v>Retenção FY24</v>
       </c>
       <c r="B160" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/R2R01-IndicadoresEstratgicos_16958287260440/R2REstratgico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Reteno/RetenoFY24</v>
       </c>
       <c r="C160" t="str">
-        <v>BICSCFINANCAS - Base R2R</v>
+        <v>Centro_Lucro; Contabil; Planilha1 (Target diretoria); Retention; Sheet1 (Target Segmento)</v>
       </c>
       <c r="D160" t="str">
-        <v>Planilha ou fonte sem Custom SQL Query identificavel</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1209/lineage</v>
       </c>
       <c r="E160" t="str">
-        <v>*Ano; *Campo Positivo; *Campo Positivo Imagem ETR; *Campo Positivo Imagem ROA; *CampoNegativo; *CampoNegativo Imagems ETR; *CampoNegativo Imagems ROA; *Cor; *Cor ETR; *Cor méd 1,0; *Data Atualização; *Data_Hora; *Dif%; *Dif% (cópia); *Login_Usuario; *Usuario; Base R2R (Count); Cálculo; Cálculo1; Descrição; Empresa; Mês/Ano; Mês/Ano (MAX); MIN(0); MIN(0) (1); MIN(0) (cópia 2); MIN(0) (cópia); Path; Periodicidade; Período; Periodo 12 meses; Periodo 3 meses; Sheet; ToolTip; Unidade; Valor; Valor (eixo negativo); Valor (eixo positivo); Valor ETR; Valores</v>
-      </c>
-      <c r="F160" t="str">
-        <v>Campo Calculado</v>
+        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; %; % Retenção FY24; % total target; Diretoria; Planilha1 (Count); Target; Valor; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Period1; Reason for losing1; Regional; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target %; Target valor</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>R2R01 - Indicadores Estratégicos</v>
+        <v>FISCAL12 - XML Extração ICMS</v>
       </c>
       <c r="B161" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/R2R01-IndicadoresEstratgicos_16958287260440/R2REstratgico</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL12-XMLExtraoICMS/PainelXMLExtraoICMS</v>
       </c>
       <c r="C161" t="str">
-        <v>BICSCFINANCAS - Base R2R</v>
+        <v>BIVARREDURA - XML EXTRAÇÃO ICMS</v>
       </c>
       <c r="D161" t="str">
-        <v>Planilha ou fonte sem Custom SQL Query identificavel</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1837/lineage</v>
       </c>
       <c r="E161" t="str">
-        <v/>
-      </c>
-      <c r="F161" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>COD_CHAVE_NFE; index; NE_COD_UNIDADE; NE_DTA_RECEBIMENTO; NE_OPERACAO; VLR_VICMSST; XML (Count); XML_CNPJ_DESTINATARIO; XML_CNPJ_FORNECEDOR; XML_DTEMISSAO; XML_IE_DESTINATARIO; XML_NMFORNECEDOR; XML_NRONOTAFISCAL; XML_NROSERIE; XML_OBSERVACAO_ADICIONAL; XML_UF_DESTINATARIO; XML_VL_PRODUTOS; XMLI_COD_CFOP; XMLI_COD_CST; XMLI_COD_CST_COFINSALIQ; XMLI_COD_CST_PISALIQ; XMLI_COD_ITEM; XMLI_COD_NCM; XMLI_DES_ITEM; XMLI_NUM_ITEM; XMLI_VLR_ICMS; XMLI_VLR_TOTAL; XMLI_VLR_VCOFINS_COFINSALIQ; XMLI_VLR_VPIS_PISALIQ</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>MDM01 - MDM Estratégicos</v>
+        <v>FISCAL01 - Painel de Erro Rotina de Envio Ciência Automática</v>
       </c>
       <c r="B162" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MDM01-MDMEstratgicos/MateriaiseFornecedores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL01-PaineldeErroRotinadeEnvioCinciaAutomtica/CheckErro-RotinadeEnviodeCinciaAutomtica</v>
       </c>
       <c r="C162" t="str">
-        <v>BICSCFINANCAS - Base MDM</v>
+        <v>Varredura - XML NF Header</v>
       </c>
       <c r="D162" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/43041/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
       </c>
       <c r="E162" t="str">
-        <v>Custom SQL Query (Count); DSC_SEGMENTO_TIPO; DSC_TIPO; DT_COMPETENCIA; Dt_competencia (Max); DT_COMPETENCIA 1; Filtro 12 meses; Filtro máx mês; FY; Período; Período FY; QTD; Qtd abrev.; Qtd Mês Atual; Qtd Total (Fixed); TP_METRICA</v>
-      </c>
-      <c r="F162" t="str">
-        <v>Campo Calculado</v>
+        <v>Status XML; :Measure Names; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Mascara 20 NL; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd pessoal NL; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; CNPJ Fornecedor NL; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>MDM01 - MDM Estratégicos</v>
+        <v>Conciliação ISS Serviços Tomados</v>
       </c>
       <c r="B163" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MDM01-MDMEstratgicos/MateriaiseFornecedores</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/ConciliaoISSServiosTomados/ISSServTomados</v>
       </c>
       <c r="C163" t="str">
-        <v>BICSCFINANCAS - Base MDM</v>
+        <v>PREFEITURA++ (Múltiplas conexões)</v>
       </c>
       <c r="D163" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/43041/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E163" t="str">
-        <v/>
-      </c>
-      <c r="F163" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>:Measure Names; Alíquota; Aliquota ISS; Bairro do Prestador; Bairro do Tomador; Centro; Centro Custo; CEP do Prestador; CEP do Tomador; Cidade Centro; Cidade do Prestador; Cidade do Tomador; Cidade Filial; Cidade Recolhimento; CNPJ Centro; CNPJ do Prestador; CNPJ Filial; COD SERV SAP; Cod. Fornecedor; Código Imposto; Complemento do Endereço do Prestador; Complemento do Endereço do Tomador; CPF/CNPJ do Tomador; Data de Cancelamento; Data de Quitação da Guia Vinculada a Nota Fiscal; Data Hora NFE; Data SAP; Desc. Conta Despesa; Descrição do Material; Descrição NCM; Discriminação dos Serviços; Doc. Contabil; Doc. Estorno; Doc. Fiscal; Domicílio Centro; Domicílio Filial; Domicílio Recolhimento; Dt. Documento; Dt. Pagamento; Email do Prestador</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Bonificação Coca</v>
+        <v>Indicadores - ISS Próprio</v>
       </c>
       <c r="B164" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BonificaoCoca/ReteioCoca</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadores-ISSPrprio/Indicadores-ISSPrprio</v>
       </c>
       <c r="C164" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v>Base_original (indicadores V2)</v>
       </c>
       <c r="D164" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
       </c>
       <c r="E164" t="str">
-        <v/>
-      </c>
-      <c r="F164" t="str">
-        <v>Campo Calculado</v>
+        <v>Base_original (Count); CL; Erro; Mês; Município; Observação; Serviço; Tipo</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Bonificação Coca</v>
+        <v>Notas emitidas x lançadas BRF e Ecolab</v>
       </c>
       <c r="B165" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BonificaoCoca/ReteioCoca</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/NotasemitidasxlanadasBRFeEcolab/PainelNF</v>
       </c>
       <c r="C165" t="str">
-        <v>BICompras - Compras Mensal</v>
+        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
       </c>
       <c r="D165" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
+        <v>Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
       </c>
       <c r="E165" t="str">
-        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
-      </c>
-      <c r="F165" t="str">
-        <v>Nao e Campo Calculado</v>
+        <v>Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Grafico Familias</v>
+        <v>FISCAL04 - Painel Gestão do Manifesto - Filtro por Data Emissão</v>
       </c>
       <c r="B166" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TabGraficoFamilias/InflaoRTM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto-FiltroporDataEmisso/Painel-GestodoManifesto</v>
       </c>
       <c r="C166" t="str">
-        <v>Planilha1 (TesteTableau)</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
       </c>
       <c r="D166" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2232/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/299/lineage</v>
       </c>
       <c r="E166" t="str">
-        <v/>
-      </c>
-      <c r="F166" t="str">
-        <v>Campo Calculado</v>
+        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CFOP_VENDA; Chave NFe; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE; Dt Abertura; Dt Ano Mes; Dt Carga; XMLI_COD_CFOP; XMLI_DES_CHAVE_NFE</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Grafico Familias</v>
+        <v>FISCAL07 - Painel Gestão de Fornecedores</v>
       </c>
       <c r="B167" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TabGraficoFamilias/InflaoRTM</v>
+        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL07-PainelGestodeFornecedores/Painel-GestodeFornecedores</v>
       </c>
       <c r="C167" t="str">
-        <v>Planilha1 (TesteTableau)</v>
+        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
       </c>
       <c r="D167" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2232/lineage</v>
+        <v>https://analyticsbi.sodexo.com.br/#/workbooks/289/lineage</v>
       </c>
       <c r="E167" t="str">
-        <v>Família; Inflação MoM; Inflação RTM; Inflação YoY; Inflação YTD; Mês; Planilha1 (Count); Segmento; Visão</v>
-      </c>
-      <c r="F167" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>Base ordem de compras</v>
-      </c>
-      <c r="B168" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831929220/Baseordemdecompras</v>
-      </c>
-      <c r="C168" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
-      </c>
-      <c r="D168" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
-      </c>
-      <c r="E168" t="str">
-        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
-      </c>
-      <c r="F168" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>Base ordem de compras</v>
-      </c>
-      <c r="B169" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831929220/Baseordemdecompras</v>
-      </c>
-      <c r="C169" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
-      </c>
-      <c r="D169" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
-      </c>
-      <c r="E169" t="str">
-        <v/>
-      </c>
-      <c r="F169" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>Retenção FY25</v>
-      </c>
-      <c r="B170" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY25/KPIReteno</v>
-      </c>
-      <c r="C170" t="str">
-        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
-      </c>
-      <c r="D170" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1790/lineage</v>
-      </c>
-      <c r="E170" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; Diretoria; F6; FAT Dir LY; FY24 (Count); GP Dir LY; Regional; Segmento; % Retenção FY24; % total target; Data; Desvio; MF; Planilha3 (Count); Portfólio; Real; Tipo; % GM OR; % GM Site perdidos; % GM vendas; Cálculo1; FAT OR FY25; Fat perda anual; FAT YTD FY25; Faturamento; GP; GP OR FY25; GP perda anual; GP YTD FY25; Período; Planilha1 (Count); Retenção Faturamento; Retenção Faturamento (cópia); Retenção GP; Taxa de conversão; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Period1; Reason for losing1; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target; Target %; Target valor</v>
-      </c>
-      <c r="F170" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>Retenção FY25</v>
-      </c>
-      <c r="B171" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RetenoFY25/KPIReteno</v>
-      </c>
-      <c r="C171" t="str">
-        <v>Centro_Lucro; Contabil; Fonte de dados sem título; Meta fixa; Planilha1 (LY Retenção); Retention; Sheet1 (Target Segmento)</v>
-      </c>
-      <c r="D171" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1790/lineage</v>
-      </c>
-      <c r="E171" t="str">
-        <v/>
-      </c>
-      <c r="F171" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>P2P02 - P2P T&amp;E Despesas</v>
-      </c>
-      <c r="B172" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/P2P02-P2PTEDespesas_17574268903820/VisoGeral</v>
-      </c>
-      <c r="C172" t="str">
-        <v>BICSCFINANCAS - P2P TAE DESPESAS; BICSCFINANCAS - P2P TAE DESPESAS (local copy)</v>
-      </c>
-      <c r="D172" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/4948/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2241/lineage</v>
-      </c>
-      <c r="E172" t="str">
-        <v>:Measure Names; Dsc Conta; Dsc Conta (copy); Dsc Politica; Dsc Politica (cor 2); Dsc Politica (cor 3); Dsc Servico; Dt Competencia; Dt Competencia (máx); Filtro Data Competência; FY; Gauge tabela; Hoje(); Max. Dt Competência; Nm Segmento; NR_DIARIAS; Per N Viagens; Per Viagens; Período; Ticket médio; Ticket médio (hosp.); Ticket médio Ajustado; Ticket médio Ajustado (hosp.); Ticket Médio Ajustado (rótulo) (cópia); Últimos 12 meses; Últimos 3 meses; Vl Quantidade; Vl Quantidade Ajustado; Vl Quantidade Ajustado (rótulo); Vl Target Dif; Vl Tarifa; Vl Total; Vl Total Ajustado; Vl Total Ajustado (rótulo); VL_N_VIAGEM; Vl_quantidade_relacionados_a_viagens; Vl_total_contas_relacionados_a_viagens; VL_VIAGEM; VW_F_P2P_TAE_INDICADORES_ESTRA (Count)</v>
-      </c>
-      <c r="F172" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>P2P02 - P2P T&amp;E Despesas</v>
-      </c>
-      <c r="B173" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/P2P02-P2PTEDespesas_17574268903820/VisoGeral</v>
-      </c>
-      <c r="C173" t="str">
-        <v>BICSCFINANCAS - P2P TAE DESPESAS; BICSCFINANCAS - P2P TAE DESPESAS (local copy)</v>
-      </c>
-      <c r="D173" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/4948/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2241/lineage</v>
-      </c>
-      <c r="E173" t="str">
-        <v/>
-      </c>
-      <c r="F173" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>Análise PROVISÃO NF</v>
-      </c>
-      <c r="B174" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF_17661662030420/Provisodenotasfora</v>
-      </c>
-      <c r="C174" t="str">
-        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
-      </c>
-      <c r="D174" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2431/lineage</v>
-      </c>
-      <c r="E174" t="str">
-        <v>Cd Business Unit; Cd Cardapio; Cd Centro Lucro; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Grupoeconomico; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Nota Item Ordem Compra; Cd Produto; Cd Produto (Vw Mdt Produto); Cd Regional; Cd Segmento; Cd Site; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; CD_FORNECEDOR (Consulta do SQL personalizado); CD_ITEM_RECEITA_NL; Ch Documento; CH_DOCUMENTO (Consulta do SQL personalizado); Ctl Dt Check Encerrado; Ctl Dt Encerramento 92Dias; Ctl Dt Encerramento Sap D4; Ctl Dt Encerramento Su; Ctl Dt Encerramento Termo; Ctl Dt Notificacao; DSC_ITEM_RECEITA_NL; Dt Abertura; Dt Carga (Vw Mdt Centro Lucro); Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Centro Custo; Cd Tipoprocesso; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; Chave NF; CL Provisão; Planilha1 (Count); Chave NFe; Chave NFe2; CL; CNPJ Fornecedor; Conta; Conta concat; Data atual; Data de reversão; Data de reversão (grupo); Data provisão; Data reversão 2; Dias vencimento; Diferença dias; Emissão NF; Fornecedor; Lançamento provisão; Nº Nf; Origem Da Identificação; Provisão; Provisão (grupo); Provisão (grupo) 1; Provisão Notas fora (Count); Reversão; Série; Status; Tipo; Tipo (grupo); Valor NF</v>
-      </c>
-      <c r="F174" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>Análise PROVISÃO NF</v>
-      </c>
-      <c r="B175" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePROVISONF_17661662030420/Provisodenotasfora</v>
-      </c>
-      <c r="C175" t="str">
-        <v>BISILVER - Finance - Nota Fiscal Recebimento; BIVarredura - XML NF Supply; Centro_Lucro; Planilha1 (Chave); Provisão Notas fora (Base Tableau NF)</v>
-      </c>
-      <c r="D175" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48338/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2431/lineage</v>
-      </c>
-      <c r="E175" t="str">
-        <v/>
-      </c>
-      <c r="F175" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>Calculo ICMS Antecipado Arroz MG V2</v>
-      </c>
-      <c r="B176" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CalculoICMSAntecipadoArrozMGV2/AntecipadoArroz</v>
-      </c>
-      <c r="C176" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D176" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E176" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
-      </c>
-      <c r="F176" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>Calculo ICMS Antecipado Arroz MG V2</v>
-      </c>
-      <c r="B177" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CalculoICMSAntecipadoArrozMGV2/AntecipadoArroz</v>
-      </c>
-      <c r="C177" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D177" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E177" t="str">
-        <v/>
-      </c>
-      <c r="F177" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>Dashboard Aéreo</v>
-      </c>
-      <c r="B178" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DashboardAreo/PainelPrincipal</v>
-      </c>
-      <c r="C178" t="str">
-        <v>Painel Aéreo</v>
-      </c>
-      <c r="D178" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2519/lineage</v>
-      </c>
-      <c r="E178" t="str">
-        <v>Adesão; Ano Fiscal; Ano Fiscal Faturamento; Antecedencia; Antecedencia (compartimento); Antecedência Ajustada; Antecedência R; Aprovador1; Atributo; Autorização; Bases (Count); Bilhete; Business Unit; Business Unit (Tabela1); Cálculo1; Cambio; Central de Compras; Central de Compras (Tabela1); Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); Chave de lançamento; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); Cidade Destino; Cidade Origem; Cidade Origem x Cidade Destino; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Cod Classe; Código Centro de Custo; Código de Autorização; Código Reason Code; Conjunto Responsável; Conta do Razão; D/C; Data abertura revisada; Data abertura revisada (Tabela1); Data de lançamento; Data do documento</v>
-      </c>
-      <c r="F178" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>Dashboard Aéreo</v>
-      </c>
-      <c r="B179" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/DashboardAreo/PainelPrincipal</v>
-      </c>
-      <c r="C179" t="str">
-        <v>Painel Aéreo</v>
-      </c>
-      <c r="D179" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2519/lineage</v>
-      </c>
-      <c r="E179" t="str">
-        <v/>
-      </c>
-      <c r="F179" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>Organic Growth YTD</v>
-      </c>
-      <c r="B180" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowthYTD/OGYTDJunho21</v>
-      </c>
-      <c r="C180" t="str">
-        <v>Contabil_FY20 OG; Contabil_MetaFixa OG FY21</v>
-      </c>
-      <c r="D180" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E180" t="str">
-        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
-      </c>
-      <c r="F180" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>Organic Growth YTD</v>
-      </c>
-      <c r="B181" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowthYTD/OGYTDJunho21</v>
-      </c>
-      <c r="C181" t="str">
-        <v>Contabil_FY20 OG; Contabil_MetaFixa OG FY21</v>
-      </c>
-      <c r="D181" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E181" t="str">
-        <v/>
-      </c>
-      <c r="F181" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>Labor Efficiency</v>
-      </c>
-      <c r="B182" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiency_17678934428780/ReduesLabor</v>
-      </c>
-      <c r="C182" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha; Planilha1 (HC Budget); Sheet 1 (Labor dezembro)</v>
-      </c>
-      <c r="D182" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2453/lineage</v>
-      </c>
-      <c r="E182" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; CL; HC b; Planilha1 (Count); Desvio Fat/HC; Desvio Pess/HC; Fat OR; Fat RL; Fat/HC; Fat/HC OR; Hc Or; Pess/HC; Pess/HC OR; Pessoal OR; Pessoal RL; Real HC; Reduções; Sheet 1 (Count)</v>
-      </c>
-      <c r="F182" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>Labor Efficiency</v>
-      </c>
-      <c r="B183" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/LaborEfficiency_17678934428780/ReduesLabor</v>
-      </c>
-      <c r="C183" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha; Planilha1 (HC Budget); Sheet 1 (Labor dezembro)</v>
-      </c>
-      <c r="D183" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2453/lineage</v>
-      </c>
-      <c r="E183" t="str">
-        <v/>
-      </c>
-      <c r="F183" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>Campanha de incentivo GU Q1</v>
-      </c>
-      <c r="B184" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
-      </c>
-      <c r="C184" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
-      </c>
-      <c r="D184" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
-      </c>
-      <c r="E184" t="str">
-        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
-      </c>
-      <c r="F184" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>Campanha de incentivo GU Q1</v>
-      </c>
-      <c r="B185" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
-      </c>
-      <c r="C185" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
-      </c>
-      <c r="D185" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
-      </c>
-      <c r="E185" t="str">
-        <v/>
-      </c>
-      <c r="F185" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>NES Oficial vs NES prevista EDU</v>
-      </c>
-      <c r="B186" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NESOficialvsNESprevistaEDU/NESOficial</v>
-      </c>
-      <c r="C186" t="str">
-        <v>BICOMPRAS Corporate - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO Corporate - Faturamento NL NES Item</v>
-      </c>
-      <c r="D186" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2461/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3022/lineage</v>
-      </c>
-      <c r="E186" t="str">
-        <v/>
-      </c>
-      <c r="F186" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>NES Oficial vs NES prevista EDU</v>
-      </c>
-      <c r="B187" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NESOficialvsNESprevistaEDU/NESOficial</v>
-      </c>
-      <c r="C187" t="str">
-        <v>BICOMPRAS Corporate - NES NL Cardapio &amp; Faturamento; BIFATURAMENTO Corporate - Faturamento NL NES Item</v>
-      </c>
-      <c r="D187" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/2461/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3022/lineage</v>
-      </c>
-      <c r="E187" t="str">
-        <v>Cd Agrupamento Nl; Cd Cliente NL; Cd Cliente Sap; Cd Diretoria; Cd Filial; Cd Filial Nl; Cd Item Cardapio; Cd Item Venda; Cd Matriz; Cd Padrao Cardapio; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Status Contrato; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Nes; CD_LISTA_PRECO_VENDA; CD_TIP_PERIODO; Cnpj Cliente; Cód CPR; Código Item Cardápio; Código Item Venda; Cpf Cliente; CPR; Des Status Contrato; Des Tipo Cliente; Dia Fat; Dia Fim Fat; Dia Inicio Fat; DIA_LIMITE_FAT; DIA_VCTO10; DIA_VCTO3; DIA_VCTO4; DIA_VCTO5; DIA_VCTO6; DIA_VCTO7; DIA_VCTO8; DIA_VCTO9; Dsc Agrupamento Nl; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Config Contrato; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Produto Venda; Cd Sistema Origem; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_BUSINESS_UNIT; CD_GRUPOECONOMICO; CD_MASCARA_NL_175; CD_SITE; Cód Completo NL 175</v>
-      </c>
-      <c r="F187" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>Hospedagem</v>
-      </c>
-      <c r="B188" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Hospedagem/PainelPrincipal</v>
-      </c>
-      <c r="C188" t="str">
-        <v>Bases+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D188" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2518/lineage</v>
-      </c>
-      <c r="E188" t="str">
-        <v>[Diárias por OS (uma vez) por mês]; Adesão; Agencia; Ano Fiscal; Ano Fiscal Faturamento; Antecedencia; Aprovador; Atributo; Autorização; Bases (Count); Bilhete; Business Unit; Business Unit (Tabela1); C/D; Calculo 1; Cálculo1; Cálculo2; Cálculo2 (cópia); Cambio; Cancelada Por; Cancelados; Cargo; Categoria PVM; Central de Compras; Central de Compras (Tabela1); Centro de Custo; Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); CEP; Chave de lançamento; Cidade; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); Cidade Destino; Cidade Origem; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Cod Classe; Codigo C Custo Cliente</v>
-      </c>
-      <c r="F188" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Hospedagem</v>
-      </c>
-      <c r="B189" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Hospedagem/PainelPrincipal</v>
-      </c>
-      <c r="C189" t="str">
-        <v>Bases+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D189" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2518/lineage</v>
-      </c>
-      <c r="E189" t="str">
-        <v/>
-      </c>
-      <c r="F189" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Conferência_Food</v>
-      </c>
-      <c r="B190" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_Food/FechamentoFood-Integracao</v>
-      </c>
-      <c r="C190" t="str">
-        <v>NL.TXT+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D190" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E190" t="str">
-        <v>:Measure Names; 0; Acréscimos; AE; Aliq. COFINS; Aliq. ICMS; Aliq. IPI; Aliq. PIS; Ativo Soma; Ativos; Cálculo1; cc; CC NL; CC SAP; CD; Cd filial NL; Cd filial SAP; Centro de Lucro; Cfop; CFOP (Sheet1); CL; CL RNF2; Clie/Fornec; Cliente; CNPJ Dest; Cofins; Ctg. NF; Data da RNF; Data Emissão; Data Lanc; Desc. Clie/Fornec; Descrição Material; DIF TEKNISA; Doc; Doc Fisc Relac; Doc. Contábil; Doc. Fiscal; Empresa; Excluído; Exercício</v>
-      </c>
-      <c r="F190" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Conferência_Food</v>
-      </c>
-      <c r="B191" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_Food/FechamentoFood-Integracao</v>
-      </c>
-      <c r="C191" t="str">
-        <v>NL.TXT+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D191" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E191" t="str">
-        <v/>
-      </c>
-      <c r="F191" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>Painel para Lançamento de NFe</v>
-      </c>
-      <c r="B192" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe/PainelLanamentodeNFe</v>
-      </c>
-      <c r="C192" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
-      </c>
-      <c r="D192" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
-      </c>
-      <c r="E192" t="str">
-        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
-      </c>
-      <c r="F192" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>Painel para Lançamento de NFe</v>
-      </c>
-      <c r="B193" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe/PainelLanamentodeNFe</v>
-      </c>
-      <c r="C193" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
-      </c>
-      <c r="D193" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Análise de resultado - Mapa Portfólio</v>
-      </c>
-      <c r="B194" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaPortflio/Anlisedefaturamento-mapa</v>
-      </c>
-      <c r="C194" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
-      </c>
-      <c r="D194" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E194" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR</v>
-      </c>
-      <c r="F194" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Análise de resultado - Mapa Portfólio</v>
-      </c>
-      <c r="B195" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Anlisederesultado-MapaPortflio/Anlisedefaturamento-mapa</v>
-      </c>
-      <c r="C195" t="str">
-        <v>Centro_Lucro; Contabil; RH - Colaborador Folha</v>
-      </c>
-      <c r="D195" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>TRE01 - TRE Visão Financeira</v>
-      </c>
-      <c r="B196" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TRE01-TREVisoFinanceira/VisoGeral</v>
-      </c>
-      <c r="C196" t="str">
-        <v>BICSCFINANCAS - TRE Estratégicos</v>
-      </c>
-      <c r="D196" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57473/lineage</v>
-      </c>
-      <c r="E196" t="str">
-        <v>[fn] Data atualização; [fn] Usuario; Check TRE; Dsc Indicador; Dsc Periodo; Dsc Source; Dt Ano Fiscal; Dt Carga; Dt Competencia; Dt Competência; Dt Competência (Max); F_CSC_TRE (Count); Filtro Ano Fiscal; Filtro Dt Competência 12 Meses; Filtro Dt Competência 6 Meses; Filtro Dt Competência 6 Meses (Ger. de Caixa); Filtro Dt Competência Mês Anterior; Filtro Dt Competência Mês Atual; Filtro FYTD; lbl DataHora; lbl Usuario; Nm Banco; Vl Met Blc 1 Forecast; Vl Met Blc 1 Receita; Vl Met Blc 1 Receita (tooltip); Vl Met Blc 2 Rendimento CDI; Vl Met Blc 2 Rendimento CDI (tooltip); Vl Met Blc 3 Saldo por Banco; Vl Met Blc 4 Fluxo Operacional; Vl Met Blc 4 Fluxo Operacional (tooltip); Vl Met Blc 4 Saldo de Tesouraria; Vl Met Blc 5 Despesas; Vl Met Blc 5 Despesas (tooltip); Vl Met Blc 6 Fiança e Garantias; Vl Met Blc 6 Fiança e Garantias (tooltip); Vl Metrica; Vl Métrica Mês Anterior; Vl Métrica Mês Atual; Vl Perc Blc 1; Vl Perc Blc 1 Cor</v>
-      </c>
-      <c r="F196" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>TRE01 - TRE Visão Financeira</v>
-      </c>
-      <c r="B197" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/TRE01-TREVisoFinanceira/VisoGeral</v>
-      </c>
-      <c r="C197" t="str">
-        <v>BICSCFINANCAS - TRE Estratégicos</v>
-      </c>
-      <c r="D197" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/57473/lineage</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>PFD100 - VARIAÇÃO DE NES E LANÇAMENTOS (Ajustes Rótulos)</v>
-      </c>
-      <c r="B198" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PFD100-VARIAODENESELANAMENTOSAjustesRtulos_17519186689340/TABELA</v>
-      </c>
-      <c r="C198" t="str">
-        <v/>
-      </c>
-      <c r="D198" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>PFD100 - VARIAÇÃO DE NES E LANÇAMENTOS (Ajustes Rótulos)</v>
-      </c>
-      <c r="B199" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PFD100-VARIAODENESELANAMENTOSAjustesRtulos_17519186689340/TABELA</v>
-      </c>
-      <c r="C199" t="str">
-        <v/>
-      </c>
-      <c r="D199" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Price List FY24_v2</v>
-      </c>
-      <c r="B200" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PriceListFY24_v2/PriceListFY24</v>
-      </c>
-      <c r="C200" t="str">
-        <v/>
-      </c>
-      <c r="D200" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Price List FY24_v2</v>
-      </c>
-      <c r="B201" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PriceListFY24_v2/PriceListFY24</v>
-      </c>
-      <c r="C201" t="str">
-        <v/>
-      </c>
-      <c r="D201" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Resultado financeiro - SG&amp;A Teste budget</v>
-      </c>
-      <c r="B202" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-SGATestebudget/ResultadoSGA</v>
-      </c>
-      <c r="C202" t="str">
-        <v>Centro_Lucro; Contabil (cópia); Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; March_Fcst_v9 (Compactada_FPA_March_Fcst_2025-03-11-v9)</v>
-      </c>
-      <c r="D202" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2359/lineage</v>
-      </c>
-      <c r="E202" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; Budget (Count); Data; Desvio; March Forecast; Nº conta; Numero do CL; Tagetik; Valor; Versão; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F202" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Resultado financeiro - SG&amp;A Teste budget</v>
-      </c>
-      <c r="B203" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-SGATestebudget/ResultadoSGA</v>
-      </c>
-      <c r="C203" t="str">
-        <v>Centro_Lucro; Contabil (cópia); Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; March_Fcst_v9 (Compactada_FPA_March_Fcst_2025-03-11-v9)</v>
-      </c>
-      <c r="D203" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2359/lineage</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Base ordem de compras consumo</v>
-      </c>
-      <c r="B204" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831706610/Baseordemdecompras</v>
-      </c>
-      <c r="C204" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
-      </c>
-      <c r="D204" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
-      </c>
-      <c r="E204" t="str">
-        <v>:Measure Names; Cd Cnpj; CD Produto; Cd Tipo Situacao; Cod CD; Cod Produto Excluir; Codigo Excluir; Dados migrados (Count); Data Competencia Previsão; Data Previsão Entrega; Dsc Tipo Ordem; Dsc Tipo Situacao; FILI_BAIRRO; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILDIROPERACIONAL; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; FILI_CDBUSINESSUNIT; FILI_CDMATRIZCARDAPIO; FILI_EMAILBUSINESSUNIT</v>
-      </c>
-      <c r="F204" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Base ordem de compras consumo</v>
-      </c>
-      <c r="B205" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Baseordemdecompras_16860831706610/Baseordemdecompras</v>
-      </c>
-      <c r="C205" t="str">
-        <v>BICOMPRAS - PONTO A PONTO; PIS/COFINS_Gasto CD</v>
-      </c>
-      <c r="D205" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/3854/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Análise Prévia Consumo Janeiro 2026</v>
-      </c>
-      <c r="B206" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C206" t="str">
-        <v/>
-      </c>
-      <c r="D206" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Análise Prévia Consumo Janeiro 2026</v>
-      </c>
-      <c r="B207" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C207" t="str">
-        <v/>
-      </c>
-      <c r="D207" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Price List_FY24</v>
-      </c>
-      <c r="B208" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PriceList_FY24/PriceListFY24</v>
-      </c>
-      <c r="C208" t="str">
-        <v/>
-      </c>
-      <c r="D208" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Price List_FY24</v>
-      </c>
-      <c r="B209" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PriceList_FY24/PriceListFY24</v>
-      </c>
-      <c r="C209" t="str">
-        <v/>
-      </c>
-      <c r="D209" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Análise Prévia Consumo Média PAP - Janeiro 26</v>
-      </c>
-      <c r="B210" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Janeiro26/Anliseprviaconsumo</v>
-      </c>
-      <c r="C210" t="str">
-        <v/>
-      </c>
-      <c r="D210" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E210" t="str">
-        <v/>
-      </c>
-      <c r="F210" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Análise Prévia Consumo Média PAP - Janeiro 26</v>
-      </c>
-      <c r="B211" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Janeiro26/Anliseprviaconsumo</v>
-      </c>
-      <c r="C211" t="str">
-        <v/>
-      </c>
-      <c r="D211" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E211" t="str">
-        <v/>
-      </c>
-      <c r="F211" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Mobilidade</v>
-      </c>
-      <c r="B212" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Mobilidade/PainelPrincipal</v>
-      </c>
-      <c r="C212" t="str">
-        <v>Bases (Mobilidade)</v>
-      </c>
-      <c r="D212" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2517/lineage</v>
-      </c>
-      <c r="E212" t="str">
-        <v>Ano; Ano Fiscal; Ano Fiscal Faturamento; Atributo; Autorização; Bases (Count); BU; Business Unit; Business Unit (Tabela1); Cargo; Cargo Superior; CCusto Superior; Central de Compras; Central de Compras (Tabela1); Centro de lucro; Centro de lucro (Sheet1); Centro de lucro (Tabela1); Centro de Lucro F; Chave de lançamento; Cidade (End.Entrega); Cidade (End.Entrega) (Tabela1); CL; CNPJ Centralizador; CNPJ Centralizador (Tabela1); Colaborador; Conta do Razão; Data abertura revisada; Data abertura revisada (Tabela1); Data de lançamento; Data do documento; Destino; Diretoria; Diretoria (Tabela1); E-mail; E-mail (Bases); E-mail RYDOO; Email Superior; Empresa; Empresa (Sheet1); Empresa (Tabela1)</v>
-      </c>
-      <c r="F212" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Mobilidade</v>
-      </c>
-      <c r="B213" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Mobilidade/PainelPrincipal</v>
-      </c>
-      <c r="C213" t="str">
-        <v>Bases (Mobilidade)</v>
-      </c>
-      <c r="D213" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2517/lineage</v>
-      </c>
-      <c r="E213" t="str">
-        <v/>
-      </c>
-      <c r="F213" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Contratos Data Limite Faturamento - Serviço</v>
-      </c>
-      <c r="B214" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosDataLimiteFaturamento-Servio/ContratosDataLimite</v>
-      </c>
-      <c r="C214" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
-      </c>
-      <c r="D214" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
-      </c>
-      <c r="E214" t="str">
-        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento</v>
-      </c>
-      <c r="F214" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Contratos Data Limite Faturamento - Serviço</v>
-      </c>
-      <c r="B215" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosDataLimiteFaturamento-Servio/ContratosDataLimite</v>
-      </c>
-      <c r="C215" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
-      </c>
-      <c r="D215" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
-      </c>
-      <c r="E215" t="str">
-        <v/>
-      </c>
-      <c r="F215" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Extração de XML por UF com Impostos</v>
-      </c>
-      <c r="B216" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraodeXMLporUFcomImpostos/ExtraodeXMLporUFcomImpostos</v>
-      </c>
-      <c r="C216" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D216" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E216" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
-      </c>
-      <c r="F216" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Extração de XML por UF com Impostos</v>
-      </c>
-      <c r="B217" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraodeXMLporUFcomImpostos/ExtraodeXMLporUFcomImpostos</v>
-      </c>
-      <c r="C217" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D217" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E217" t="str">
-        <v/>
-      </c>
-      <c r="F217" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Risco Sacado</v>
-      </c>
-      <c r="B218" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RiscoSacado/RiscoSacado</v>
-      </c>
-      <c r="C218" t="str">
-        <v>BASE (Consolidado Risco Sacado)</v>
-      </c>
-      <c r="D218" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E218" t="str">
-        <v>:Measure Names; BASE (Count); Cnpj; Cnpj (Fornecedores); Cond. Pgto (FORNECEDORES1); Consolidado ZA e ZF (Count); Data de compensação (Consolidado ZA e ZF); Data De Lanç; Data de lançamento; Data De Venc; Data Inclusão; Data Inclusão (FORNECEDORES1); Dias; Dt Competência; Dt Competência (Compensadas); Dt Competência (Faturas); Dt Competência (Fornecedores); Dt Competência (Max); Empresa; Faturas enviadas (KM) (Count); Filtro 12 meses; Filtro 12 meses (Compensadas); Filtro 12 meses (Faturas); Filtro Dt Competência; Filtro gráfico; Filtro Mês Anterior; Filtro Mês Atual; Filtro Mês Atual (Compensadas); Filtro Mês Atual (Faturas); Fornecedor; Fornecedor (FORNECEDORES1); FORNECEDORES (Count); FORNECEDORES1 (Count); Montante em moeda interna; Montante em moeda interna (ajustado); Montante em moeda interna (Consolidado ZA e ZF); N° Doc; Período; Período (Faturas); Prazo médio da fatura</v>
-      </c>
-      <c r="F218" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>Risco Sacado</v>
-      </c>
-      <c r="B219" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RiscoSacado/RiscoSacado</v>
-      </c>
-      <c r="C219" t="str">
-        <v>BASE (Consolidado Risco Sacado)</v>
-      </c>
-      <c r="D219" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E219" t="str">
-        <v/>
-      </c>
-      <c r="F219" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Estorno</v>
-      </c>
-      <c r="B220" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Estorno/Estorno</v>
-      </c>
-      <c r="C220" t="str">
-        <v/>
-      </c>
-      <c r="D220" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E220" t="str">
-        <v/>
-      </c>
-      <c r="F220" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Estorno</v>
-      </c>
-      <c r="B221" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Estorno/Estorno</v>
-      </c>
-      <c r="C221" t="str">
-        <v/>
-      </c>
-      <c r="D221" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E221" t="str">
-        <v/>
-      </c>
-      <c r="F221" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>Conferência Food</v>
-      </c>
-      <c r="B222" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ConfernciaFood/FechamentoFood-Integracao</v>
-      </c>
-      <c r="C222" t="str">
-        <v/>
-      </c>
-      <c r="D222" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E222" t="str">
-        <v/>
-      </c>
-      <c r="F222" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>Conferência Food</v>
-      </c>
-      <c r="B223" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ConfernciaFood/FechamentoFood-Integracao</v>
-      </c>
-      <c r="C223" t="str">
-        <v/>
-      </c>
-      <c r="D223" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E223" t="str">
-        <v/>
-      </c>
-      <c r="F223" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>Contratos Pedido</v>
-      </c>
-      <c r="B224" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosPedido/ContratosPedido</v>
-      </c>
-      <c r="C224" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
-      </c>
-      <c r="D224" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
-      </c>
-      <c r="E224" t="str">
-        <v>Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Grupoeconomico; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Site; Cd Status Contrato; Cd Tip Periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Uf; CD_LISTA_PRECO_VENDA; Cnpj Cliente; Cpf Cliente; Dados Migrados (Count); Data Pedido; Des Cliente Nl; Des Config Contrato; Des Filial Nl; Des Status Contrato; Des Tipo Adiantamento</v>
-      </c>
-      <c r="F224" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>Contratos Pedido</v>
-      </c>
-      <c r="B225" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ContratosPedido/ContratosPedido</v>
-      </c>
-      <c r="C225" t="str">
-        <v>BIFATURAMENTO - Cadastro Contrato NL</v>
-      </c>
-      <c r="D225" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48323/lineage</v>
-      </c>
-      <c r="E225" t="str">
-        <v/>
-      </c>
-      <c r="F225" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>Análise de Estorno</v>
-      </c>
-      <c r="B226" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisedeEstorno/Estorno</v>
-      </c>
-      <c r="C226" t="str">
-        <v/>
-      </c>
-      <c r="D226" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E226" t="str">
-        <v/>
-      </c>
-      <c r="F226" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>Análise de Estorno</v>
-      </c>
-      <c r="B227" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisedeEstorno/Estorno</v>
-      </c>
-      <c r="C227" t="str">
-        <v/>
-      </c>
-      <c r="D227" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E227" t="str">
-        <v/>
-      </c>
-      <c r="F227" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>Comparativo Food</v>
-      </c>
-      <c r="B228" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ComparativoFood/ComparativoFood</v>
-      </c>
-      <c r="C228" t="str">
-        <v/>
-      </c>
-      <c r="D228" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E228" t="str">
-        <v/>
-      </c>
-      <c r="F228" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>Comparativo Food</v>
-      </c>
-      <c r="B229" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ComparativoFood/ComparativoFood</v>
-      </c>
-      <c r="C229" t="str">
-        <v/>
-      </c>
-      <c r="D229" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E229" t="str">
-        <v/>
-      </c>
-      <c r="F229" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>Insights de Cancelamento de Notas Fiscais - Fatores e Impactos</v>
-      </c>
-      <c r="B230" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/InsightsdeCancelamentodeNotasFiscais-FatoreseImpactos_17313493325020/VisoGeral</v>
-      </c>
-      <c r="C230" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item; Compilado (Estorno Compilado)</v>
-      </c>
-      <c r="D230" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1792/lineage</v>
-      </c>
-      <c r="E230" t="str">
-        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175; Business Unit; Cancelados Mês Anterior; Cancelados Mês Atual; CC; Cfop; Cliente; CNPJ Remetente; Coluna1; Competência; Competência (Max); Compilado (Count); Data Lanc; Destacar Picos; Diretoria; Display; Dt Competência; Eixo; Fator Gerador; Filial; Filial2; Filtra Mês Atual; Filtro 13 meses; Filtro Mês Anterior; Filtro Mês Atual; Ícone; IE Remetente; Imp Credit; Isentas; Motivo; NF; NF origem; Nm Filial; Nº da NF; Origem do Estorno; Outras; Qt Cancelamentos; Qt Clientes; Rank Centro de Lucro; Rank Clientes</v>
-      </c>
-      <c r="F230" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>Insights de Cancelamento de Notas Fiscais - Fatores e Impactos</v>
-      </c>
-      <c r="B231" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/InsightsdeCancelamentodeNotasFiscais-FatoreseImpactos_17313493325020/VisoGeral</v>
-      </c>
-      <c r="C231" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item; Compilado (Estorno Compilado)</v>
-      </c>
-      <c r="D231" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1792/lineage</v>
-      </c>
-      <c r="E231" t="str">
-        <v/>
-      </c>
-      <c r="F231" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="str">
-        <v>Resultado financeiro - SG&amp;A</v>
-      </c>
-      <c r="B232" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmico_17320354393150/Colaboradoresativoseafastados</v>
-      </c>
-      <c r="C232" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D232" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1802/lineage</v>
-      </c>
-      <c r="E232" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F232" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v>Resultado financeiro - SG&amp;A</v>
-      </c>
-      <c r="B233" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmico_17320354393150/Colaboradoresativoseafastados</v>
-      </c>
-      <c r="C233" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D233" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1802/lineage</v>
-      </c>
-      <c r="E233" t="str">
-        <v/>
-      </c>
-      <c r="F233" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="str">
-        <v>Resultado financeiro - Grupo conta</v>
-      </c>
-      <c r="B234" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoconta/Resultadogrupoconta</v>
-      </c>
-      <c r="C234" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha</v>
-      </c>
-      <c r="D234" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1503/lineage</v>
-      </c>
-      <c r="E234" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F234" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v>Resultado financeiro - Grupo conta</v>
-      </c>
-      <c r="B235" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoconta/Resultadogrupoconta</v>
-      </c>
-      <c r="C235" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha</v>
-      </c>
-      <c r="D235" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1503/lineage</v>
-      </c>
-      <c r="E235" t="str">
-        <v/>
-      </c>
-      <c r="F235" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="str">
-        <v>CR04 - Títulos Vencidos</v>
-      </c>
-      <c r="B236" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR04-TtulosVencidos/TtulosVencidos</v>
-      </c>
-      <c r="C236" t="str">
-        <v>Análise de Títulos Vencidos</v>
-      </c>
-      <c r="D236" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/577/lineage</v>
-      </c>
-      <c r="E236" t="str">
-        <v>% do Total; :Measure Names; Ano Arquivo; Ano Fiscal; Ano Fiscal Data Referência; Atraso; Atribuição; Base; CD_ATR; CD_BUSINESS_UNIT; CD_CARDAPIO; CD_CENTRO_CUSTO; CD_CLIENTE_NL; CD_DIRETORIA; CD_EMPRESA_SODEXO; CD_FILIAL_FICTICIA; CD_FILIAL_NL; CD_GRUPOECONOMICO; CD_MATRICULA_DIRETOR_OPERAC; CD_MATRICULA_GERENTE_AREA; CD_MATRICULA_GERENTE_REGIONAL; CD_MATRIZ; CD_ORIGEM; CD_REGIONAL; CD_SEGMENTO; CD_TIPO_ATUACAO; CD_TIPO_CONTRATO; CD_TIPO_SERVICO; CD_UF; Cliente; Cliente CNPJ CPF; Clúster Títulos Vencidos; Cód Filial; Consulta do SQL personalizado (Count); Conta; Data; Data Vencimento; Diretoria; DSC_ORIGEM; DSC_TEXTO_CABECALHO_DOCUMENTO</v>
-      </c>
-      <c r="F236" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>CR04 - Títulos Vencidos</v>
-      </c>
-      <c r="B237" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR04-TtulosVencidos/TtulosVencidos</v>
-      </c>
-      <c r="C237" t="str">
-        <v>Análise de Títulos Vencidos</v>
-      </c>
-      <c r="D237" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/577/lineage</v>
-      </c>
-      <c r="E237" t="str">
-        <v/>
-      </c>
-      <c r="F237" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>Resultado financeiro - Fat e GP Ano Fiscal mês a mês</v>
-      </c>
-      <c r="B238" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscalmsams/FateGPSAP-Anofiscal</v>
-      </c>
-      <c r="C238" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D238" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2051/lineage</v>
-      </c>
-      <c r="E238" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F238" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>Resultado financeiro - Fat e GP Ano Fiscal mês a mês</v>
-      </c>
-      <c r="B239" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-FateGPAnoFiscalmsams/FateGPSAP-Anofiscal</v>
-      </c>
-      <c r="C239" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D239" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2051/lineage</v>
-      </c>
-      <c r="E239" t="str">
-        <v/>
-      </c>
-      <c r="F239" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>Organic Growth - FY24</v>
-      </c>
-      <c r="B240" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY24/OrganicGrowth</v>
-      </c>
-      <c r="C240" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
-      </c>
-      <c r="D240" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E240" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
-      </c>
-      <c r="F240" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>Organic Growth - FY24</v>
-      </c>
-      <c r="B241" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY24/OrganicGrowth</v>
-      </c>
-      <c r="C241" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
-      </c>
-      <c r="D241" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E241" t="str">
-        <v/>
-      </c>
-      <c r="F241" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>F03 - Extração de Itens XML por UF com Imposto</v>
-      </c>
-      <c r="B242" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/F03-ExtraodeItensXMLporUFcomImposto/ExtraodeItensXMLporUFcomImposto</v>
-      </c>
-      <c r="C242" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D242" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E242" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
-      </c>
-      <c r="F242" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>F03 - Extração de Itens XML por UF com Imposto</v>
-      </c>
-      <c r="B243" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/F03-ExtraodeItensXMLporUFcomImposto/ExtraodeItensXMLporUFcomImposto</v>
-      </c>
-      <c r="C243" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D243" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E243" t="str">
-        <v/>
-      </c>
-      <c r="F243" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>IE01 - Performance de Atendimento - V2.1</v>
-      </c>
-      <c r="B244" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento-V2_1/SatisfaodoClientenoAtendimento</v>
-      </c>
-      <c r="C244" t="str">
-        <v>BICSCFINANCAS - Chamados CA (NEW); BICSCFINANCAS - Satisfação</v>
-      </c>
-      <c r="D244" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2102/lineage</v>
-      </c>
-      <c r="E244" t="str">
-        <v>% Total; *CC Comprovante pagamento; :Measure Names; [fn] Data atualização; [fn] Usuario; Ano Fiscal Competência; Ano Fiscal Parâmetro; Ano Fiscal Parâmetro Histórico; Calculation1; CC: % Atend. &lt;= 2 dias; CC: % Atend. &lt;= 2 dias (eixo hist); CC: % Atend. &lt;= 2 dias (hist AVG); CC: % Atend. &lt;= 2 dias (hist AVG) (copy); CC: % Atend. &lt;= 2 dias (hist MAX); CC: % Atend. &lt;= 2 dias (hist MIN); CC: % Atend. &lt;= 2 dias (hist); CC: % Atend. &lt;= 2 dias (hist) (new); CC: % Atend. &lt;= 2 dias Mês Anterior; CC: % Atendimentos SLA Cumprido; CC: % Atendimentos SLA Cumprido (cor); CC: % Atendimentos SLA Cumprido (eixo hist); CC: % Atendimentos SLA Cumprido (hist); CC: % Atendimentos SLA Cumprido (hist) (copy); CC: % Atendimentos SLA Violado; CC: Data Competência; CC: Filtro Abertos Mês Anterior; CC: Filtro Abertos Mês Selecionado; CC: Filtro Ano Fiscal; CC: Filtro Ano Fiscal Histórico; CC: Filtro Concluídos; CC: Filtro Mês Anterior; CC: Filtro Mês Selecionado; CC: Filtro Perc; CC: Filtro Último Mês; CC: Filtro Últimos 3 meses; CC: Nr Dias Atendimento (c/ pendente); CC: Nr Dias Atendimento (s/ pendente); CC: Tempo de Resolucao; Cd Canal; Cd Uf; Custom SQL Query (Count); Domain; DS_CANAL; DS_HIERARQUIA; DSC_CATEGORIA; DSC_COMENTARIO_RESPOSTA; DSC_DOMAIN; DSC_GRUPO; DSC_PESQUISA_RESPONDIDA; DSC_RSP_ATENDIMENTO; DSC_RSP_ENTREGA; Dt Competência; Dt Competência (Max); Dt Competência Anterior (short text); DT_ABERTURA; DT_ENCERRAMENTO; DT_RESOLUCAO; DT_RESPOSTA; Filtro Detrator; Filtro Dsc Rsp Atendimento; Filtro Mês Anterior; Filtro Mês Selecionado; Filtro Promotor; Filtro últimos 12 meses; FY; Gauge Detrator Atendimento Comparativo; Gauge Detrator Entrega Comparativo; Gauge Promotor Atendimento Comparativo; Gauge Promotor Entrega Comparativo; Gauge Respondidos vs Concluídos Comparativo; Gauge Total Atendimento Comparativo; Gauge Total Entrega Comparativo; Insatisfeito; Insatisfeito Entrega; NM_ANALISTA; NM_GRUPO; NM_SRC; NM_USR_AFETADO; NR_CHAMADO</v>
-      </c>
-      <c r="F244" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>IE01 - Performance de Atendimento - V2.1</v>
-      </c>
-      <c r="B245" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IE01-PerformancedeAtendimento-V2_1/SatisfaodoClientenoAtendimento</v>
-      </c>
-      <c r="C245" t="str">
-        <v>BICSCFINANCAS - Chamados CA (NEW); BICSCFINANCAS - Satisfação</v>
-      </c>
-      <c r="D245" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2102/lineage</v>
-      </c>
-      <c r="E245" t="str">
-        <v/>
-      </c>
-      <c r="F245" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>Resultado financeiro - Grupo econômico análise pessoal %</v>
-      </c>
-      <c r="B246" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmicoanlisepessoal_17392198009060/Anlisepessoalporservio</v>
-      </c>
-      <c r="C246" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; Clipboard_20250210T152659; Clipboard_20250210T152751; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D246" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1937/lineage</v>
-      </c>
-      <c r="E246" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; % Pessoal; % Pessoal OR; Clipboard_20250210T152659 (Count); Mês de CONT DTFECHAMENTO; Nomes de medida; Clipboard_20250210T152751 (Count); ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F246" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>Resultado financeiro - Grupo econômico análise pessoal %</v>
-      </c>
-      <c r="B247" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Grupoeconmicoanlisepessoal_17392198009060/Anlisepessoalporservio</v>
-      </c>
-      <c r="C247" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; Clipboard_20250210T152659; Clipboard_20250210T152751; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D247" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1937/lineage</v>
-      </c>
-      <c r="E247" t="str">
-        <v/>
-      </c>
-      <c r="F247" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>Resultado financeiro - Trimestre</v>
-      </c>
-      <c r="B248" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Trimestre/ResultadoSAPFateGP</v>
-      </c>
-      <c r="C248" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D248" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1746/lineage</v>
-      </c>
-      <c r="E248" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real; IRFS Real</v>
-      </c>
-      <c r="F248" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>Resultado financeiro - Trimestre</v>
-      </c>
-      <c r="B249" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-Trimestre/ResultadoSAPFateGP</v>
-      </c>
-      <c r="C249" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D249" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1746/lineage</v>
-      </c>
-      <c r="E249" t="str">
-        <v/>
-      </c>
-      <c r="F249" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>Painel</v>
-      </c>
-      <c r="B250" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Painel/Equinor_</v>
-      </c>
-      <c r="C250" t="str">
-        <v/>
-      </c>
-      <c r="D250" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E250" t="str">
-        <v/>
-      </c>
-      <c r="F250" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>Painel</v>
-      </c>
-      <c r="B251" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Painel/Equinor_</v>
-      </c>
-      <c r="C251" t="str">
-        <v/>
-      </c>
-      <c r="D251" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E251" t="str">
-        <v/>
-      </c>
-      <c r="F251" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>Relatorio de Materiais de Venda - MDM</v>
-      </c>
-      <c r="B252" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeMateriaisdeVenda-MDM/RelatriodeMateriaisdeVenda</v>
-      </c>
-      <c r="C252" t="str">
-        <v/>
-      </c>
-      <c r="D252" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E252" t="str">
-        <v/>
-      </c>
-      <c r="F252" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="str">
-        <v>Relatorio de Materiais de Venda - MDM</v>
-      </c>
-      <c r="B253" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeMateriaisdeVenda-MDM/RelatriodeMateriaisdeVenda</v>
-      </c>
-      <c r="C253" t="str">
-        <v/>
-      </c>
-      <c r="D253" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E253" t="str">
-        <v/>
-      </c>
-      <c r="F253" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="str">
-        <v>Medição x Vencimento</v>
-      </c>
-      <c r="B254" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MedioxVencimento/MedioxVencimento</v>
-      </c>
-      <c r="C254" t="str">
-        <v/>
-      </c>
-      <c r="D254" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E254" t="str">
-        <v/>
-      </c>
-      <c r="F254" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="str">
-        <v>Medição x Vencimento</v>
-      </c>
-      <c r="B255" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/MedioxVencimento/MedioxVencimento</v>
-      </c>
-      <c r="C255" t="str">
-        <v/>
-      </c>
-      <c r="D255" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E255" t="str">
-        <v/>
-      </c>
-      <c r="F255" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="str">
-        <v>Relatorio de Quantidade UF</v>
-      </c>
-      <c r="B256" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidadeUF/Quantidade</v>
-      </c>
-      <c r="C256" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
-      </c>
-      <c r="D256" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
-      </c>
-      <c r="E256" t="str">
-        <v/>
-      </c>
-      <c r="F256" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="str">
-        <v>Relatorio de Quantidade UF</v>
-      </c>
-      <c r="B257" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidadeUF/Quantidade</v>
-      </c>
-      <c r="C257" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
-      </c>
-      <c r="D257" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
-      </c>
-      <c r="E257" t="str">
-        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
-      </c>
-      <c r="F257" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="str">
-        <v>Relatorio de Quantidade_Cliente</v>
-      </c>
-      <c r="B258" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade_Cliente/Quantidade</v>
-      </c>
-      <c r="C258" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
-      </c>
-      <c r="D258" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
-      </c>
-      <c r="E258" t="str">
-        <v/>
-      </c>
-      <c r="F258" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="str">
-        <v>Relatorio de Quantidade_Cliente</v>
-      </c>
-      <c r="B259" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RelatoriodeQuantidade_Cliente/Quantidade</v>
-      </c>
-      <c r="C259" t="str">
-        <v>BIFATURAMENTO - Faturamento NL NES Item</v>
-      </c>
-      <c r="D259" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48326/lineage</v>
-      </c>
-      <c r="E259" t="str">
-        <v>:Measure Names; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cliente Nl; Cd Cliente Sap; Cd Config Contrato; Cd Diretoria; Cd Empresa Sodexo; Cd Familia Venda; Cd Filial; Cd Filial Ficticia; Cd Filial Nl; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Produto Venda; Cd Regional; Cd Segmento; Cd Seq Periodo; Cd Sistema Origem; Cd Status Contrato; cd tip periodo; Cd Tipo Adiantamento; Cd Tipo Atuacao; Cd Tipo Cliente; Cd Tipo Contrato; Cd Tipo Contrato (Vw D Filial); Cd Tipo Dia Vcto; Cd Tipo Servico; Cd Tp Nes; Cd Uf; Cd Unidade Medida; CD_GRUPOECONOMICO; CD_LISTA_PRECO_VENDA; CD_MASCARA_NL_175; CD_SITE; Cnpj Cliente; Cód Completo NL 175</v>
-      </c>
-      <c r="F259" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="str">
-        <v>Banco de Dados Processos CSC Finanças (ITIs)</v>
-      </c>
-      <c r="B260" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BancodeDadosProcessosCSCFinanasITIs/BancodeDadosProcessosCSCFinanasITIs</v>
-      </c>
-      <c r="C260" t="str">
-        <v>Banco de Dados Processos CSC FY26__6829137108881284s_(ITI_s) (Smartsheet: juliana.pantoja@sodexo.com)</v>
-      </c>
-      <c r="D260" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2282/lineage</v>
-      </c>
-      <c r="E260" t="str">
-        <v>_Attachcount; _Childids; _Discusscount; _Discusstext; _Outlinelevel; _Parentid; _Rowid; _Rownum; _Workspaceid; _Workspacename; Antecessores; Aprovador; Atividades Filho; Atrasadas; Banco de Dados Processos CSC FY26__6829137108881284s_(ITI_s) (Count); Código da ITI; Controle Relacionado; Data da revisão; Data limite para revisão; Data Planejado Assessment Controle; Data Próximo Revisão de ITI por CI; Duração; Eixo; Fase Assessment; Hierarquia; N° Atrasadas; Nome da ITI; Prazos; Processo; Quant. por domain; Quant. Status; Responsável pela Revisão; Status; Status CI; Status padronizado; Subprocesso; Tipo de automação</v>
-      </c>
-      <c r="F260" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="str">
-        <v>Banco de Dados Processos CSC Finanças (ITIs)</v>
-      </c>
-      <c r="B261" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BancodeDadosProcessosCSCFinanasITIs/BancodeDadosProcessosCSCFinanasITIs</v>
-      </c>
-      <c r="C261" t="str">
-        <v>Banco de Dados Processos CSC FY26__6829137108881284s_(ITI_s) (Smartsheet: juliana.pantoja@sodexo.com)</v>
-      </c>
-      <c r="D261" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2282/lineage</v>
-      </c>
-      <c r="E261" t="str">
-        <v/>
-      </c>
-      <c r="F261" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="str">
-        <v>Rateio Bonificação CD_FY26</v>
-      </c>
-      <c r="B262" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioBonificaoCD_FY26_17611615626620/RateioBonificaoCDs-Dirio</v>
-      </c>
-      <c r="C262" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
-      </c>
-      <c r="D262" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
-      </c>
-      <c r="E262" t="str">
-        <v/>
-      </c>
-      <c r="F262" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="str">
-        <v>Rateio Bonificação CD_FY26</v>
-      </c>
-      <c r="B263" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/RateioBonificaoCD_FY26_17611615626620/RateioBonificaoCDs-Dirio</v>
-      </c>
-      <c r="C263" t="str">
-        <v>BICOMPRAS - Compras Diaria</v>
-      </c>
-      <c r="D263" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48067/lineage</v>
-      </c>
-      <c r="E263" t="str">
-        <v>[FIE] Bairro; [FIE] CD Filial; [FIE] CEP; [FIE] Cidade; [FIE] Logadouro; [FIE] UF; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Filial Ficticia; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Sistema Origem; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida</v>
-      </c>
-      <c r="F263" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="str">
-        <v>Análise Prévia Consumo Dezembro 2025</v>
-      </c>
-      <c r="B264" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoDezembro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C264" t="str">
-        <v/>
-      </c>
-      <c r="D264" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E264" t="str">
-        <v/>
-      </c>
-      <c r="F264" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="str">
-        <v>Análise Prévia Consumo Dezembro 2025</v>
-      </c>
-      <c r="B265" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoDezembro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C265" t="str">
-        <v/>
-      </c>
-      <c r="D265" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E265" t="str">
-        <v/>
-      </c>
-      <c r="F265" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="str">
-        <v>CR08 - Provisão e Faturamento</v>
-      </c>
-      <c r="B266" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR08-ProvisoeFaturamento/EvoluodoFaturamento</v>
-      </c>
-      <c r="C266" t="str">
-        <v/>
-      </c>
-      <c r="D266" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E266" t="str">
-        <v/>
-      </c>
-      <c r="F266" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="str">
-        <v>CR08 - Provisão e Faturamento</v>
-      </c>
-      <c r="B267" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CR08-ProvisoeFaturamento/EvoluodoFaturamento</v>
-      </c>
-      <c r="C267" t="str">
-        <v/>
-      </c>
-      <c r="D267" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E267" t="str">
-        <v/>
-      </c>
-      <c r="F267" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="str">
-        <v>Análise Prévia Consumo Média PAP - Dezembro 25</v>
-      </c>
-      <c r="B268" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Dezembro25/Anliseprviaconsumo</v>
-      </c>
-      <c r="C268" t="str">
-        <v/>
-      </c>
-      <c r="D268" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E268" t="str">
-        <v/>
-      </c>
-      <c r="F268" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="str">
-        <v>Análise Prévia Consumo Média PAP - Dezembro 25</v>
-      </c>
-      <c r="B269" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoMdiaPAP-Dezembro25/Anliseprviaconsumo</v>
-      </c>
-      <c r="C269" t="str">
-        <v/>
-      </c>
-      <c r="D269" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E269" t="str">
-        <v/>
-      </c>
-      <c r="F269" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="str">
-        <v>Base Reajuste completa</v>
-      </c>
-      <c r="B270" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BaseReajustecompleta/Basereajuste</v>
-      </c>
-      <c r="C270" t="str">
-        <v>Reajuste_Contrato</v>
-      </c>
-      <c r="D270" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage</v>
-      </c>
-      <c r="E270" t="str">
-        <v/>
-      </c>
-      <c r="F270" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="str">
-        <v>Base Reajuste completa</v>
-      </c>
-      <c r="B271" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/BaseReajustecompleta/Basereajuste</v>
-      </c>
-      <c r="C271" t="str">
-        <v>Reajuste_Contrato</v>
-      </c>
-      <c r="D271" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48348/lineage</v>
-      </c>
-      <c r="E271" t="str">
-        <v>:Measure Names; ANDAMENTO; CODUNIDADEFILIAL; Dados migrados (Count); DATAHORAFIMHIST; DATAHORAINICIOHIST; DATAMESCORRENTE; DATAMESREAJUSTERETROATIVO; DATAREAJUSTERETROATIVO; DESCINDICECOMPOSICAOREAJUSTE; DESCSITUACAOPROCESSO; DESCWORKFLOW; DIFERENCAAPLICADOCALCULADO; FATORMESACUMULADO; FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO</v>
-      </c>
-      <c r="F271" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="str">
-        <v>Saving</v>
-      </c>
-      <c r="B272" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Saving/Anlise</v>
-      </c>
-      <c r="C272" t="str">
-        <v/>
-      </c>
-      <c r="D272" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E272" t="str">
-        <v/>
-      </c>
-      <c r="F272" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="str">
-        <v>Saving</v>
-      </c>
-      <c r="B273" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Saving/Anlise</v>
-      </c>
-      <c r="C273" t="str">
-        <v/>
-      </c>
-      <c r="D273" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E273" t="str">
-        <v/>
-      </c>
-      <c r="F273" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="str">
-        <v>FISCAL10 - Painel Manifestação Manual</v>
-      </c>
-      <c r="B274" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL10-PainelManifestaoManual/ManifestaoManual</v>
-      </c>
-      <c r="C274" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
-      </c>
-      <c r="D274" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/21/lineage</v>
-      </c>
-      <c r="E274" t="str">
-        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Migrated Data (Count); Number of Records; Status XML; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE</v>
-      </c>
-      <c r="F274" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="str">
-        <v>FISCAL10 - Painel Manifestação Manual</v>
-      </c>
-      <c r="B275" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL10-PainelManifestaoManual/ManifestaoManual</v>
-      </c>
-      <c r="C275" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
-      </c>
-      <c r="D275" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/21/lineage</v>
-      </c>
-      <c r="E275" t="str">
-        <v/>
-      </c>
-      <c r="F275" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="str">
-        <v>Organic Growth - FY25</v>
-      </c>
-      <c r="B276" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY25/OGClientes</v>
-      </c>
-      <c r="C276" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
-      </c>
-      <c r="D276" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E276" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro</v>
-      </c>
-      <c r="F276" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="str">
-        <v>Organic Growth - FY25</v>
-      </c>
-      <c r="B277" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/OrganicGrowth-FY25/OGClientes</v>
-      </c>
-      <c r="C277" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa</v>
-      </c>
-      <c r="D277" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage</v>
-      </c>
-      <c r="E277" t="str">
-        <v/>
-      </c>
-      <c r="F277" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="str">
-        <v>Evolução dos processos de reajuste FY26</v>
-      </c>
-      <c r="B278" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/EvoluodosprocessosdereajusteFY26/Reajuste-Evoluoprocessos</v>
-      </c>
-      <c r="C278" t="str">
-        <v>Sheet 1 (REAJUSTE 2)</v>
-      </c>
-      <c r="D278" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2242/lineage</v>
-      </c>
-      <c r="E278" t="str">
-        <v/>
-      </c>
-      <c r="F278" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="str">
-        <v>Evolução dos processos de reajuste FY26</v>
-      </c>
-      <c r="B279" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/EvoluodosprocessosdereajusteFY26/Reajuste-Evoluoprocessos</v>
-      </c>
-      <c r="C279" t="str">
-        <v>Sheet 1 (REAJUSTE 2)</v>
-      </c>
-      <c r="D279" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/2242/lineage</v>
-      </c>
-      <c r="E279" t="str">
-        <v>% Calculado; % Concedido; :Measure Names; Centro de lucro; Cliente; Direção1; Fat. média 3 meses da data fim; Fator; Mês, Ano de Data Base1; Mês, Ano de Data fim processo; Mês, Ano de Data inicio do processo; Mês, Dia, Ano de Data reajuste retroativo mes; Nome; Período1; Processo; Reajuste calculado mês; Reajuste calculado YTD; Reajuste concedido mês; Reajuste concedido YTD; Regional; Segmento1; Serviço; Sheet 1 (Count); Situação do processo1; Tipo reajuste1</v>
-      </c>
-      <c r="F279" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="str">
-        <v>Livro1</v>
-      </c>
-      <c r="B280" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Livro1_17625386860670/Painel1</v>
-      </c>
-      <c r="C280" t="str">
-        <v>BICompras - Compras Mensal</v>
-      </c>
-      <c r="D280" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
-      </c>
-      <c r="E280" t="str">
-        <v/>
-      </c>
-      <c r="F280" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="str">
-        <v>Livro1</v>
-      </c>
-      <c r="B281" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Livro1_17625386860670/Painel1</v>
-      </c>
-      <c r="C281" t="str">
-        <v>BICompras - Compras Mensal</v>
-      </c>
-      <c r="D281" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
-      </c>
-      <c r="E281" t="str">
-        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
-      </c>
-      <c r="F281" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="str">
-        <v>Painel de ICMS - RS</v>
-      </c>
-      <c r="B282" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeICMS-RS/ICMS-RS</v>
-      </c>
-      <c r="C282" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D282" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E282" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
-      </c>
-      <c r="F282" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="str">
-        <v>Painel de ICMS - RS</v>
-      </c>
-      <c r="B283" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeICMS-RS/ICMS-RS</v>
-      </c>
-      <c r="C283" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D283" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E283" t="str">
-        <v/>
-      </c>
-      <c r="F283" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="str">
-        <v>XMLs Emitidos mês</v>
-      </c>
-      <c r="B284" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosms/Painel1</v>
-      </c>
-      <c r="C284" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
-      </c>
-      <c r="D284" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
-      </c>
-      <c r="E284" t="str">
-        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação</v>
-      </c>
-      <c r="F284" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="str">
-        <v>XMLs Emitidos mês</v>
-      </c>
-      <c r="B285" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosms/Painel1</v>
-      </c>
-      <c r="C285" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
-      </c>
-      <c r="D285" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
-      </c>
-      <c r="E285" t="str">
-        <v/>
-      </c>
-      <c r="F285" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="str">
-        <v>Análise Prévia Consumo Janeiro 2025</v>
-      </c>
-      <c r="B286" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C286" t="str">
-        <v/>
-      </c>
-      <c r="D286" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E286" t="str">
-        <v/>
-      </c>
-      <c r="F286" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="str">
-        <v>Análise Prévia Consumo Janeiro 2025</v>
-      </c>
-      <c r="B287" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/AnlisePrviaConsumoJaneiro2025/AnlisePrviadoConsumo</v>
-      </c>
-      <c r="C287" t="str">
-        <v/>
-      </c>
-      <c r="D287" t="str">
-        <v>ERRO: O painel nao pode ser acessado com a sessao atual no Tableau.</v>
-      </c>
-      <c r="E287" t="str">
-        <v/>
-      </c>
-      <c r="F287" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="str">
-        <v>Notas Oper Não Realizada e Manif Manual</v>
-      </c>
-      <c r="B288" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasOperNoRealizadaeManifManual/OutrasManifestaes</v>
-      </c>
-      <c r="C288" t="str">
-        <v/>
-      </c>
-      <c r="D288" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E288" t="str">
-        <v/>
-      </c>
-      <c r="F288" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="str">
-        <v>Notas Oper Não Realizada e Manif Manual</v>
-      </c>
-      <c r="B289" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasOperNoRealizadaeManifManual/OutrasManifestaes</v>
-      </c>
-      <c r="C289" t="str">
-        <v/>
-      </c>
-      <c r="D289" t="str">
-        <v>ERRO: Nao encontrei o link do workbook no painel Data Details.</v>
-      </c>
-      <c r="E289" t="str">
-        <v/>
-      </c>
-      <c r="F289" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="str">
-        <v>ADH04 - Rateio Custos Ecolab Duque</v>
-      </c>
-      <c r="B290" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH04-RateioCustosEcolabDuque/ADH4-RateioCustosEcolabMaca</v>
-      </c>
-      <c r="C290" t="str">
-        <v>BICompras - Compras Mensal</v>
-      </c>
-      <c r="D290" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
-      </c>
-      <c r="E290" t="str">
-        <v/>
-      </c>
-      <c r="F290" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="str">
-        <v>ADH04 - Rateio Custos Ecolab Duque</v>
-      </c>
-      <c r="B291" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ADH04-RateioCustosEcolabDuque/ADH4-RateioCustosEcolabMaca</v>
-      </c>
-      <c r="C291" t="str">
-        <v>BICompras - Compras Mensal</v>
-      </c>
-      <c r="D291" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/49876/lineage</v>
-      </c>
-      <c r="E291" t="str">
-        <v>Bairro; CD; Cd Ano Mes; Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Cnpj; Cd Diretoria; Cd Empresa Sodexo; Cd Familia; Cd Filial; Cd Fornecedor; Cd Gerente Compras; Cd Item Receita Nl; Cd Macro Familia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Negociador; Cd Produto Compras; Cd Produto Generico; Cd Produto Nl; Cd Produto Operacional; Cd Regional; Cd Segmento; Cd Subfamilia; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Entrega; Cd Tipo Servico; Cd Uf; Cd Unidade Medida; Cdsetorindustrial; CEP; Cidade; Cnpj Cpf; CT_LEVEL1; CT_LEVEL2; CT_LEVEL3</v>
-      </c>
-      <c r="F291" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="str">
-        <v>Painel XML informação XPED</v>
-      </c>
-      <c r="B292" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED/1-PainelNFSXPED</v>
-      </c>
-      <c r="C292" t="str">
-        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
-      </c>
-      <c r="D292" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E292" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Mascara 20 NL; Cd pessoal NL; CNPJ Fornecedor NL; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
-      </c>
-      <c r="F292" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="str">
-        <v>Painel XML informação XPED</v>
-      </c>
-      <c r="B293" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED/1-PainelNFSXPED</v>
-      </c>
-      <c r="C293" t="str">
-        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
-      </c>
-      <c r="D293" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E293" t="str">
-        <v/>
-      </c>
-      <c r="F293" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="str">
-        <v>Resultado financeiro - conta a conta por cl</v>
-      </c>
-      <c r="B294" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-contaacontaporcl/9-ContaacontaSAP</v>
-      </c>
-      <c r="C294" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D294" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2452/lineage</v>
-      </c>
-      <c r="E294" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_CODIGONOME; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; FILI_EMAILGERENTEAREA; FILI_EMAILGERENTEREGIONAL; FILI_EXERCICIODVP; FILI_EXERCICIOENC; FILI_IMPORTAHFM; FILI_LATITUDE; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; FILI_CDTIPOSUBSERVICO; CONTC_CONTA; CONTC_CONTA_DESC; CONTC_DTFECHAMENTO; CONTC_GRUPO_CONTA; CONTC_TIMESTAMP; CONTC_VLORCADO; CONTC_VLREALIZADO; CONT_DEVPORT; CONT_FONTE; FILI_NMBUSINESSUNIT; FILI_NMDIRECAO; FILI_NMGRUPOCL; FILI_NMREGIONAL; FILI_NMSEGMENTO; FILI_NMSUBGRUPOCL; H_GRUPOCENTROLUCRO; H_NEGOCIO; Meta Fixa; Meta_Fixa_Com_SGA; Number of Records; Orçado; Real; USUA_ACESSO; Usuario_Filtro; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; Cd Contrato; Cd Cota Aprendiz CBO; Cd Diretoria; Cd Empresa; Cd Estr Hierar; Cd Estr Hierar Colab; Cd Filial; Cd Filial Colaborador; Cd Grupo CL; Cd Grupo Economico; Cd Matriz Cardapio; Cd Matriz Compras; Cd Regional; Cd Segmento; Cd Sindicato; Cd Site; Cd Situacao; Cd SubGrupo CL; Cd Tipo Atuação; Cd Tipo Contrato; Cd Tipo Serviço; CD_FLEXIVEL; CD_HORARIO; CD_STATUS_VAGA; CD_TP_FILIAL_COLABORADOR; ATR; Atribuição; BR-Denominação TpDV; BR - Cliente CNPJ o CPF; BR - Nome de centro de lucro; BR - Nome de grupo do cliente; BR - Nome do cliente; BR - Nome do regional 1; BR - Nome do segmento; BR - Nome do segmento1; CL; Conta; Data do documento; Empresa; Gr Ec; JAN E FEV (Count); Montante; PDD 60 dias; Referência; Texto; Texto cabeçalho documento; Vencimento líquido; % Desvio; % Desvio SAP; % GP MF; % GP Real; % MF; % Real; :Measure Names; Atingimento de budget; BoasVinda_Data; BoasVinda_Hora; Bonif MF; Bonif Real; Cons MF; Cons Real; Dados migrados; Deprec MF; Deprec Real; Desvio; Desvio errado; Desvio M; Fat Desvio; Fat MF; Fat Real; FILI_NMSEGMENTO (grupo); GP Desvio; GP MF; GP Real</v>
-      </c>
-      <c r="F294" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="str">
-        <v>Resultado financeiro - conta a conta por cl</v>
-      </c>
-      <c r="B295" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Resultadofinanceiro-contaacontaporcl/9-ContaacontaSAP</v>
-      </c>
-      <c r="C295" t="str">
-        <v>Centro_Lucro; Contabil; Contabil_Conta; Contabil_MetaFixa (2); RH - Colaborador Folha; JAN E FEV (PDD 60 DIAS (003))</v>
-      </c>
-      <c r="D295" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48347/lineage; https://analyticsbi.sodexo.com.br/#/datasources/51198/lineage; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2452/lineage</v>
-      </c>
-      <c r="E295" t="str">
-        <v/>
-      </c>
-      <c r="F295" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="str">
-        <v>XMLs Emitidos mês Ju</v>
-      </c>
-      <c r="B296" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosmsJu/Painel1</v>
-      </c>
-      <c r="C296" t="str">
-        <v/>
-      </c>
-      <c r="D296" t="str">
-        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
-      </c>
-      <c r="E296" t="str">
-        <v/>
-      </c>
-      <c r="F296" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="str">
-        <v>XMLs Emitidos mês Ju</v>
-      </c>
-      <c r="B297" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/XMLsEmitidosmsJu/Painel1</v>
-      </c>
-      <c r="C297" t="str">
-        <v/>
-      </c>
-      <c r="D297" t="str">
-        <v>Nenhum datasource encontrado na pagina do workbook/lineage</v>
-      </c>
-      <c r="E297" t="str">
-        <v/>
-      </c>
-      <c r="F297" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="str">
-        <v>Painel para Lançamento de NFe - Ativo com NitemPed</v>
-      </c>
-      <c r="B298" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe-AtivocomNitemPed/PainelLanamentodeNFe-Ativo</v>
-      </c>
-      <c r="C298" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
-      </c>
-      <c r="D298" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
-      </c>
-      <c r="E298" t="str">
-        <v>% Identificado; % Ñ Identificado; % Ñ Informado; % Xped informado; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Filial OC; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Status Manifestacao; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cfop Venda; Cnpj Completo Oc; Cnpj Raiz; Cnpj Raiz-Setor Industrial; Cnpj Raiz-Setor Industrial Bd; Cnpj Raiz-Setor Industrial OLD; Cnpj Raiz , Fornecedor; Cnpj Raiz Bd; Cod Chave Nfe; Cod Oper OC; Dados migrados (Count); DePara; Status XML; CD_FLAGNFE; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; COD_CCLASSTRIBIS_IS; COD_CCLASSTRIBREG_GTBREG; COD_CCLASSTRIBSCBS_IBSCBS; COD_CCREDPRES_GCBSCRPRES; COD_CCREDPRES_GIBSCRPRES; COD_CST_IBSCBS; COD_CST_ICMS02; COD_CST_ICMS15; COD_CST_ICMS53; COD_CST_ICMS61; COD_CSTIS_IS; COD_CSTREG_GTBREG; COD_UM_TRIB; COD_UTRIB_IS; Dsc Flagnfe; Dtcarga (F Xml Item); FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento</v>
-      </c>
-      <c r="F298" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="str">
-        <v>Painel para Lançamento de NFe - Ativo com NitemPed</v>
-      </c>
-      <c r="B299" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelparaLanamentodeNFe-AtivocomNitemPed/PainelLanamentodeNFe-Ativo</v>
-      </c>
-      <c r="C299" t="str">
-        <v>BIVARREDURA - Check Unidade Xped; BIVarredura - XML NF Item; BIVarredura - XML NF Supply; BIVARREDURA - XML SEFAZ</v>
-      </c>
-      <c r="D299" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/13616/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage; https://analyticsbi.sodexo.com.br/#/datasources/2494/lineage</v>
-      </c>
-      <c r="E299" t="str">
-        <v/>
-      </c>
-      <c r="F299" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="str">
-        <v>Extração XML Outras Operações</v>
-      </c>
-      <c r="B300" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLOutrasOperaes/Painel1</v>
-      </c>
-      <c r="C300" t="str">
-        <v>BIVarredura - Docs Simples Remessa</v>
-      </c>
-      <c r="D300" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/11972/lineage</v>
-      </c>
-      <c r="E300" t="str">
-        <v>Cd Chave Nfe; Cd Flagnfe; Cd Serie; Cd Status Manifestacao; Cfop; Chaves Referenciada; Cnpj Unidade; Dados migrados (Count); Dsc Empresa Unidade; Dsc Flagnfe; Dsc Status Manifestacao; Dt Emissao; Dth Inclusao; FLEG_CNPJCPF; For Cdcondicaopagamento; For Cdgrupoconta; For Cdnl; For Cdobrigatorionfe; For Cdsap; For Cdsapantigo; For Cdsetorindustrial; For Cnpjcpf; For Distribuidorfabricante; For Dscobrigatorionfe; For Dtalteracao; For Dtcriacao; For Email; For Homologado; For Nmcondicaopagamento; For Nmfantasia; For Nmgrupoconta; For Nmsetorindustrial; For Razaosocial; For Status; For Telefone; For Tipopagamento; Ind Proc Devolução; Nro Modelo; Nro Notafiscal; Number of Records</v>
-      </c>
-      <c r="F300" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="str">
-        <v>Extração XML Outras Operações</v>
-      </c>
-      <c r="B301" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ExtraoXMLOutrasOperaes/Painel1</v>
-      </c>
-      <c r="C301" t="str">
-        <v>BIVarredura - Docs Simples Remessa</v>
-      </c>
-      <c r="D301" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/11972/lineage</v>
-      </c>
-      <c r="E301" t="str">
-        <v/>
-      </c>
-      <c r="F301" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="str">
-        <v>Integração RNF</v>
-      </c>
-      <c r="B302" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IntegraoRNF/Painel1</v>
-      </c>
-      <c r="C302" t="str">
-        <v>BIVARREDURA - Notas Fora</v>
-      </c>
-      <c r="D302" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
-      </c>
-      <c r="E302" t="str">
-        <v/>
-      </c>
-      <c r="F302" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="str">
-        <v>Integração RNF</v>
-      </c>
-      <c r="B303" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/IntegraoRNF/Painel1</v>
-      </c>
-      <c r="C303" t="str">
-        <v>BIVARREDURA - Notas Fora</v>
-      </c>
-      <c r="D303" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
-      </c>
-      <c r="E303" t="str">
-        <v>:Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Serie Nota Fiscal; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Nl; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cnpj Fornecedor Nl; Cod Empresa; DES_CHAVE_NFE; Dias Excedentes; Diretoria; Dsc Flagnfe; Dt Abertura; Dt Carga; Dt Competencia; Dt Emissao Nota Fiscal; Dt Encerramento; Dt Importacao Rnf; Dt Lancamento Nota Fiscal; Dt Processamento Rnf; Dt Rnf; F_NOTAS_FORA (Count); Fili Email; Filial</v>
-      </c>
-      <c r="F303" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="str">
-        <v>Painel XML informação XPED-Indicadores</v>
-      </c>
-      <c r="B304" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED-Indicadores/BaseIndicadoresXped_Nitem</v>
-      </c>
-      <c r="C304" t="str">
-        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
-      </c>
-      <c r="D304" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E304" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Mascara 20 NL; Cd pessoal NL; CNPJ Fornecedor NL; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
-      </c>
-      <c r="F304" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="str">
-        <v>Painel XML informação XPED-Indicadores</v>
-      </c>
-      <c r="B305" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelXMLinformaoXPED-Indicadores/BaseIndicadoresXped_Nitem</v>
-      </c>
-      <c r="C305" t="str">
-        <v>BIVarredura - XML NF Item; Varredura - XML NF Header</v>
-      </c>
-      <c r="D305" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E305" t="str">
-        <v/>
-      </c>
-      <c r="F305" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="str">
-        <v>Painel Conciliação RNF NL vs SAP</v>
-      </c>
-      <c r="B306" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelConciliaoRNFNLvsSAP/ConciliaoRNFNLvsSAP</v>
-      </c>
-      <c r="C306" t="str">
-        <v>BIVARREDURA - Notas Fora</v>
-      </c>
-      <c r="D306" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
-      </c>
-      <c r="E306" t="str">
-        <v/>
-      </c>
-      <c r="F306" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="str">
-        <v>Painel Conciliação RNF NL vs SAP</v>
-      </c>
-      <c r="B307" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelConciliaoRNFNLvsSAP/ConciliaoRNFNLvsSAP</v>
-      </c>
-      <c r="C307" t="str">
-        <v>BIVARREDURA - Notas Fora</v>
-      </c>
-      <c r="D307" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/44811/lineage</v>
-      </c>
-      <c r="E307" t="str">
-        <v>:Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Flagnfe; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Serie Nota Fiscal; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Unidade Nl; CD_BUSINESS_UNIT; CD_GRUPO_ECONOMICO; Cnpj Fornecedor Nl; Cod Empresa; DES_CHAVE_NFE; Dias Excedentes; Diretoria; Dsc Flagnfe; Dt Abertura; Dt Carga; Dt Competencia; Dt Emissao Nota Fiscal; Dt Encerramento; Dt Importacao Rnf; Dt Lancamento Nota Fiscal; Dt Processamento Rnf; Dt Rnf; F_NOTAS_FORA (Count); Fili Email; Filial</v>
-      </c>
-      <c r="F307" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="str">
-        <v>Campanha de incentivo GU Q1 FY26</v>
-      </c>
-      <c r="B308" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
-      </c>
-      <c r="C308" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
-      </c>
-      <c r="D308" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
-      </c>
-      <c r="E308" t="str">
-        <v>CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; FILI_CDSITE; FILI_CDTIPOATUACAO; FILI_CDTIPOCC; FILI_CDTIPOCONTRATO; FILI_CDTIPOSERVICO; FILI_CDTIPOSUBSERVICO; FILI_CEP; FILI_CIDADE; FILI_CODIGO; FILI_DTABERTURA; FILI_DTENCERRAMENTO; FILI_EMAIL; FILI_EMAILBUSINESSUNIT; FILI_EMAILDIROPERACIONAL; FILI_EMAILDIRSEGMENTO; % Fidelização; % Horas Extras; % Rotatividade; % Rotatividade Acumulada; Bairro; Bh Credito Mes; Bh Descanso; Bh Horas Pagas; Bh Saldo Anterior; Bh Saldo Atual; Cargo Elegivel Jovem Aprendiz; CBO; Cd Business Unit; Cd Cargo; Cd Cargo HR Reporting; % Notas fora; Filial; Planilha1 (Count); Resolvidas trimestre; Total emitidas (qtd)</v>
-      </c>
-      <c r="F308" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="str">
-        <v>Campanha de incentivo GU Q1 FY26</v>
-      </c>
-      <c r="B309" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/CampanhadeincentivoGUQ1/CampanhadeincentivoGU</v>
-      </c>
-      <c r="C309" t="str">
-        <v>Contabil; Contabil_Conta; RH - Colaborador Folha; Planilha1 (NOtas fora trimestre)</v>
-      </c>
-      <c r="D309" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/56353/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/2428/lineage</v>
-      </c>
-      <c r="E309" t="str">
-        <v/>
-      </c>
-      <c r="F309" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="str">
-        <v>Conferência_FM</v>
-      </c>
-      <c r="B310" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_FM/ConfernciaFM</v>
-      </c>
-      <c r="C310" t="str">
-        <v>NL.TXT+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D310" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1765/lineage</v>
-      </c>
-      <c r="E310" t="str">
-        <v>0; Ação (CC,Mun. Emitente); Aliq INSS; Aliq IRF; Aliq ISS; Aliq PIS; AlIq. CSLL; AliqCOFINS; Área De Hierarquia; Cálculo1; CC; Centro; Centro de Lucro; CL; CL de Mandato.; CL Mandato; CL NL; CL NL TESTE; Cliente; CNPJ Cli; CNPJ Emit.; CNPJ FIL.; Cod. Cliente; Código Material; Cofins; COFINS Ret; CSLL Ret; Data Comp; Data de lançamento; Data do faturamento; Descrição; Descrição Material; Descrição NCM; Descripção do area de hierarquia standar; DIF 0; Diferença; Doc Contábil; Doc.Comp.; DocFat.; Documento de vendas</v>
-      </c>
-      <c r="F310" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="str">
-        <v>Conferência_FM</v>
-      </c>
-      <c r="B311" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Conferncia_FM/ConfernciaFM</v>
-      </c>
-      <c r="C311" t="str">
-        <v>NL.TXT+ (Múltiplas conexões)</v>
-      </c>
-      <c r="D311" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1765/lineage</v>
-      </c>
-      <c r="E311" t="str">
-        <v/>
-      </c>
-      <c r="F311" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="str">
-        <v>Painel de ST - MG</v>
-      </c>
-      <c r="B312" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeST-MG/ST-MG</v>
-      </c>
-      <c r="C312" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D312" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E312" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_BUSINESS_UNIT; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; Cod Csosn; Cod Csosn (F Ai Ne Nfe Imposto Icmssn202); Cod Csosn (F Ai Ne Nfe Imposto Icmssn500); Cod Csosn (F Ai Ne Nfe Imposto Icmssn900); Cod Cst; Cod Cst (F Ai Ne Nfe Imposto Icms30); Cod Cst (F Ai Ne Nfe Imposto Icms60); Cod Cst (F Ai Ne Nfe Imposto Icms70); Cod Cst (F Ai Ne Nfe Imposto Icms90); Cod Cst (F Ai Ne Nfe Imposto Icmspart); Cod Cst (F Ai Ne Nfe Imposto Icmsst); Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf</v>
-      </c>
-      <c r="F312" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="str">
-        <v>Painel de ST - MG</v>
-      </c>
-      <c r="B313" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PaineldeST-MG/ST-MG</v>
-      </c>
-      <c r="C313" t="str">
-        <v>BIVarredura - XML NF Item</v>
-      </c>
-      <c r="D313" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage</v>
-      </c>
-      <c r="E313" t="str">
-        <v/>
-      </c>
-      <c r="F313" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="str">
-        <v>FI01 - Mapa Fiscal - Extração - V4</v>
-      </c>
-      <c r="B314" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V4/Painel-MapaFiscalporUF</v>
-      </c>
-      <c r="C314" t="str">
-        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
-      </c>
-      <c r="D314" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/424/lineage</v>
-      </c>
-      <c r="E314" t="str">
-        <v>Aliquotadifal; Aliquotadiferenca; Aliquotainterna; Aliquotaorigem; Basedecalculo; Cd Filial; Cnpjremetente; Dados migrados (Count); Dtcompetencia; Dtlancamento; Ieremetente; Impostocreditado; Isentas; Nronf; Number of Records; Outras; Percaliqinterestadual; Percaliqinterna; Percdiferencialaliquota; Serie; Sk Aliquotauf Od; Sk Aliquotauf Od (D Aliquotauf Od); Sk Filial; Uf Destino; Uf Origem; Uf Origemdestino; Uffilial; Ufremetente; Valorcontabil; Valordiferencialaliquota; VL Difal; Vlraliqinterest; Vlraliqinterna; Cargauf; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial (Vw D Filial); Cd Filial Ficticia; Cd Lancamento; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Uf; Cd Uf (Vw D Filial); Cfop; Cnpjdestinatario; Conta Contabil; Creditoentradas; Dt Abertura; Dt Ano Mes; Dt Carga; Dt Carga (Vw D Tempo); Dt Encerramento; Dtcompetencia filtra ate jan21; Filial; FILIAL UF; Centrodelucro; Competencia; SK_FILIAL; VALOR_CALCULO; VL Outros Créditos; VL OutrosCreditos Calculo; Cd Contacontabil; Chavelancamento; Conta Contabil (grupo); Contacontabil; Dt Carga (Vw D Filial); Estornocom; Fl Ficticia; Hierarquia; Inscricaoestadual; Locnegocios; Nm Bairro; Nm Cardapio; Nm Cidade; Nm Contacontabil; Nm Diretor Operacional; Nm Diretoria</v>
-      </c>
-      <c r="F314" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="str">
-        <v>FI01 - Mapa Fiscal - Extração - V4</v>
-      </c>
-      <c r="B315" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FI01-MapaFiscal-Extrao-V4/Painel-MapaFiscalporUF</v>
-      </c>
-      <c r="C315" t="str">
-        <v>F_ZFI074; NF Header; OutrosCreditos; Razão</v>
-      </c>
-      <c r="D315" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/424/lineage</v>
-      </c>
-      <c r="E315" t="str">
-        <v/>
-      </c>
-      <c r="F315" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="str">
-        <v>Painel ICMS ST SP V3</v>
-      </c>
-      <c r="B316" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelICMSSTSPV3/PainelICMSSTSP</v>
-      </c>
-      <c r="C316" t="str">
-        <v>BIVarredura - XML NF Item; Tabela NCM credito ST SP</v>
-      </c>
-      <c r="D316" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1666/lineage</v>
-      </c>
-      <c r="E316" t="str">
-        <v>Status XML; :Measure Names; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Descrição; NCM; NCM editado; Relacionamento NCM; Tabela NCM credito ST SP.csv (Count)</v>
-      </c>
-      <c r="F316" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="str">
-        <v>Painel ICMS ST SP V3</v>
-      </c>
-      <c r="B317" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/PainelICMSSTSPV3/PainelICMSSTSP</v>
-      </c>
-      <c r="C317" t="str">
-        <v>BIVarredura - XML NF Item; Tabela NCM credito ST SP</v>
-      </c>
-      <c r="D317" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53691/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1666/lineage</v>
-      </c>
-      <c r="E317" t="str">
-        <v/>
-      </c>
-      <c r="F317" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="str">
-        <v>Retenção FY24</v>
-      </c>
-      <c r="B318" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Reteno/RetenoFY24</v>
-      </c>
-      <c r="C318" t="str">
-        <v>Centro_Lucro; Contabil; Planilha1 (Target diretoria); Retention; Sheet1 (Target Segmento)</v>
-      </c>
-      <c r="D318" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1209/lineage</v>
-      </c>
-      <c r="E318" t="str">
-        <v>Dados migrados (Count); FILI_BAIRRO; FILI_CDBUSINESSUNIT; FILI_CDCONTRATO; FILI_CDDIRETORIA; FILI_CDEMPRESA; FILI_CDGRUPOECONOMICO; FILI_CDGRUPORESULTADO; FILI_CDILAGRUPO; FILI_CDMATRIZCARDAPIO; FILI_CDPAIS; FILI_CDREGIONAL; FILI_CDSEGMENTO; FILI_CDSEGMENTOGRUPO; FILI_CDSERVICOGRUPO; CONT_DTFECHAMENTO; CONT_GRUPO_CONTA; CONT_TIMESTAMP; CONT_VLORCADO; CONT_VLREALIZADO; %; % Retenção FY24; % total target; Diretoria; Planilha1 (Count); Target; Valor; # Of Employees; # Of Meals; % Gp; % GP anual; % Gp Ytd; :Measure Names; Annual Gross Profit during previous Fiscal year; Annual Revenue during previous Fiscal year; City; Client1; Closing date; Company; Competitor; Contract End; Contract Start; Directorship; Economic Group; GP YTD without IFRS16; Loss Reason; Notification date; PC Code; PC Name; Period1; Reason for losing1; Regional; Retention (Count); Revenue YTD; Segment1; Service; Site Code; Site Name; UF; UF, City; Valores do Competidor; Vigência do Contrato do Competidor; % Target retenção; Fat Fy23; Sheet1 (Count); Target %; Target valor</v>
-      </c>
-      <c r="F318" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="str">
-        <v>Retenção FY24</v>
-      </c>
-      <c r="B319" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Reteno/RetenoFY24</v>
-      </c>
-      <c r="C319" t="str">
-        <v>Centro_Lucro; Contabil; Planilha1 (Target diretoria); Retention; Sheet1 (Target Segmento)</v>
-      </c>
-      <c r="D319" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/48339/lineage; https://analyticsbi.sodexo.com.br/#/datasources/48329/lineage; https://analyticsbi.sodexo.com.br/#/workbooks/1209/lineage</v>
-      </c>
-      <c r="E319" t="str">
-        <v/>
-      </c>
-      <c r="F319" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="str">
-        <v>FISCAL12 - XML Extração ICMS</v>
-      </c>
-      <c r="B320" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL12-XMLExtraoICMS/PainelXMLExtraoICMS</v>
-      </c>
-      <c r="C320" t="str">
-        <v>BIVARREDURA - XML EXTRAÇÃO ICMS</v>
-      </c>
-      <c r="D320" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1837/lineage</v>
-      </c>
-      <c r="E320" t="str">
-        <v>COD_CHAVE_NFE; index; NE_COD_UNIDADE; NE_DTA_RECEBIMENTO; NE_OPERACAO; VLR_VICMSST; XML (Count); XML_CNPJ_DESTINATARIO; XML_CNPJ_FORNECEDOR; XML_DTEMISSAO; XML_IE_DESTINATARIO; XML_NMFORNECEDOR; XML_NRONOTAFISCAL; XML_NROSERIE; XML_OBSERVACAO_ADICIONAL; XML_UF_DESTINATARIO; XML_VL_PRODUTOS; XMLI_COD_CFOP; XMLI_COD_CST; XMLI_COD_CST_COFINSALIQ; XMLI_COD_CST_PISALIQ; XMLI_COD_ITEM; XMLI_COD_NCM; XMLI_DES_ITEM; XMLI_NUM_ITEM; XMLI_VLR_ICMS; XMLI_VLR_TOTAL; XMLI_VLR_VCOFINS_COFINSALIQ; XMLI_VLR_VPIS_PISALIQ</v>
-      </c>
-      <c r="F320" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="str">
-        <v>FISCAL12 - XML Extração ICMS</v>
-      </c>
-      <c r="B321" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL12-XMLExtraoICMS/PainelXMLExtraoICMS</v>
-      </c>
-      <c r="C321" t="str">
-        <v>BIVARREDURA - XML EXTRAÇÃO ICMS</v>
-      </c>
-      <c r="D321" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/1837/lineage</v>
-      </c>
-      <c r="E321" t="str">
-        <v/>
-      </c>
-      <c r="F321" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="str">
-        <v>FISCAL01 - Painel de Erro Rotina de Envio Ciência Automática</v>
-      </c>
-      <c r="B322" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL01-PaineldeErroRotinadeEnvioCinciaAutomtica/CheckErro-RotinadeEnviodeCinciaAutomtica</v>
-      </c>
-      <c r="C322" t="str">
-        <v>Varredura - XML NF Header</v>
-      </c>
-      <c r="D322" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E322" t="str">
-        <v>Status XML; :Measure Names; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Business Unit; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Mascara 20 NL; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd pessoal NL; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CD_GRUPO_ECONOMICO; CFOP_VENDA; Ciencia; CNPJ Fornecedor NL; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; COD_REGIAO; Dados migrados (Count); Des Uf; Dia Vcto</v>
-      </c>
-      <c r="F322" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="str">
-        <v>FISCAL01 - Painel de Erro Rotina de Envio Ciência Automática</v>
-      </c>
-      <c r="B323" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL01-PaineldeErroRotinadeEnvioCinciaAutomtica/CheckErro-RotinadeEnviodeCinciaAutomtica</v>
-      </c>
-      <c r="C323" t="str">
-        <v>Varredura - XML NF Header</v>
-      </c>
-      <c r="D323" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/datasources/53690/lineage</v>
-      </c>
-      <c r="E323" t="str">
-        <v/>
-      </c>
-      <c r="F323" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="str">
-        <v>Conciliação ISS Serviços Tomados</v>
-      </c>
-      <c r="B324" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ConciliaoISSServiosTomados/ISSServTomados</v>
-      </c>
-      <c r="C324" t="str">
-        <v>PREFEITURA++ (Múltiplas conexões)</v>
-      </c>
-      <c r="D324" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E324" t="str">
-        <v>:Measure Names; Alíquota; Aliquota ISS; Bairro do Prestador; Bairro do Tomador; Centro; Centro Custo; CEP do Prestador; CEP do Tomador; Cidade Centro; Cidade do Prestador; Cidade do Tomador; Cidade Filial; Cidade Recolhimento; CNPJ Centro; CNPJ do Prestador; CNPJ Filial; COD SERV SAP; Cod. Fornecedor; Código Imposto; Complemento do Endereço do Prestador; Complemento do Endereço do Tomador; CPF/CNPJ do Tomador; Data de Cancelamento; Data de Quitação da Guia Vinculada a Nota Fiscal; Data Hora NFE; Data SAP; Desc. Conta Despesa; Descrição do Material; Descrição NCM; Discriminação dos Serviços; Doc. Contabil; Doc. Estorno; Doc. Fiscal; Domicílio Centro; Domicílio Filial; Domicílio Recolhimento; Dt. Documento; Dt. Pagamento; Email do Prestador</v>
-      </c>
-      <c r="F324" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="str">
-        <v>Conciliação ISS Serviços Tomados</v>
-      </c>
-      <c r="B325" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/ConciliaoISSServiosTomados/ISSServTomados</v>
-      </c>
-      <c r="C325" t="str">
-        <v>PREFEITURA++ (Múltiplas conexões)</v>
-      </c>
-      <c r="D325" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E325" t="str">
-        <v/>
-      </c>
-      <c r="F325" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="str">
-        <v>Indicadores - ISS Próprio</v>
-      </c>
-      <c r="B326" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadores-ISSPrprio/Indicadores-ISSPrprio</v>
-      </c>
-      <c r="C326" t="str">
-        <v>Base_original (indicadores V2)</v>
-      </c>
-      <c r="D326" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E326" t="str">
-        <v/>
-      </c>
-      <c r="F326" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="str">
-        <v>Indicadores - ISS Próprio</v>
-      </c>
-      <c r="B327" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/Indicadores-ISSPrprio/Indicadores-ISSPrprio</v>
-      </c>
-      <c r="C327" t="str">
-        <v>Base_original (indicadores V2)</v>
-      </c>
-      <c r="D327" t="str">
-        <v>Sem link de datasource no Tableau; fonte embutida/planilha ou conexao sem Custom SQL Query</v>
-      </c>
-      <c r="E327" t="str">
-        <v>Base_original (Count); CL; Erro; Mês; Município; Observação; Serviço; Tipo</v>
-      </c>
-      <c r="F327" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="str">
-        <v>Notas emitidas x lançadas BRF e Ecolab</v>
-      </c>
-      <c r="B328" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasemitidasxlanadasBRFeEcolab/PainelNF</v>
-      </c>
-      <c r="C328" t="str">
-        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
-      </c>
-      <c r="D328" t="str">
-        <v>Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
-      </c>
-      <c r="E328" t="str">
-        <v>Status XML; :Measure Names; CD; Cd Ano Mes; Cd Ano Mes (Vw D Tempo); Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz</v>
-      </c>
-      <c r="F328" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="str">
-        <v>Notas emitidas x lançadas BRF e Ecolab</v>
-      </c>
-      <c r="B329" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/NotasemitidasxlanadasBRFeEcolab/PainelNF</v>
-      </c>
-      <c r="C329" t="str">
-        <v>BIVarredura - XML NF Item; BIVarredura - XML NF Supply</v>
-      </c>
-      <c r="D329" t="str">
-        <v>Planilha ou fonte sem Custom SQL Query identificavel; https://analyticsbi.sodexo.com.br/#/datasources/3041/lineage</v>
-      </c>
-      <c r="E329" t="str">
-        <v/>
-      </c>
-      <c r="F329" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="str">
-        <v>FISCAL04 - Painel Gestão do Manifesto - Filtro por Data Emissão</v>
-      </c>
-      <c r="B330" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto-FiltroporDataEmisso/Painel-GestodoManifesto</v>
-      </c>
-      <c r="C330" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
-      </c>
-      <c r="D330" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/299/lineage</v>
-      </c>
-      <c r="E330" t="str">
-        <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CFOP_VENDA; Chave NFe; Ciencia; Cod Gu; Cod Operadora; Cod Pais; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Digitação; Dsc Tipoprocesso; DSC_FLAGNFE; Dt Abertura; Dt Ano Mes; Dt Carga; XMLI_COD_CFOP; XMLI_DES_CHAVE_NFE</v>
-      </c>
-      <c r="F330" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="str">
-        <v>FISCAL04 - Painel Gestão do Manifesto - Filtro por Data Emissão</v>
-      </c>
-      <c r="B331" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL04-PainelGestodoManifesto-FiltroporDataEmisso/Painel-GestodoManifesto</v>
-      </c>
-      <c r="C331" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA); Filtro CFOP (BIVARREDURA)</v>
-      </c>
-      <c r="D331" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/299/lineage</v>
-      </c>
-      <c r="E331" t="str">
-        <v/>
-      </c>
-      <c r="F331" t="str">
-        <v>Nao e Campo Calculado</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="str">
-        <v>FISCAL07 - Painel Gestão de Fornecedores</v>
-      </c>
-      <c r="B332" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL07-PainelGestodeFornecedores/Painel-GestodeFornecedores</v>
-      </c>
-      <c r="C332" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
-      </c>
-      <c r="D332" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/289/lineage</v>
-      </c>
-      <c r="E332" t="str">
         <v>Descrição; Dtfim; DTFIM_XMLNF; Dtinicio; Number of Records; :Measure Names; Cd Ano Mes; Cd Cardapio; Cd Centro Custo; Cd Diretoria; Cd Empresa Sodexo; Cd Filial; Cd Filial Ficticia; Cd Matricula Diretor Operac; Cd Matricula Gerente Area; Cd Matricula Gerente Regional; Cd Matriz; Cd Regional; Cd Segmento; Cd Tipo Atuacao; Cd Tipo Contrato; Cd Tipo Servico; Cd Tipoprocesso; Cd Uf; CD_FLAGNFE; CFOP_VENDA; Chave NFe; Check CNPJ Destinatario; Ciencia; Cod Gu; Cód NL; Cod Operadora; Cod Pais; Cód SAP; Cod Sefaz; Cod Uf; Cod Uf Gia; Cod Uf Nfe; Des Uf; Dia Vcto; DiasCiencia; DiasSemManifestação; Diretoria; Dsc Tipoprocesso; Dt Abertura</v>
-      </c>
-      <c r="F332" t="str">
-        <v>Campo Calculado</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="str">
-        <v>FISCAL07 - Painel Gestão de Fornecedores</v>
-      </c>
-      <c r="B333" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/views/FISCAL07-PainelGestodeFornecedores/Painel-GestodeFornecedores</v>
-      </c>
-      <c r="C333" t="str">
-        <v>F_XMLNF_HEADER_LOG (BIVARREDURA); F_XMLNF_HEADER+ (BIVARREDURA)</v>
-      </c>
-      <c r="D333" t="str">
-        <v>https://analyticsbi.sodexo.com.br/#/workbooks/289/lineage</v>
-      </c>
-      <c r="E333" t="str">
-        <v/>
-      </c>
-      <c r="F333" t="str">
-        <v>Nao e Campo Calculado</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F333"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E167"/>
   </ignoredErrors>
 </worksheet>
 </file>